--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30309"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B74CCCFB-9025-4911-9635-E3C3B97009EF}"/>
+  <xr:revisionPtr revIDLastSave="464" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8809713-4E18-4D4C-B370-A82EE7544C86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -660,7 +660,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,27 +1212,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O109"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.26953125" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1279,7 +1280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1294,11 +1295,11 @@
       </c>
       <c r="E2" s="13">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F2" s="11">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>16</v>
@@ -1323,7 +1324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1338,11 +1339,11 @@
       </c>
       <c r="E3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1367,7 +1368,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1382,11 +1383,11 @@
       </c>
       <c r="E4" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1411,7 +1412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1426,11 +1427,11 @@
       </c>
       <c r="E5" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F5" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1455,7 +1456,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1470,11 +1471,11 @@
       </c>
       <c r="E6" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1499,7 +1500,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1514,11 +1515,11 @@
       </c>
       <c r="E7" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1543,7 +1544,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1558,11 +1559,11 @@
       </c>
       <c r="E8" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-158</v>
+        <v>-162</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1587,7 +1588,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1602,11 +1603,11 @@
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-395</v>
+        <v>-399</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1629,7 +1630,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1644,11 +1645,11 @@
       </c>
       <c r="E10" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1671,7 +1672,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1686,11 +1687,11 @@
       </c>
       <c r="E11" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1715,7 +1716,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1730,11 +1731,11 @@
       </c>
       <c r="E12" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -1760,7 +1761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -1775,11 +1776,11 @@
       </c>
       <c r="E13" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -1805,7 +1806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -1820,11 +1821,11 @@
       </c>
       <c r="E14" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -1848,7 +1849,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
@@ -1863,11 +1864,11 @@
       </c>
       <c r="E15" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -1893,7 +1894,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
@@ -1908,11 +1909,11 @@
       </c>
       <c r="E16" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -1936,7 +1937,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -1951,11 +1952,11 @@
       </c>
       <c r="E17" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -1979,7 +1980,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>50</v>
       </c>
@@ -1994,11 +1995,11 @@
       </c>
       <c r="E18" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2022,7 +2023,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>52</v>
       </c>
@@ -2037,11 +2038,11 @@
       </c>
       <c r="E19" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
@@ -2065,7 +2066,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>53</v>
       </c>
@@ -2080,11 +2081,11 @@
       </c>
       <c r="E20" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2108,7 +2109,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>54</v>
       </c>
@@ -2123,11 +2124,11 @@
       </c>
       <c r="E21" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F21" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2152,7 +2153,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
@@ -2167,11 +2168,11 @@
       </c>
       <c r="E22" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F22" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2196,7 +2197,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>56</v>
       </c>
@@ -2211,11 +2212,11 @@
       </c>
       <c r="E23" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F23" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2240,7 +2241,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
         <v>58</v>
       </c>
@@ -2255,11 +2256,11 @@
       </c>
       <c r="E24" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="31" t="s">
         <v>59</v>
@@ -2286,7 +2287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="23" t="s">
         <v>58</v>
       </c>
@@ -2301,11 +2302,11 @@
       </c>
       <c r="E25" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F25" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>59</v>
@@ -2332,7 +2333,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>58</v>
       </c>
@@ -2347,11 +2348,11 @@
       </c>
       <c r="E26" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F26" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2378,7 +2379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
@@ -2393,11 +2394,11 @@
       </c>
       <c r="E27" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F27" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2424,7 +2425,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="30" customFormat="1">
+    <row r="28" spans="1:15" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>62</v>
       </c>
@@ -2439,11 +2440,11 @@
       </c>
       <c r="E28" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F28" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5282</v>
+        <v>5278</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>63</v>
@@ -2467,7 +2468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="30" customFormat="1">
+    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>62</v>
       </c>
@@ -2482,11 +2483,11 @@
       </c>
       <c r="E29" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F29" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>32</v>
@@ -2511,7 +2512,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>65</v>
       </c>
@@ -2526,11 +2527,11 @@
       </c>
       <c r="E30" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F30" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>66</v>
@@ -2555,7 +2556,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="23" t="s">
         <v>67</v>
       </c>
@@ -2570,11 +2571,11 @@
       </c>
       <c r="E31" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F31" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>16</v>
@@ -2599,7 +2600,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>68</v>
       </c>
@@ -2614,11 +2615,11 @@
       </c>
       <c r="E32" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F32" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2643,7 +2644,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
@@ -2658,11 +2659,11 @@
       </c>
       <c r="E33" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F33" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2687,7 +2688,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>70</v>
       </c>
@@ -2702,11 +2703,11 @@
       </c>
       <c r="E34" s="13">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F34" s="11">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -2731,7 +2732,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>71</v>
       </c>
@@ -2746,11 +2747,11 @@
       </c>
       <c r="E35" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F35" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -2775,7 +2776,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>72</v>
       </c>
@@ -2790,11 +2791,11 @@
       </c>
       <c r="E36" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F36" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>73</v>
@@ -2818,7 +2819,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
@@ -2833,11 +2834,11 @@
       </c>
       <c r="E37" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F37" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>75</v>
@@ -2861,7 +2862,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>76</v>
       </c>
@@ -2876,11 +2877,11 @@
       </c>
       <c r="E38" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F38" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>73</v>
@@ -2905,7 +2906,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>77</v>
       </c>
@@ -2920,11 +2921,11 @@
       </c>
       <c r="E39" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F39" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -2949,7 +2950,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>77</v>
       </c>
@@ -2964,11 +2965,11 @@
       </c>
       <c r="E40" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F40" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>78</v>
@@ -2993,7 +2994,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="23" t="s">
         <v>79</v>
       </c>
@@ -3008,11 +3009,11 @@
       </c>
       <c r="E41" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F41" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>80</v>
@@ -3036,7 +3037,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>83</v>
       </c>
@@ -3051,11 +3052,11 @@
       </c>
       <c r="E42" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F42" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3080,7 +3081,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>83</v>
       </c>
@@ -3095,11 +3096,11 @@
       </c>
       <c r="E43" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F43" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3124,7 +3125,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="30" customFormat="1">
+    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>84</v>
       </c>
@@ -3139,11 +3140,11 @@
       </c>
       <c r="E44" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F44" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>85</v>
@@ -3168,7 +3169,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>86</v>
       </c>
@@ -3183,11 +3184,11 @@
       </c>
       <c r="E45" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F45" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3212,7 +3213,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>87</v>
       </c>
@@ -3227,11 +3228,11 @@
       </c>
       <c r="E46" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F46" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3256,7 +3257,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>88</v>
       </c>
@@ -3271,11 +3272,11 @@
       </c>
       <c r="E47" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F47" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3300,7 +3301,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>89</v>
       </c>
@@ -3315,11 +3316,11 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F48" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>63</v>
@@ -3346,7 +3347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>90</v>
       </c>
@@ -3361,11 +3362,11 @@
       </c>
       <c r="E49" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F49" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>63</v>
@@ -3390,7 +3391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>91</v>
       </c>
@@ -3405,11 +3406,11 @@
       </c>
       <c r="E50" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F50" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3436,7 +3437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>91</v>
       </c>
@@ -3451,11 +3452,11 @@
       </c>
       <c r="E51" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F51" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3482,7 +3483,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>91</v>
       </c>
@@ -3497,11 +3498,11 @@
       </c>
       <c r="E52" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F52" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3528,7 +3529,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="30" customFormat="1">
+    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>93</v>
       </c>
@@ -3543,11 +3544,11 @@
       </c>
       <c r="E53" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>78</v>
@@ -3572,7 +3573,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="30" customFormat="1">
+    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>94</v>
       </c>
@@ -3587,11 +3588,11 @@
       </c>
       <c r="E54" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F54" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>63</v>
@@ -3616,7 +3617,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>95</v>
       </c>
@@ -3631,11 +3632,11 @@
       </c>
       <c r="E55" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F55" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3660,7 +3661,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>96</v>
       </c>
@@ -3675,11 +3676,11 @@
       </c>
       <c r="E56" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F56" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>97</v>
@@ -3704,7 +3705,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>96</v>
       </c>
@@ -3719,11 +3720,11 @@
       </c>
       <c r="E57" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F57" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>63</v>
@@ -3748,7 +3749,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>98</v>
       </c>
@@ -3763,11 +3764,11 @@
       </c>
       <c r="E58" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F58" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -3792,7 +3793,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
@@ -3807,11 +3808,11 @@
       </c>
       <c r="E59" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F59" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -3835,7 +3836,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
@@ -3850,11 +3851,11 @@
       </c>
       <c r="E60" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F60" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -3879,7 +3880,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>102</v>
       </c>
@@ -3894,11 +3895,11 @@
       </c>
       <c r="E61" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F61" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-197</v>
+        <v>-201</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>66</v>
@@ -3923,7 +3924,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>103</v>
       </c>
@@ -3938,11 +3939,11 @@
       </c>
       <c r="E62" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F62" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>104</v>
@@ -3967,7 +3968,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>105</v>
       </c>
@@ -3982,11 +3983,11 @@
       </c>
       <c r="E63" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F63" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G63" s="12" t="s">
         <v>66</v>
@@ -4011,7 +4012,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
         <v>105</v>
       </c>
@@ -4026,11 +4027,11 @@
       </c>
       <c r="E64" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F64" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>-137</v>
+        <v>-141</v>
       </c>
       <c r="G64" s="31" t="s">
         <v>16</v>
@@ -4055,7 +4056,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>106</v>
       </c>
@@ -4070,11 +4071,11 @@
       </c>
       <c r="E65" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F65" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>63</v>
@@ -4098,7 +4099,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>107</v>
       </c>
@@ -4113,11 +4114,11 @@
       </c>
       <c r="E66" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F66" s="11">
-        <f t="shared" ref="F66:F97" ca="1" si="7">D66-E66</f>
-        <v>-2023</v>
+        <f t="shared" ref="F66:F68" ca="1" si="7">D66-E66</f>
+        <v>-2027</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4142,7 +4143,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>107</v>
       </c>
@@ -4157,11 +4158,11 @@
       </c>
       <c r="E67" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F67" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>63</v>
@@ -4186,7 +4187,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="30" customFormat="1">
+    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
         <v>108</v>
       </c>
@@ -4201,11 +4202,11 @@
       </c>
       <c r="E68" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F68" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>32</v>
@@ -4230,7 +4231,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>109</v>
       </c>
@@ -4253,7 +4254,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="23" t="s">
         <v>109</v>
       </c>
@@ -4268,11 +4269,11 @@
       </c>
       <c r="E70" s="25">
         <f t="shared" ref="E70:E103" ca="1" si="8">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F70" s="27">
         <f t="shared" ref="F70:F103" ca="1" si="9">D70-E70</f>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G70" s="31" t="s">
         <v>22</v>
@@ -4295,7 +4296,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
         <v>110</v>
       </c>
@@ -4310,11 +4311,11 @@
       </c>
       <c r="E71" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F71" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4340,7 +4341,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
         <v>113</v>
       </c>
@@ -4355,11 +4356,11 @@
       </c>
       <c r="E72" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F72" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>66</v>
@@ -4382,7 +4383,7 @@
       <c r="N72" s="14"/>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>113</v>
       </c>
@@ -4397,11 +4398,11 @@
       </c>
       <c r="E73" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F73" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4426,7 +4427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
         <v>114</v>
       </c>
@@ -4441,11 +4442,11 @@
       </c>
       <c r="E74" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F74" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>32</v>
@@ -4472,7 +4473,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>114</v>
       </c>
@@ -4487,11 +4488,11 @@
       </c>
       <c r="E75" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F75" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>85</v>
@@ -4518,7 +4519,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>116</v>
       </c>
@@ -4533,11 +4534,11 @@
       </c>
       <c r="E76" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F76" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>23</v>
@@ -4564,7 +4565,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>118</v>
       </c>
@@ -4579,11 +4580,11 @@
       </c>
       <c r="E77" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F77" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>119</v>
@@ -4609,7 +4610,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
         <v>122</v>
       </c>
@@ -4624,11 +4625,11 @@
       </c>
       <c r="E78" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F78" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>34</v>
@@ -4653,7 +4654,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
         <v>124</v>
       </c>
@@ -4668,11 +4669,11 @@
       </c>
       <c r="E79" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F79" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>66</v>
@@ -4697,7 +4698,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>124</v>
       </c>
@@ -4712,11 +4713,11 @@
       </c>
       <c r="E80" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F80" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>26</v>
@@ -4741,7 +4742,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>124</v>
       </c>
@@ -4756,11 +4757,11 @@
       </c>
       <c r="E81" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F81" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -4785,7 +4786,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
         <v>125</v>
       </c>
@@ -4800,11 +4801,11 @@
       </c>
       <c r="E82" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F82" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>22</v>
@@ -4829,7 +4830,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>125</v>
       </c>
@@ -4844,11 +4845,11 @@
       </c>
       <c r="E83" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F83" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>16</v>
@@ -4873,7 +4874,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
         <v>126</v>
       </c>
@@ -4888,11 +4889,11 @@
       </c>
       <c r="E84" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F84" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>75</v>
@@ -4914,7 +4915,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
         <v>126</v>
       </c>
@@ -4929,11 +4930,11 @@
       </c>
       <c r="E85" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F85" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>34</v>
@@ -4957,7 +4958,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
         <v>126</v>
       </c>
@@ -4972,11 +4973,11 @@
       </c>
       <c r="E86" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F86" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>73</v>
@@ -5000,7 +5001,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>130</v>
       </c>
@@ -5015,11 +5016,11 @@
       </c>
       <c r="E87" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F87" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>21</v>
@@ -5042,7 +5043,7 @@
       <c r="N87" s="14"/>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>131</v>
       </c>
@@ -5057,11 +5058,11 @@
       </c>
       <c r="E88" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F88" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>31</v>
@@ -5086,7 +5087,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>132</v>
       </c>
@@ -5101,11 +5102,11 @@
       </c>
       <c r="E89" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F89" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>104</v>
@@ -5127,7 +5128,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
         <v>134</v>
       </c>
@@ -5142,11 +5143,11 @@
       </c>
       <c r="E90" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F90" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>22</v>
@@ -5171,7 +5172,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>134</v>
       </c>
@@ -5186,11 +5187,11 @@
       </c>
       <c r="E91" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F91" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>16</v>
@@ -5213,7 +5214,7 @@
       <c r="N91" s="14"/>
       <c r="O91" s="19"/>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>135</v>
       </c>
@@ -5228,11 +5229,11 @@
       </c>
       <c r="E92" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F92" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>136</v>
@@ -5257,7 +5258,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
         <v>137</v>
       </c>
@@ -5272,11 +5273,11 @@
       </c>
       <c r="E93" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F93" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G93" s="31" t="s">
         <v>26</v>
@@ -5303,7 +5304,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="23" t="s">
         <v>137</v>
       </c>
@@ -5318,11 +5319,11 @@
       </c>
       <c r="E94" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F94" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G94" s="31" t="s">
         <v>16</v>
@@ -5349,7 +5350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>138</v>
       </c>
@@ -5364,11 +5365,11 @@
       </c>
       <c r="E95" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F95" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>31</v>
@@ -5393,7 +5394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="30" customFormat="1">
+    <row r="96" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23" t="s">
         <v>139</v>
       </c>
@@ -5408,11 +5409,11 @@
       </c>
       <c r="E96" s="25">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F96" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G96" s="31" t="s">
         <v>32</v>
@@ -5437,7 +5438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.25" customHeight="1">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
         <v>140</v>
       </c>
@@ -5452,11 +5453,11 @@
       </c>
       <c r="E97" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F97" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>21</v>
@@ -5481,7 +5482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
         <v>141</v>
       </c>
@@ -5496,11 +5497,11 @@
       </c>
       <c r="E98" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F98" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>85</v>
@@ -5525,7 +5526,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>142</v>
       </c>
@@ -5540,11 +5541,11 @@
       </c>
       <c r="E99" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F99" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>31</v>
@@ -5569,7 +5570,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="8" t="s">
         <v>143</v>
       </c>
@@ -5584,11 +5585,11 @@
       </c>
       <c r="E100" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F100" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>104</v>
@@ -5613,7 +5614,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>144</v>
       </c>
@@ -5628,11 +5629,11 @@
       </c>
       <c r="E101" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F101" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>104</v>
@@ -5657,7 +5658,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
         <v>146</v>
       </c>
@@ -5672,11 +5673,11 @@
       </c>
       <c r="E102" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F102" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>16</v>
@@ -5701,7 +5702,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15" s="30" customFormat="1">
+    <row r="103" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
         <v>147</v>
       </c>
@@ -5716,11 +5717,11 @@
       </c>
       <c r="E103" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F103" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>148</v>
@@ -5745,7 +5746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
         <v>149</v>
       </c>
@@ -5770,7 +5771,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="8" t="s">
         <v>150</v>
       </c>
@@ -5785,11 +5786,11 @@
       </c>
       <c r="E105" s="14">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F105" s="11">
         <f ca="1">D105-E105</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -5812,7 +5813,7 @@
       <c r="N105" s="14"/>
       <c r="O105" s="19"/>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
         <v>150</v>
       </c>
@@ -5827,11 +5828,11 @@
       </c>
       <c r="E106" s="14">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F106" s="11">
         <f ca="1">D106-E106</f>
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -5856,7 +5857,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="8" t="s">
         <v>151</v>
       </c>
@@ -5871,11 +5872,11 @@
       </c>
       <c r="E107" s="14">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F107" s="11">
         <f ca="1">D107-E107</f>
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -5900,7 +5901,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>152</v>
       </c>
@@ -5915,11 +5916,11 @@
       </c>
       <c r="E108" s="14">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F108" s="11">
         <f ca="1">D108-E108</f>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>136</v>
@@ -5944,7 +5945,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
         <v>152</v>
       </c>
@@ -5959,11 +5960,11 @@
       </c>
       <c r="E109" s="14">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="F109" s="11">
         <f ca="1">D109-E109</f>
-        <v>-2023</v>
+        <v>-2027</v>
       </c>
       <c r="G109" s="12" t="s">
         <v>31</v>
@@ -5990,6 +5991,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N109" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="AVULSO"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N109">
       <sortCondition ref="A1:A109"/>
     </sortState>
@@ -6001,25 +6007,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6063,7 +6069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>158</v>
       </c>
@@ -6101,7 +6107,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>163</v>
       </c>
@@ -6139,7 +6145,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>165</v>
       </c>
@@ -6177,7 +6183,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>167</v>
       </c>
@@ -6215,7 +6221,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>168</v>
       </c>
@@ -6253,7 +6259,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
@@ -6291,7 +6297,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>171</v>
       </c>
@@ -6329,7 +6335,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>172</v>
       </c>
@@ -6367,7 +6373,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>173</v>
       </c>
@@ -6405,7 +6411,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>174</v>
       </c>
@@ -6443,7 +6449,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6481,7 +6487,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6519,7 +6525,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>175</v>
       </c>
@@ -6557,7 +6563,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>176</v>
       </c>
@@ -6595,7 +6601,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>178</v>
       </c>
@@ -6633,7 +6639,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>179</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>181</v>
       </c>
@@ -6709,7 +6715,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>182</v>
       </c>
@@ -6747,7 +6753,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>183</v>
       </c>
@@ -6785,7 +6791,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>184</v>
       </c>
@@ -6823,7 +6829,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -6861,7 +6867,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>186</v>
       </c>
@@ -6899,7 +6905,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>188</v>
       </c>
@@ -6937,7 +6943,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>189</v>
       </c>
@@ -6975,7 +6981,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>190</v>
       </c>
@@ -7013,7 +7019,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>191</v>
       </c>
@@ -7051,7 +7057,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>193</v>
       </c>
@@ -7089,7 +7095,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>194</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
@@ -7165,7 +7171,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>195</v>
       </c>
@@ -7203,7 +7209,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>196</v>
       </c>
@@ -7241,7 +7247,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>197</v>
       </c>
@@ -7279,7 +7285,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>199</v>
       </c>
@@ -7317,7 +7323,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>200</v>
       </c>
@@ -7355,7 +7361,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>201</v>
       </c>
@@ -7393,7 +7399,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>202</v>
       </c>
@@ -7431,7 +7437,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>202</v>
       </c>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
@@ -660,7 +660,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1214,26 +1214,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O109"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.26953125" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="4" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1295,11 +1295,11 @@
       </c>
       <c r="E2" s="13">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F2" s="11">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>16</v>
@@ -1324,7 +1324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1339,11 +1339,11 @@
       </c>
       <c r="E3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1368,7 +1368,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="E4" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1412,7 +1412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="E5" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F5" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1456,7 +1456,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1471,11 +1471,11 @@
       </c>
       <c r="E6" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1500,7 +1500,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1515,11 +1515,11 @@
       </c>
       <c r="E7" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1544,7 +1544,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1559,11 +1559,11 @@
       </c>
       <c r="E8" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1588,7 +1588,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-399</v>
+        <v>-401</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1630,7 +1630,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1645,11 +1645,11 @@
       </c>
       <c r="E10" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1672,7 +1672,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1687,11 +1687,11 @@
       </c>
       <c r="E11" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1716,7 +1716,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="E12" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -1761,7 +1761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -1776,11 +1776,11 @@
       </c>
       <c r="E13" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -1806,7 +1806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" hidden="1">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -1821,11 +1821,11 @@
       </c>
       <c r="E14" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -1849,7 +1849,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1">
       <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
@@ -1864,11 +1864,11 @@
       </c>
       <c r="E15" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -1894,7 +1894,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" hidden="1">
       <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="E16" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -1937,7 +1937,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" hidden="1">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -1952,11 +1952,11 @@
       </c>
       <c r="E17" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -1980,7 +1980,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15">
       <c r="A18" s="8" t="s">
         <v>50</v>
       </c>
@@ -1995,11 +1995,11 @@
       </c>
       <c r="E18" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2023,7 +2023,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15">
       <c r="A19" s="8" t="s">
         <v>52</v>
       </c>
@@ -2038,11 +2038,11 @@
       </c>
       <c r="E19" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
@@ -2066,7 +2066,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15">
       <c r="A20" s="8" t="s">
         <v>53</v>
       </c>
@@ -2081,11 +2081,11 @@
       </c>
       <c r="E20" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2109,7 +2109,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15">
       <c r="A21" s="8" t="s">
         <v>54</v>
       </c>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="E21" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F21" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2153,7 +2153,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15">
       <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
@@ -2168,11 +2168,11 @@
       </c>
       <c r="E22" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F22" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2197,7 +2197,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15">
       <c r="A23" s="8" t="s">
         <v>56</v>
       </c>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="E23" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F23" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2241,7 +2241,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" hidden="1">
       <c r="A24" s="23" t="s">
         <v>58</v>
       </c>
@@ -2256,11 +2256,11 @@
       </c>
       <c r="E24" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="G24" s="31" t="s">
         <v>59</v>
@@ -2287,7 +2287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" hidden="1">
       <c r="A25" s="23" t="s">
         <v>58</v>
       </c>
@@ -2302,11 +2302,11 @@
       </c>
       <c r="E25" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F25" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>59</v>
@@ -2333,7 +2333,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" hidden="1">
       <c r="A26" s="8" t="s">
         <v>58</v>
       </c>
@@ -2348,11 +2348,11 @@
       </c>
       <c r="E26" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F26" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2379,7 +2379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15">
       <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
@@ -2394,11 +2394,11 @@
       </c>
       <c r="E27" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F27" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2425,7 +2425,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" s="30" customFormat="1" hidden="1">
       <c r="A28" s="8" t="s">
         <v>62</v>
       </c>
@@ -2440,11 +2440,11 @@
       </c>
       <c r="E28" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F28" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5278</v>
+        <v>5276</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>63</v>
@@ -2468,7 +2468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" s="30" customFormat="1">
       <c r="A29" s="8" t="s">
         <v>62</v>
       </c>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="E29" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F29" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>32</v>
@@ -2512,7 +2512,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15">
       <c r="A30" s="8" t="s">
         <v>65</v>
       </c>
@@ -2527,11 +2527,11 @@
       </c>
       <c r="E30" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F30" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>66</v>
@@ -2556,7 +2556,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15">
       <c r="A31" s="23" t="s">
         <v>67</v>
       </c>
@@ -2571,11 +2571,11 @@
       </c>
       <c r="E31" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F31" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>16</v>
@@ -2600,7 +2600,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>68</v>
       </c>
@@ -2615,11 +2615,11 @@
       </c>
       <c r="E32" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F32" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2644,7 +2644,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15">
       <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="E33" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F33" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2688,7 +2688,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15">
       <c r="A34" s="8" t="s">
         <v>70</v>
       </c>
@@ -2703,11 +2703,11 @@
       </c>
       <c r="E34" s="13">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F34" s="11">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -2732,7 +2732,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15">
       <c r="A35" s="8" t="s">
         <v>71</v>
       </c>
@@ -2747,11 +2747,11 @@
       </c>
       <c r="E35" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F35" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -2776,7 +2776,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>72</v>
       </c>
@@ -2791,11 +2791,11 @@
       </c>
       <c r="E36" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F36" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>73</v>
@@ -2819,7 +2819,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15">
       <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
@@ -2834,11 +2834,11 @@
       </c>
       <c r="E37" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F37" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>75</v>
@@ -2862,7 +2862,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15">
       <c r="A38" s="8" t="s">
         <v>76</v>
       </c>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="E38" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F38" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>73</v>
@@ -2906,7 +2906,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15">
       <c r="A39" s="8" t="s">
         <v>77</v>
       </c>
@@ -2921,11 +2921,11 @@
       </c>
       <c r="E39" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F39" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -2950,7 +2950,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15">
       <c r="A40" s="8" t="s">
         <v>77</v>
       </c>
@@ -2965,11 +2965,11 @@
       </c>
       <c r="E40" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F40" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>78</v>
@@ -2994,7 +2994,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" hidden="1">
       <c r="A41" s="23" t="s">
         <v>79</v>
       </c>
@@ -3009,11 +3009,11 @@
       </c>
       <c r="E41" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F41" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>80</v>
@@ -3037,7 +3037,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15">
       <c r="A42" s="8" t="s">
         <v>83</v>
       </c>
@@ -3052,11 +3052,11 @@
       </c>
       <c r="E42" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F42" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3081,7 +3081,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15">
       <c r="A43" s="8" t="s">
         <v>83</v>
       </c>
@@ -3096,11 +3096,11 @@
       </c>
       <c r="E43" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F43" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3125,7 +3125,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" s="30" customFormat="1">
       <c r="A44" s="8" t="s">
         <v>84</v>
       </c>
@@ -3140,11 +3140,11 @@
       </c>
       <c r="E44" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F44" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>85</v>
@@ -3169,7 +3169,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15">
       <c r="A45" s="8" t="s">
         <v>86</v>
       </c>
@@ -3184,11 +3184,11 @@
       </c>
       <c r="E45" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F45" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3213,7 +3213,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15">
       <c r="A46" s="8" t="s">
         <v>87</v>
       </c>
@@ -3228,11 +3228,11 @@
       </c>
       <c r="E46" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F46" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3257,7 +3257,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15">
       <c r="A47" s="8" t="s">
         <v>88</v>
       </c>
@@ -3272,11 +3272,11 @@
       </c>
       <c r="E47" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F47" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3301,7 +3301,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15">
       <c r="A48" s="8" t="s">
         <v>89</v>
       </c>
@@ -3316,11 +3316,11 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F48" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>63</v>
@@ -3347,7 +3347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15">
       <c r="A49" s="8" t="s">
         <v>90</v>
       </c>
@@ -3362,11 +3362,11 @@
       </c>
       <c r="E49" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F49" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>63</v>
@@ -3391,7 +3391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" hidden="1">
       <c r="A50" s="8" t="s">
         <v>91</v>
       </c>
@@ -3406,11 +3406,11 @@
       </c>
       <c r="E50" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F50" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3437,7 +3437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" hidden="1">
       <c r="A51" s="8" t="s">
         <v>91</v>
       </c>
@@ -3452,11 +3452,11 @@
       </c>
       <c r="E51" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F51" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3483,7 +3483,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" hidden="1">
       <c r="A52" s="8" t="s">
         <v>91</v>
       </c>
@@ -3498,11 +3498,11 @@
       </c>
       <c r="E52" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F52" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3529,7 +3529,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" s="30" customFormat="1">
       <c r="A53" s="8" t="s">
         <v>93</v>
       </c>
@@ -3544,11 +3544,11 @@
       </c>
       <c r="E53" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>78</v>
@@ -3573,7 +3573,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" s="30" customFormat="1">
       <c r="A54" s="8" t="s">
         <v>94</v>
       </c>
@@ -3588,11 +3588,11 @@
       </c>
       <c r="E54" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F54" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>63</v>
@@ -3617,7 +3617,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15">
       <c r="A55" s="8" t="s">
         <v>95</v>
       </c>
@@ -3632,11 +3632,11 @@
       </c>
       <c r="E55" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F55" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3661,7 +3661,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15">
       <c r="A56" s="8" t="s">
         <v>96</v>
       </c>
@@ -3676,11 +3676,11 @@
       </c>
       <c r="E56" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F56" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>97</v>
@@ -3705,7 +3705,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15">
       <c r="A57" s="8" t="s">
         <v>96</v>
       </c>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="E57" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F57" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>63</v>
@@ -3749,7 +3749,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15">
       <c r="A58" s="8" t="s">
         <v>98</v>
       </c>
@@ -3764,11 +3764,11 @@
       </c>
       <c r="E58" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F58" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -3793,7 +3793,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" hidden="1">
       <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
@@ -3808,11 +3808,11 @@
       </c>
       <c r="E59" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F59" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -3836,7 +3836,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15">
       <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
@@ -3851,11 +3851,11 @@
       </c>
       <c r="E60" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F60" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -3880,7 +3880,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15">
       <c r="A61" s="8" t="s">
         <v>102</v>
       </c>
@@ -3895,11 +3895,11 @@
       </c>
       <c r="E61" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F61" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-201</v>
+        <v>-203</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>66</v>
@@ -3924,7 +3924,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15">
       <c r="A62" s="8" t="s">
         <v>103</v>
       </c>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="E62" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F62" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>104</v>
@@ -3968,7 +3968,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15">
       <c r="A63" s="8" t="s">
         <v>105</v>
       </c>
@@ -3983,11 +3983,11 @@
       </c>
       <c r="E63" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F63" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G63" s="12" t="s">
         <v>66</v>
@@ -4012,7 +4012,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15">
       <c r="A64" s="23" t="s">
         <v>105</v>
       </c>
@@ -4027,11 +4027,11 @@
       </c>
       <c r="E64" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F64" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>-141</v>
+        <v>-143</v>
       </c>
       <c r="G64" s="31" t="s">
         <v>16</v>
@@ -4056,7 +4056,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" hidden="1">
       <c r="A65" s="8" t="s">
         <v>106</v>
       </c>
@@ -4071,11 +4071,11 @@
       </c>
       <c r="E65" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F65" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>63</v>
@@ -4099,7 +4099,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15">
       <c r="A66" s="8" t="s">
         <v>107</v>
       </c>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="E66" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F66" s="11">
         <f t="shared" ref="F66:F68" ca="1" si="7">D66-E66</f>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4143,7 +4143,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15">
       <c r="A67" s="8" t="s">
         <v>107</v>
       </c>
@@ -4158,11 +4158,11 @@
       </c>
       <c r="E67" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F67" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>63</v>
@@ -4187,7 +4187,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" s="30" customFormat="1">
       <c r="A68" s="8" t="s">
         <v>108</v>
       </c>
@@ -4202,11 +4202,11 @@
       </c>
       <c r="E68" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F68" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>32</v>
@@ -4231,7 +4231,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15">
       <c r="A69" s="8" t="s">
         <v>109</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" hidden="1">
       <c r="A70" s="23" t="s">
         <v>109</v>
       </c>
@@ -4269,11 +4269,11 @@
       </c>
       <c r="E70" s="25">
         <f t="shared" ref="E70:E103" ca="1" si="8">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F70" s="27">
         <f t="shared" ref="F70:F103" ca="1" si="9">D70-E70</f>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G70" s="31" t="s">
         <v>22</v>
@@ -4296,7 +4296,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" hidden="1">
       <c r="A71" s="8" t="s">
         <v>110</v>
       </c>
@@ -4311,11 +4311,11 @@
       </c>
       <c r="E71" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F71" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4341,7 +4341,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15">
       <c r="A72" s="8" t="s">
         <v>113</v>
       </c>
@@ -4356,11 +4356,11 @@
       </c>
       <c r="E72" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F72" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>66</v>
@@ -4383,7 +4383,7 @@
       <c r="N72" s="14"/>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15">
       <c r="A73" s="8" t="s">
         <v>113</v>
       </c>
@@ -4398,11 +4398,11 @@
       </c>
       <c r="E73" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F73" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4427,7 +4427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15">
       <c r="A74" s="8" t="s">
         <v>114</v>
       </c>
@@ -4442,11 +4442,11 @@
       </c>
       <c r="E74" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F74" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>32</v>
@@ -4473,7 +4473,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15">
       <c r="A75" s="8" t="s">
         <v>114</v>
       </c>
@@ -4488,11 +4488,11 @@
       </c>
       <c r="E75" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F75" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>85</v>
@@ -4519,7 +4519,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" hidden="1">
       <c r="A76" s="8" t="s">
         <v>116</v>
       </c>
@@ -4534,11 +4534,11 @@
       </c>
       <c r="E76" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F76" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>23</v>
@@ -4565,7 +4565,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" hidden="1">
       <c r="A77" s="8" t="s">
         <v>118</v>
       </c>
@@ -4580,11 +4580,11 @@
       </c>
       <c r="E77" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F77" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>119</v>
@@ -4610,7 +4610,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" hidden="1">
       <c r="A78" s="8" t="s">
         <v>122</v>
       </c>
@@ -4625,11 +4625,11 @@
       </c>
       <c r="E78" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F78" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>34</v>
@@ -4654,7 +4654,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15">
       <c r="A79" s="8" t="s">
         <v>124</v>
       </c>
@@ -4669,11 +4669,11 @@
       </c>
       <c r="E79" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F79" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>66</v>
@@ -4698,7 +4698,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15">
       <c r="A80" s="8" t="s">
         <v>124</v>
       </c>
@@ -4713,11 +4713,11 @@
       </c>
       <c r="E80" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F80" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>26</v>
@@ -4742,7 +4742,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15">
       <c r="A81" s="8" t="s">
         <v>124</v>
       </c>
@@ -4757,11 +4757,11 @@
       </c>
       <c r="E81" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F81" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -4786,7 +4786,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15">
       <c r="A82" s="8" t="s">
         <v>125</v>
       </c>
@@ -4801,11 +4801,11 @@
       </c>
       <c r="E82" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F82" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>22</v>
@@ -4830,7 +4830,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15">
       <c r="A83" s="8" t="s">
         <v>125</v>
       </c>
@@ -4845,11 +4845,11 @@
       </c>
       <c r="E83" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F83" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>16</v>
@@ -4874,7 +4874,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" hidden="1">
       <c r="A84" s="8" t="s">
         <v>126</v>
       </c>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="E84" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F84" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>75</v>
@@ -4915,7 +4915,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" hidden="1">
       <c r="A85" s="8" t="s">
         <v>126</v>
       </c>
@@ -4930,11 +4930,11 @@
       </c>
       <c r="E85" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F85" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>34</v>
@@ -4958,7 +4958,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" hidden="1">
       <c r="A86" s="8" t="s">
         <v>126</v>
       </c>
@@ -4973,11 +4973,11 @@
       </c>
       <c r="E86" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F86" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>73</v>
@@ -5001,7 +5001,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15">
       <c r="A87" s="10" t="s">
         <v>130</v>
       </c>
@@ -5016,11 +5016,11 @@
       </c>
       <c r="E87" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F87" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>21</v>
@@ -5043,7 +5043,7 @@
       <c r="N87" s="14"/>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15">
       <c r="A88" s="10" t="s">
         <v>131</v>
       </c>
@@ -5058,11 +5058,11 @@
       </c>
       <c r="E88" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F88" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>31</v>
@@ -5087,7 +5087,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" hidden="1">
       <c r="A89" s="10" t="s">
         <v>132</v>
       </c>
@@ -5102,11 +5102,11 @@
       </c>
       <c r="E89" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F89" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>104</v>
@@ -5128,7 +5128,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15">
       <c r="A90" s="8" t="s">
         <v>134</v>
       </c>
@@ -5143,11 +5143,11 @@
       </c>
       <c r="E90" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F90" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>22</v>
@@ -5172,7 +5172,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15">
       <c r="A91" s="8" t="s">
         <v>134</v>
       </c>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="E91" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F91" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>16</v>
@@ -5214,7 +5214,7 @@
       <c r="N91" s="14"/>
       <c r="O91" s="19"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15">
       <c r="A92" s="8" t="s">
         <v>135</v>
       </c>
@@ -5229,11 +5229,11 @@
       </c>
       <c r="E92" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F92" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>136</v>
@@ -5258,7 +5258,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" hidden="1">
       <c r="A93" s="23" t="s">
         <v>137</v>
       </c>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="E93" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F93" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G93" s="31" t="s">
         <v>26</v>
@@ -5304,7 +5304,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" hidden="1">
       <c r="A94" s="23" t="s">
         <v>137</v>
       </c>
@@ -5319,11 +5319,11 @@
       </c>
       <c r="E94" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F94" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G94" s="31" t="s">
         <v>16</v>
@@ -5350,7 +5350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15">
       <c r="A95" s="8" t="s">
         <v>138</v>
       </c>
@@ -5365,11 +5365,11 @@
       </c>
       <c r="E95" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F95" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>31</v>
@@ -5394,7 +5394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" s="30" customFormat="1">
       <c r="A96" s="23" t="s">
         <v>139</v>
       </c>
@@ -5409,11 +5409,11 @@
       </c>
       <c r="E96" s="25">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F96" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G96" s="31" t="s">
         <v>32</v>
@@ -5438,7 +5438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>140</v>
       </c>
@@ -5453,11 +5453,11 @@
       </c>
       <c r="E97" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F97" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>21</v>
@@ -5482,7 +5482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15">
       <c r="A98" s="8" t="s">
         <v>141</v>
       </c>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="E98" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F98" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>85</v>
@@ -5526,7 +5526,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15">
       <c r="A99" s="8" t="s">
         <v>142</v>
       </c>
@@ -5541,11 +5541,11 @@
       </c>
       <c r="E99" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F99" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>31</v>
@@ -5570,7 +5570,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15">
       <c r="A100" s="8" t="s">
         <v>143</v>
       </c>
@@ -5585,11 +5585,11 @@
       </c>
       <c r="E100" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F100" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>104</v>
@@ -5614,7 +5614,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" hidden="1">
       <c r="A101" s="8" t="s">
         <v>144</v>
       </c>
@@ -5629,11 +5629,11 @@
       </c>
       <c r="E101" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F101" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>104</v>
@@ -5658,7 +5658,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15">
       <c r="A102" s="8" t="s">
         <v>146</v>
       </c>
@@ -5673,11 +5673,11 @@
       </c>
       <c r="E102" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F102" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>16</v>
@@ -5702,7 +5702,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" s="30" customFormat="1">
       <c r="A103" s="8" t="s">
         <v>147</v>
       </c>
@@ -5717,11 +5717,11 @@
       </c>
       <c r="E103" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F103" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>148</v>
@@ -5746,7 +5746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15">
       <c r="A104" s="8" t="s">
         <v>149</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15">
       <c r="A105" s="8" t="s">
         <v>150</v>
       </c>
@@ -5786,11 +5786,11 @@
       </c>
       <c r="E105" s="14">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F105" s="11">
         <f ca="1">D105-E105</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -5813,7 +5813,7 @@
       <c r="N105" s="14"/>
       <c r="O105" s="19"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15">
       <c r="A106" s="8" t="s">
         <v>150</v>
       </c>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="E106" s="14">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F106" s="11">
         <f ca="1">D106-E106</f>
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -5857,7 +5857,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15">
       <c r="A107" s="8" t="s">
         <v>151</v>
       </c>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="E107" s="14">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F107" s="11">
         <f ca="1">D107-E107</f>
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -5901,7 +5901,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15">
       <c r="A108" s="8" t="s">
         <v>152</v>
       </c>
@@ -5916,11 +5916,11 @@
       </c>
       <c r="E108" s="14">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F108" s="11">
         <f ca="1">D108-E108</f>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>136</v>
@@ -5945,7 +5945,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15">
       <c r="A109" s="8" t="s">
         <v>152</v>
       </c>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="E109" s="14">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F109" s="11">
         <f ca="1">D109-E109</f>
-        <v>-2027</v>
+        <v>-2029</v>
       </c>
       <c r="G109" s="12" t="s">
         <v>31</v>
@@ -6007,25 +6007,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="4" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>158</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>163</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>165</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
         <v>167</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
         <v>168</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
         <v>171</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
         <v>172</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
         <v>173</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>174</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
         <v>175</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
         <v>176</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
         <v>178</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
         <v>179</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="2" t="s">
         <v>181</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
         <v>182</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="2" t="s">
         <v>183</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
         <v>184</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
         <v>186</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="2" t="s">
         <v>188</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
         <v>189</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" s="2" t="s">
         <v>190</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
         <v>191</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" s="2" t="s">
         <v>193</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
         <v>194</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
         <v>195</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" s="2" t="s">
         <v>196</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
         <v>197</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" s="2" t="s">
         <v>199</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
         <v>200</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" s="2" t="s">
         <v>201</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
         <v>202</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" s="2" t="s">
         <v>202</v>
       </c>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="464" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8809713-4E18-4D4C-B370-A82EE7544C86}"/>
+  <xr:revisionPtr revIDLastSave="465" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B765FFF9-DED6-43AB-955C-1F8915F05EB3}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
@@ -660,7 +660,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,28 +1212,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O109"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.26953125" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1280,7 +1279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1295,11 +1294,11 @@
       </c>
       <c r="E2" s="13">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F2" s="11">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>16</v>
@@ -1324,7 +1323,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1339,11 +1338,11 @@
       </c>
       <c r="E3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1368,7 +1367,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1383,11 +1382,11 @@
       </c>
       <c r="E4" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1412,7 +1411,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1427,11 +1426,11 @@
       </c>
       <c r="E5" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F5" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1456,7 +1455,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1471,11 +1470,11 @@
       </c>
       <c r="E6" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1500,7 +1499,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1515,11 +1514,11 @@
       </c>
       <c r="E7" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1544,7 +1543,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1559,11 +1558,11 @@
       </c>
       <c r="E8" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1588,7 +1587,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1603,11 +1602,11 @@
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-401</v>
+        <v>-402</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1630,7 +1629,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1645,11 +1644,11 @@
       </c>
       <c r="E10" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1672,7 +1671,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1687,11 +1686,11 @@
       </c>
       <c r="E11" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1716,7 +1715,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1731,11 +1730,11 @@
       </c>
       <c r="E12" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -1761,7 +1760,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -1776,11 +1775,11 @@
       </c>
       <c r="E13" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -1806,7 +1805,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -1821,11 +1820,11 @@
       </c>
       <c r="E14" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -1849,7 +1848,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
@@ -1864,11 +1863,11 @@
       </c>
       <c r="E15" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -1894,7 +1893,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
@@ -1909,11 +1908,11 @@
       </c>
       <c r="E16" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -1937,7 +1936,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
@@ -1952,11 +1951,11 @@
       </c>
       <c r="E17" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -1980,7 +1979,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>50</v>
       </c>
@@ -1995,11 +1994,11 @@
       </c>
       <c r="E18" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2023,7 +2022,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>52</v>
       </c>
@@ -2038,11 +2037,11 @@
       </c>
       <c r="E19" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
@@ -2066,7 +2065,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>53</v>
       </c>
@@ -2081,11 +2080,11 @@
       </c>
       <c r="E20" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2109,7 +2108,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>54</v>
       </c>
@@ -2124,11 +2123,11 @@
       </c>
       <c r="E21" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F21" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2153,7 +2152,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
@@ -2168,11 +2167,11 @@
       </c>
       <c r="E22" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F22" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2197,7 +2196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>56</v>
       </c>
@@ -2212,11 +2211,11 @@
       </c>
       <c r="E23" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F23" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2241,7 +2240,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
         <v>58</v>
       </c>
@@ -2256,11 +2255,11 @@
       </c>
       <c r="E24" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G24" s="31" t="s">
         <v>59</v>
@@ -2287,7 +2286,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="23" t="s">
         <v>58</v>
       </c>
@@ -2302,11 +2301,11 @@
       </c>
       <c r="E25" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F25" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>59</v>
@@ -2333,7 +2332,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>58</v>
       </c>
@@ -2348,11 +2347,11 @@
       </c>
       <c r="E26" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F26" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2379,7 +2378,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
@@ -2394,11 +2393,11 @@
       </c>
       <c r="E27" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F27" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2425,7 +2424,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="30" customFormat="1" hidden="1">
+    <row r="28" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>62</v>
       </c>
@@ -2440,11 +2439,11 @@
       </c>
       <c r="E28" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F28" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>63</v>
@@ -2468,7 +2467,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="30" customFormat="1">
+    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>62</v>
       </c>
@@ -2483,11 +2482,11 @@
       </c>
       <c r="E29" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F29" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>32</v>
@@ -2512,7 +2511,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>65</v>
       </c>
@@ -2527,11 +2526,11 @@
       </c>
       <c r="E30" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F30" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>66</v>
@@ -2556,7 +2555,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="23" t="s">
         <v>67</v>
       </c>
@@ -2571,11 +2570,11 @@
       </c>
       <c r="E31" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F31" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>16</v>
@@ -2600,7 +2599,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>68</v>
       </c>
@@ -2615,11 +2614,11 @@
       </c>
       <c r="E32" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F32" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2644,7 +2643,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
@@ -2659,11 +2658,11 @@
       </c>
       <c r="E33" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F33" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2688,7 +2687,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>70</v>
       </c>
@@ -2703,11 +2702,11 @@
       </c>
       <c r="E34" s="13">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F34" s="11">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -2732,7 +2731,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>71</v>
       </c>
@@ -2747,11 +2746,11 @@
       </c>
       <c r="E35" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F35" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -2776,7 +2775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>72</v>
       </c>
@@ -2791,11 +2790,11 @@
       </c>
       <c r="E36" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F36" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>73</v>
@@ -2819,7 +2818,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
@@ -2834,11 +2833,11 @@
       </c>
       <c r="E37" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F37" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>75</v>
@@ -2862,7 +2861,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>76</v>
       </c>
@@ -2877,11 +2876,11 @@
       </c>
       <c r="E38" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F38" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>73</v>
@@ -2906,7 +2905,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>77</v>
       </c>
@@ -2921,11 +2920,11 @@
       </c>
       <c r="E39" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F39" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -2950,7 +2949,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>77</v>
       </c>
@@ -2965,11 +2964,11 @@
       </c>
       <c r="E40" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F40" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>78</v>
@@ -2994,7 +2993,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="23" t="s">
         <v>79</v>
       </c>
@@ -3009,11 +3008,11 @@
       </c>
       <c r="E41" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F41" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>80</v>
@@ -3037,7 +3036,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>83</v>
       </c>
@@ -3052,11 +3051,11 @@
       </c>
       <c r="E42" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F42" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3081,7 +3080,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>83</v>
       </c>
@@ -3096,11 +3095,11 @@
       </c>
       <c r="E43" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F43" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3125,7 +3124,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="30" customFormat="1">
+    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>84</v>
       </c>
@@ -3140,11 +3139,11 @@
       </c>
       <c r="E44" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F44" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>85</v>
@@ -3169,7 +3168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>86</v>
       </c>
@@ -3184,11 +3183,11 @@
       </c>
       <c r="E45" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F45" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3213,7 +3212,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>87</v>
       </c>
@@ -3228,11 +3227,11 @@
       </c>
       <c r="E46" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F46" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3257,7 +3256,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>88</v>
       </c>
@@ -3272,11 +3271,11 @@
       </c>
       <c r="E47" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F47" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3301,7 +3300,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>89</v>
       </c>
@@ -3316,11 +3315,11 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F48" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>63</v>
@@ -3347,7 +3346,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>90</v>
       </c>
@@ -3362,11 +3361,11 @@
       </c>
       <c r="E49" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F49" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>63</v>
@@ -3391,7 +3390,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>91</v>
       </c>
@@ -3406,11 +3405,11 @@
       </c>
       <c r="E50" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F50" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3437,7 +3436,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>91</v>
       </c>
@@ -3452,11 +3451,11 @@
       </c>
       <c r="E51" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F51" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3483,7 +3482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>91</v>
       </c>
@@ -3498,11 +3497,11 @@
       </c>
       <c r="E52" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F52" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3529,7 +3528,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="30" customFormat="1">
+    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>93</v>
       </c>
@@ -3544,11 +3543,11 @@
       </c>
       <c r="E53" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>78</v>
@@ -3573,7 +3572,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="30" customFormat="1">
+    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>94</v>
       </c>
@@ -3588,11 +3587,11 @@
       </c>
       <c r="E54" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F54" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>63</v>
@@ -3617,7 +3616,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>95</v>
       </c>
@@ -3632,11 +3631,11 @@
       </c>
       <c r="E55" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F55" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3661,7 +3660,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>96</v>
       </c>
@@ -3676,11 +3675,11 @@
       </c>
       <c r="E56" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F56" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>97</v>
@@ -3705,7 +3704,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>96</v>
       </c>
@@ -3720,11 +3719,11 @@
       </c>
       <c r="E57" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F57" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>63</v>
@@ -3749,7 +3748,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>98</v>
       </c>
@@ -3764,11 +3763,11 @@
       </c>
       <c r="E58" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F58" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -3793,7 +3792,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
@@ -3808,11 +3807,11 @@
       </c>
       <c r="E59" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F59" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -3836,7 +3835,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
@@ -3851,11 +3850,11 @@
       </c>
       <c r="E60" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F60" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -3880,7 +3879,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>102</v>
       </c>
@@ -3895,11 +3894,11 @@
       </c>
       <c r="E61" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F61" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>66</v>
@@ -3924,7 +3923,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>103</v>
       </c>
@@ -3939,11 +3938,11 @@
       </c>
       <c r="E62" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F62" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>104</v>
@@ -3968,7 +3967,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>105</v>
       </c>
@@ -3983,11 +3982,11 @@
       </c>
       <c r="E63" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F63" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G63" s="12" t="s">
         <v>66</v>
@@ -4012,7 +4011,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
         <v>105</v>
       </c>
@@ -4027,11 +4026,11 @@
       </c>
       <c r="E64" s="26">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F64" s="27">
         <f t="shared" ca="1" si="5"/>
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="G64" s="31" t="s">
         <v>16</v>
@@ -4056,7 +4055,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>106</v>
       </c>
@@ -4071,11 +4070,11 @@
       </c>
       <c r="E65" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F65" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>63</v>
@@ -4099,7 +4098,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>107</v>
       </c>
@@ -4114,11 +4113,11 @@
       </c>
       <c r="E66" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F66" s="11">
         <f t="shared" ref="F66:F68" ca="1" si="7">D66-E66</f>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4143,7 +4142,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>107</v>
       </c>
@@ -4158,11 +4157,11 @@
       </c>
       <c r="E67" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F67" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>63</v>
@@ -4187,7 +4186,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="30" customFormat="1">
+    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
         <v>108</v>
       </c>
@@ -4202,11 +4201,11 @@
       </c>
       <c r="E68" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F68" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>32</v>
@@ -4231,7 +4230,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>109</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="23" t="s">
         <v>109</v>
       </c>
@@ -4269,11 +4268,11 @@
       </c>
       <c r="E70" s="25">
         <f t="shared" ref="E70:E103" ca="1" si="8">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F70" s="27">
         <f t="shared" ref="F70:F103" ca="1" si="9">D70-E70</f>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G70" s="31" t="s">
         <v>22</v>
@@ -4296,7 +4295,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
         <v>110</v>
       </c>
@@ -4311,11 +4310,11 @@
       </c>
       <c r="E71" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F71" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4341,7 +4340,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
         <v>113</v>
       </c>
@@ -4356,11 +4355,11 @@
       </c>
       <c r="E72" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F72" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>66</v>
@@ -4383,7 +4382,7 @@
       <c r="N72" s="14"/>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>113</v>
       </c>
@@ -4398,11 +4397,11 @@
       </c>
       <c r="E73" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F73" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4427,7 +4426,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
         <v>114</v>
       </c>
@@ -4442,11 +4441,11 @@
       </c>
       <c r="E74" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F74" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>32</v>
@@ -4473,7 +4472,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>114</v>
       </c>
@@ -4488,11 +4487,11 @@
       </c>
       <c r="E75" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F75" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>85</v>
@@ -4519,7 +4518,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>116</v>
       </c>
@@ -4534,11 +4533,11 @@
       </c>
       <c r="E76" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F76" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>23</v>
@@ -4565,7 +4564,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>118</v>
       </c>
@@ -4580,11 +4579,11 @@
       </c>
       <c r="E77" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F77" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>119</v>
@@ -4610,7 +4609,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
         <v>122</v>
       </c>
@@ -4625,11 +4624,11 @@
       </c>
       <c r="E78" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F78" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>34</v>
@@ -4654,7 +4653,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
         <v>124</v>
       </c>
@@ -4669,11 +4668,11 @@
       </c>
       <c r="E79" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F79" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>66</v>
@@ -4698,7 +4697,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>124</v>
       </c>
@@ -4713,11 +4712,11 @@
       </c>
       <c r="E80" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F80" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>26</v>
@@ -4742,7 +4741,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>124</v>
       </c>
@@ -4757,11 +4756,11 @@
       </c>
       <c r="E81" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F81" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -4786,7 +4785,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
         <v>125</v>
       </c>
@@ -4801,11 +4800,11 @@
       </c>
       <c r="E82" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F82" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>22</v>
@@ -4830,7 +4829,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>125</v>
       </c>
@@ -4845,11 +4844,11 @@
       </c>
       <c r="E83" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F83" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>16</v>
@@ -4874,7 +4873,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
         <v>126</v>
       </c>
@@ -4889,11 +4888,11 @@
       </c>
       <c r="E84" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F84" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>75</v>
@@ -4915,7 +4914,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
         <v>126</v>
       </c>
@@ -4930,11 +4929,11 @@
       </c>
       <c r="E85" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F85" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>34</v>
@@ -4958,7 +4957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
         <v>126</v>
       </c>
@@ -4973,11 +4972,11 @@
       </c>
       <c r="E86" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F86" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>73</v>
@@ -5001,7 +5000,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>130</v>
       </c>
@@ -5016,11 +5015,11 @@
       </c>
       <c r="E87" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F87" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>21</v>
@@ -5043,7 +5042,7 @@
       <c r="N87" s="14"/>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>131</v>
       </c>
@@ -5058,11 +5057,11 @@
       </c>
       <c r="E88" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F88" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>31</v>
@@ -5087,7 +5086,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>132</v>
       </c>
@@ -5102,11 +5101,11 @@
       </c>
       <c r="E89" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F89" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>104</v>
@@ -5128,7 +5127,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
         <v>134</v>
       </c>
@@ -5143,11 +5142,11 @@
       </c>
       <c r="E90" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F90" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>22</v>
@@ -5172,7 +5171,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>134</v>
       </c>
@@ -5187,11 +5186,11 @@
       </c>
       <c r="E91" s="13">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F91" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>16</v>
@@ -5214,7 +5213,7 @@
       <c r="N91" s="14"/>
       <c r="O91" s="19"/>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>135</v>
       </c>
@@ -5229,11 +5228,11 @@
       </c>
       <c r="E92" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F92" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>136</v>
@@ -5258,7 +5257,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="23" t="s">
         <v>137</v>
       </c>
@@ -5273,11 +5272,11 @@
       </c>
       <c r="E93" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F93" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G93" s="31" t="s">
         <v>26</v>
@@ -5304,7 +5303,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="23" t="s">
         <v>137</v>
       </c>
@@ -5319,11 +5318,11 @@
       </c>
       <c r="E94" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F94" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G94" s="31" t="s">
         <v>16</v>
@@ -5350,7 +5349,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>138</v>
       </c>
@@ -5365,11 +5364,11 @@
       </c>
       <c r="E95" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F95" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>31</v>
@@ -5394,7 +5393,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="30" customFormat="1">
+    <row r="96" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23" t="s">
         <v>139</v>
       </c>
@@ -5409,11 +5408,11 @@
       </c>
       <c r="E96" s="25">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F96" s="27">
         <f t="shared" ca="1" si="9"/>
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G96" s="31" t="s">
         <v>32</v>
@@ -5438,7 +5437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="14.25" customHeight="1">
+    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
         <v>140</v>
       </c>
@@ -5453,11 +5452,11 @@
       </c>
       <c r="E97" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F97" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>21</v>
@@ -5482,7 +5481,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
         <v>141</v>
       </c>
@@ -5497,11 +5496,11 @@
       </c>
       <c r="E98" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F98" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>85</v>
@@ -5526,7 +5525,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>142</v>
       </c>
@@ -5541,11 +5540,11 @@
       </c>
       <c r="E99" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F99" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>31</v>
@@ -5570,7 +5569,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="8" t="s">
         <v>143</v>
       </c>
@@ -5585,18 +5584,18 @@
       </c>
       <c r="E100" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F100" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>104</v>
       </c>
       <c r="H100" s="9" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
+        <v>VENDA</v>
       </c>
       <c r="I100" s="9" t="s">
         <v>17</v>
@@ -5614,7 +5613,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>144</v>
       </c>
@@ -5629,11 +5628,11 @@
       </c>
       <c r="E101" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F101" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>104</v>
@@ -5658,7 +5657,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
         <v>146</v>
       </c>
@@ -5673,11 +5672,11 @@
       </c>
       <c r="E102" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F102" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>16</v>
@@ -5702,7 +5701,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15" s="30" customFormat="1">
+    <row r="103" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
         <v>147</v>
       </c>
@@ -5717,11 +5716,11 @@
       </c>
       <c r="E103" s="14">
         <f t="shared" ca="1" si="8"/>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F103" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>148</v>
@@ -5746,7 +5745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
         <v>149</v>
       </c>
@@ -5771,7 +5770,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="8" t="s">
         <v>150</v>
       </c>
@@ -5786,11 +5785,11 @@
       </c>
       <c r="E105" s="14">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F105" s="11">
         <f ca="1">D105-E105</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -5813,7 +5812,7 @@
       <c r="N105" s="14"/>
       <c r="O105" s="19"/>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
         <v>150</v>
       </c>
@@ -5828,11 +5827,11 @@
       </c>
       <c r="E106" s="14">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F106" s="11">
         <f ca="1">D106-E106</f>
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -5857,7 +5856,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="8" t="s">
         <v>151</v>
       </c>
@@ -5872,11 +5871,11 @@
       </c>
       <c r="E107" s="14">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F107" s="11">
         <f ca="1">D107-E107</f>
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -5901,7 +5900,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>152</v>
       </c>
@@ -5916,11 +5915,11 @@
       </c>
       <c r="E108" s="14">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F108" s="11">
         <f ca="1">D108-E108</f>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>136</v>
@@ -5945,7 +5944,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
         <v>152</v>
       </c>
@@ -5960,11 +5959,11 @@
       </c>
       <c r="E109" s="14">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F109" s="11">
         <f ca="1">D109-E109</f>
-        <v>-2029</v>
+        <v>-2030</v>
       </c>
       <c r="G109" s="12" t="s">
         <v>31</v>
@@ -5991,11 +5990,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N109" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="AVULSO"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N109">
       <sortCondition ref="A1:A109"/>
     </sortState>
@@ -6007,25 +6001,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6069,7 +6063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>158</v>
       </c>
@@ -6107,7 +6101,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>163</v>
       </c>
@@ -6145,7 +6139,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>165</v>
       </c>
@@ -6183,7 +6177,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>167</v>
       </c>
@@ -6221,7 +6215,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>168</v>
       </c>
@@ -6259,7 +6253,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
@@ -6297,7 +6291,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>171</v>
       </c>
@@ -6335,7 +6329,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>172</v>
       </c>
@@ -6373,7 +6367,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>173</v>
       </c>
@@ -6411,7 +6405,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>174</v>
       </c>
@@ -6449,7 +6443,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6487,7 +6481,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6525,7 +6519,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>175</v>
       </c>
@@ -6563,7 +6557,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>176</v>
       </c>
@@ -6601,7 +6595,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>178</v>
       </c>
@@ -6639,7 +6633,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>179</v>
       </c>
@@ -6677,7 +6671,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>181</v>
       </c>
@@ -6715,7 +6709,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>182</v>
       </c>
@@ -6753,7 +6747,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>183</v>
       </c>
@@ -6791,7 +6785,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>184</v>
       </c>
@@ -6829,7 +6823,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -6867,7 +6861,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>186</v>
       </c>
@@ -6905,7 +6899,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>188</v>
       </c>
@@ -6943,7 +6937,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>189</v>
       </c>
@@ -6981,7 +6975,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>190</v>
       </c>
@@ -7019,7 +7013,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>191</v>
       </c>
@@ -7057,7 +7051,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>193</v>
       </c>
@@ -7095,7 +7089,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>194</v>
       </c>
@@ -7133,7 +7127,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
@@ -7171,7 +7165,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>195</v>
       </c>
@@ -7209,7 +7203,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>196</v>
       </c>
@@ -7247,7 +7241,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>197</v>
       </c>
@@ -7285,7 +7279,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>199</v>
       </c>
@@ -7323,7 +7317,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>200</v>
       </c>
@@ -7361,7 +7355,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>201</v>
       </c>
@@ -7399,7 +7393,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>202</v>
       </c>
@@ -7437,7 +7431,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>202</v>
       </c>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="465" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B765FFF9-DED6-43AB-955C-1F8915F05EB3}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDCFAA8D-43D9-44C4-93F2-FFC716E9E06E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="SÉRIE2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$N$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$N$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SÉRIE2!$A$1:$N$38</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="206">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -650,6 +650,15 @@
   </si>
   <si>
     <t>ULTRAPRESS EDITORA E GRAFICA</t>
+  </si>
+  <si>
+    <t>03 MESES DE MÃO DE OBRA (ATÉ 31/10/26)</t>
+  </si>
+  <si>
+    <t>03 MESES DE MÃO DE OBRA</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ENTREGA</t>
   </si>
 </sst>
 </file>
@@ -717,7 +726,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -755,22 +764,153 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC8C8C8"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFC8C8C8"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFC8C8C8"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -793,90 +933,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1212,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -1221,7 +1403,7 @@
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
@@ -1229,4769 +1411,4798 @@
     <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.26953125" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.26953125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="50" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="43">
         <v>46046</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="43">
         <v>46234</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="43">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
         <v>46226</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="44">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
         <v>8</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="46" t="str">
         <f t="shared" ref="H2:H11" ca="1" si="2">IF(F2&lt;=0,"VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="I2" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="43">
         <v>45315</v>
       </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="19">
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="48">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>45717</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="11">
         <v>51501</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="6" t="str">
+      <c r="H3" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="I3" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="11">
         <v>40368</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="19">
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>45292</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <v>51501</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="11">
         <v>43627</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="19">
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <v>45627</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <v>51501</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="6" t="str">
+      <c r="H5" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="11" t="s">
+      <c r="I5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="11">
         <v>45385</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="19">
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>45962</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <v>46265</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="I6" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="11">
         <v>42118</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="19">
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>45992</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>46265</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>39</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="6" t="str">
+      <c r="H7" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="I7" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="11">
         <v>42755</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="19">
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>45999</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>46061</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-165</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="11">
         <v>45965</v>
       </c>
-      <c r="L8" s="21"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="19">
+      <c r="L8" s="19"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>45999</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>45824</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-402</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="6" t="str">
+      <c r="H9" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="I9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="19">
+      <c r="K9" s="11"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>45670</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>44196</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="6" t="str">
+      <c r="H10" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="11" t="s">
+      <c r="I10" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="11">
         <v>45670</v>
       </c>
-      <c r="L10" s="21"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="29"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="12">
         <v>44909</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <v>44196</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="6" t="str">
+      <c r="H11" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="11" t="s">
+      <c r="I11" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="12">
         <v>43581</v>
       </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="19">
+      <c r="L11" s="19"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="12">
         <v>45992</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <v>46356</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>130</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="11" t="s">
+      <c r="I12" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="12">
         <v>43224</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="19">
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <v>45566</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <v>46326</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>100</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="11" t="s">
+      <c r="I13" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <v>45149</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="19">
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="12">
         <v>45890</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="12">
         <v>46619</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>393</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="12">
         <v>45890</v>
       </c>
-      <c r="L14" s="21"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="19">
+      <c r="L14" s="19"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="12">
         <v>45962</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <v>51501</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="12">
         <v>41969</v>
       </c>
-      <c r="L15" s="21" t="s">
+      <c r="L15" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="19">
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="14">
-        <v>46082</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D16" s="12">
         <v>46446</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>220</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="12">
         <v>42353</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="19">
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="14">
-        <v>46082</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="C17" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D17" s="12">
         <v>46446</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>220</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="12">
         <v>45524</v>
       </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="19">
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>45950</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>46863</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>637</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="11" t="s">
+      <c r="I18" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="12">
         <v>45950</v>
       </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="19">
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>42564</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <v>51501</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="11" t="s">
+      <c r="I19" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="12">
         <v>42198</v>
       </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="19">
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>46028</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <v>51501</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="11" t="s">
+      <c r="I20" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="12">
         <v>45602</v>
       </c>
-      <c r="L20" s="22"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="19">
+      <c r="L20" s="21"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <v>44911</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="11">
         <v>44196</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="9" t="str">
+      <c r="H21" s="18" t="str">
         <f t="shared" ref="H21:H27" ca="1" si="3">IF(F21&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="11" t="s">
+      <c r="I21" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="12">
         <v>40801</v>
       </c>
-      <c r="L21" s="22"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="19">
+      <c r="L21" s="21"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="12">
         <v>45352</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="11">
         <v>44196</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="9" t="str">
+      <c r="H22" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="11" t="s">
+      <c r="I22" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="12">
         <v>44089</v>
       </c>
-      <c r="L22" s="22"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="19">
+      <c r="L22" s="21"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="12">
         <v>45444</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="12">
         <v>46203</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-23</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="9" t="str">
+      <c r="H23" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="11" t="s">
+      <c r="I23" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="12">
         <v>45261</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="19">
+      <c r="L23" s="21"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="13">
         <v>45962</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <v>46203</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>-23</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="9" t="str">
+      <c r="H24" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="13">
         <v>41290</v>
       </c>
-      <c r="L24" s="21" t="s">
+      <c r="L24" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="M24" s="34"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="19">
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="13">
         <v>45962</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <v>46203</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>-23</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="9" t="str">
+      <c r="H25" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="J25" s="27" t="s">
+      <c r="J25" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="13">
         <v>42989</v>
       </c>
-      <c r="L25" s="21" t="s">
+      <c r="L25" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="34"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="19">
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="12">
         <v>45383</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="11">
         <v>44196</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="9" t="str">
+      <c r="H26" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I26" s="28" t="s">
+      <c r="I26" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="12">
         <v>43186</v>
       </c>
-      <c r="L26" s="21" t="s">
+      <c r="L26" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="19">
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="12">
         <v>45992</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <v>46477</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>251</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="9" t="str">
+      <c r="H27" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="11" t="s">
+      <c r="I27" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="12">
         <v>43923</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="12">
         <v>45689</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="12">
         <v>51501</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>5275</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="12">
         <v>42347</v>
       </c>
-      <c r="L28" s="22"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="L28" s="21"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="12">
         <v>43891</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="11">
         <v>44196</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="9" t="str">
+      <c r="H29" s="18" t="str">
         <f ca="1">IF(F29&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="11" t="s">
+      <c r="I29" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="12">
         <v>43283</v>
       </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="29">
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="32">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="12">
         <v>45925</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="11">
         <v>44196</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="9" t="str">
+      <c r="H30" s="18" t="str">
         <f ca="1">IF(F30&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="11" t="s">
+      <c r="I30" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="12">
         <v>45925</v>
       </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="19">
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="13">
         <v>45928</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="13">
         <v>46473</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>247</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="9" t="str">
+      <c r="H31" s="18" t="str">
         <f ca="1">IF(F31&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="27" t="s">
+      <c r="I31" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="25">
+      <c r="K31" s="13">
         <v>45744</v>
       </c>
-      <c r="L31" s="25"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="19">
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="12">
         <v>45139</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="11">
         <v>44196</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="9" t="str">
+      <c r="H32" s="18" t="str">
         <f ca="1">IF(F32&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="11" t="s">
+      <c r="I32" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K32" s="12">
         <v>40892</v>
       </c>
-      <c r="L32" s="14"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="19">
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="11">
         <v>45017</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="11">
         <v>44196</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>46226</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="15">
         <f t="shared" ca="1" si="1"/>
         <v>-2030</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="6" t="str">
+      <c r="H33" s="17" t="str">
         <f ca="1">IF(F33&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="11" t="s">
+      <c r="I33" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="11">
         <v>44682</v>
       </c>
-      <c r="L33" s="21"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="19">
+      <c r="L33" s="19"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="12">
         <v>44165</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="11">
         <v>44196</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
         <v>46226</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="15">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
         <v>-2030</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H34" s="9" t="str">
+      <c r="H34" s="18" t="str">
         <f ca="1">IF(F34&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="11" t="s">
+      <c r="I34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="14">
+      <c r="K34" s="12">
         <v>40736</v>
       </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="19">
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="12">
         <v>45896</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <v>46625</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>399</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="9" t="str">
+      <c r="H35" s="18" t="str">
         <f ca="1">IF(F35&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="11" t="s">
+      <c r="I35" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="14">
+      <c r="K35" s="12">
         <v>45714</v>
       </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="12">
         <v>45870</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="12">
         <v>46477</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>251</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="12" t="s">
+      <c r="I36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="12">
         <v>44896</v>
       </c>
-      <c r="L36" s="14"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="29">
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="32">
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="12">
         <v>46090</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="12">
         <v>46455</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>229</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="12" t="s">
+      <c r="I37" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="12">
         <v>46455</v>
       </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="19">
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="12">
         <v>45661</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="12">
         <v>46206</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-20</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H38" s="9" t="str">
+      <c r="H38" s="18" t="str">
         <f ca="1">IF(F38&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I38" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="12" t="s">
+      <c r="I38" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="K38" s="14">
+      <c r="K38" s="12">
         <v>45477</v>
       </c>
-      <c r="L38" s="22"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="19">
+      <c r="L38" s="21"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="12">
         <v>44909</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="11">
         <v>44196</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="9" t="str">
+      <c r="H39" s="18" t="str">
         <f ca="1">IF(F39&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I39" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="11" t="s">
+      <c r="I39" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="12">
         <v>40711</v>
       </c>
-      <c r="L39" s="14"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="19">
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="12">
         <v>44909</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="11">
         <v>44196</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="9" t="str">
+      <c r="H40" s="18" t="str">
         <f ca="1">IF(F40&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I40" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="11" t="s">
+      <c r="I40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="12">
         <v>41809</v>
       </c>
-      <c r="L40" s="14"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="19">
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="13">
         <v>46114</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="13">
         <v>47579</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="23">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="24">
         <f t="shared" ca="1" si="5"/>
         <v>1353</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H41" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="J41" s="27" t="s">
+      <c r="J41" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="13">
         <v>45959</v>
       </c>
-      <c r="L41" s="25"/>
-      <c r="M41" s="34"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="19">
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="12">
         <v>44909</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="11">
         <v>44196</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="6" t="str">
+      <c r="H42" s="17" t="str">
         <f ca="1">IF(F42&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="11" t="s">
+      <c r="I42" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="12">
         <v>41166</v>
       </c>
-      <c r="L42" s="21"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="19">
+      <c r="L42" s="19"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="12">
         <v>45625</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="11">
         <v>44196</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="G43" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="6" t="str">
+      <c r="H43" s="17" t="str">
         <f ca="1">IF(F43&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="11" t="s">
+      <c r="I43" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="12">
         <v>45625</v>
       </c>
-      <c r="L43" s="21"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="L43" s="19"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="12">
         <v>45783</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="12">
         <v>46331</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>105</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="9" t="str">
+      <c r="H44" s="18" t="str">
         <f t="shared" ref="H44:H58" ca="1" si="6">IF(F44&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="11" t="s">
+      <c r="I44" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="12">
         <v>45602</v>
       </c>
-      <c r="L44" s="14"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="29">
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="32">
         <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="12">
         <v>45583</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="11">
         <v>44196</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H45" s="9" t="str">
+      <c r="H45" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="11" t="s">
+      <c r="I45" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="12">
         <v>45583</v>
       </c>
-      <c r="L45" s="14"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="19">
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="12">
         <v>45541</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="12">
         <v>46573</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>347</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="9" t="str">
+      <c r="H46" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="11" t="s">
+      <c r="I46" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K46" s="14">
+      <c r="K46" s="12">
         <v>44810</v>
       </c>
-      <c r="L46" s="14"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="19">
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="12">
         <v>45505</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="11">
         <v>44196</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="9" t="str">
+      <c r="H47" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="11" t="s">
+      <c r="I47" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K47" s="14">
+      <c r="K47" s="12">
         <v>44655</v>
       </c>
-      <c r="L47" s="14"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="19">
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="12">
         <v>45992</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="12">
         <v>46265</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>39</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H48" s="9" t="str">
+      <c r="H48" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I48" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="11" t="s">
+      <c r="I48" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K48" s="12">
         <v>42781</v>
       </c>
-      <c r="L48" s="21" t="s">
+      <c r="L48" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M48" s="15"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="19">
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="A49" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="12">
         <v>44946</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="11">
         <v>44196</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H49" s="9" t="str">
+      <c r="H49" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="11" t="s">
+      <c r="I49" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="14">
+      <c r="K49" s="12">
         <v>44946</v>
       </c>
-      <c r="L49" s="14"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="19">
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="12">
         <v>45870</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="12">
         <v>46234</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>8</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="9" t="str">
+      <c r="H50" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="14">
+      <c r="K50" s="12">
         <v>42744</v>
       </c>
-      <c r="L50" s="21" t="s">
+      <c r="L50" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M50" s="15"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="19">
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="12">
         <v>45870</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="12">
         <v>46234</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>8</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H51" s="9" t="str">
+      <c r="H51" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K51" s="14">
+      <c r="K51" s="12">
         <v>43733</v>
       </c>
-      <c r="L51" s="21" t="s">
+      <c r="L51" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M51" s="15"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="19">
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="12">
         <v>46033</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="12">
         <v>46213</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-13</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="9" t="str">
+      <c r="H52" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K52" s="14">
+      <c r="K52" s="12">
         <v>45849</v>
       </c>
-      <c r="L52" s="21" t="s">
+      <c r="L52" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M52" s="15"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="12">
         <v>44902</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="11">
         <v>44196</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H53" s="9" t="str">
+      <c r="H53" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I53" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="11" t="s">
+      <c r="I53" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="14">
+      <c r="K53" s="12">
         <v>41320</v>
       </c>
-      <c r="L53" s="14"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="14">
-        <v>45992</v>
-      </c>
-      <c r="D54" s="14">
-        <v>46387</v>
-      </c>
-      <c r="E54" s="13">
+      <c r="C54" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D54" s="12">
+        <v>47330</v>
+      </c>
+      <c r="E54" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F54" s="11">
-        <f t="shared" ca="1" si="5"/>
-        <v>161</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H54" s="9" t="str">
-        <f t="shared" ca="1" si="6"/>
+      <c r="F54" s="15">
+        <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
+        <v>1104</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="H54" s="18" t="str">
+        <f t="shared" ref="H54" ca="1" si="8">IF(F54&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I54" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="11" t="s">
+      <c r="I54" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="J54" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="14">
-        <v>42447</v>
-      </c>
-      <c r="L54" s="14"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="29">
+      <c r="K54" s="12">
+        <v>46234</v>
+      </c>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="32">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="12">
         <v>44835</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55" s="11">
         <v>44196</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="9" t="str">
+      <c r="H55" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I55" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="11" t="s">
+      <c r="I55" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K55" s="14">
+      <c r="K55" s="12">
         <v>43693</v>
       </c>
-      <c r="L55" s="14"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="19">
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="14">
+      <c r="C56" s="12">
         <v>44841</v>
       </c>
-      <c r="D56" s="13">
+      <c r="D56" s="11">
         <v>44196</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="H56" s="9" t="str">
+      <c r="H56" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I56" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="11" t="s">
+      <c r="I56" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K56" s="14">
+      <c r="K56" s="12">
         <v>41887</v>
       </c>
-      <c r="L56" s="14"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="19">
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="14">
+      <c r="C57" s="12">
         <v>44841</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="11">
         <v>44196</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H57" s="9" t="str">
+      <c r="H57" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I57" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="11" t="s">
+      <c r="I57" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K57" s="14">
+      <c r="K57" s="12">
         <v>42216</v>
       </c>
-      <c r="L57" s="14"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="19">
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="12">
         <v>45566</v>
       </c>
-      <c r="D58" s="13">
+      <c r="D58" s="11">
         <v>44196</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="9" t="str">
+      <c r="H58" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="11" t="s">
+      <c r="I58" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K58" s="12">
         <v>45566</v>
       </c>
-      <c r="L58" s="14"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="19">
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+      <c r="O58" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="12">
         <v>45992</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D59" s="12">
         <v>46295</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>69</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="9" t="s">
+      <c r="H59" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I59" s="9" t="s">
+      <c r="I59" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K59" s="14">
+      <c r="K59" s="12">
         <v>43262</v>
       </c>
-      <c r="L59" s="14"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="19">
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+      <c r="O59" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="14">
+      <c r="C60" s="12">
         <v>44621</v>
       </c>
-      <c r="D60" s="13">
+      <c r="D60" s="11">
         <v>44196</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="9" t="str">
+      <c r="H60" s="18" t="str">
         <f ca="1">IF(F60&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I60" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="11" t="s">
+      <c r="I60" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K60" s="14">
+      <c r="K60" s="12">
         <v>43693</v>
       </c>
-      <c r="L60" s="22"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="19">
+      <c r="L60" s="21"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+      <c r="O60" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="14">
+      <c r="C61" s="12">
         <v>45962</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="12">
         <v>46022</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-204</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H61" s="9" t="str">
+      <c r="H61" s="18" t="str">
         <f ca="1">IF(F61&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="11" t="s">
+      <c r="I61" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K61" s="14">
+      <c r="K61" s="12">
         <v>40924</v>
       </c>
-      <c r="L61" s="14"/>
-      <c r="M61" s="15"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="19">
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="14">
+      <c r="C62" s="12">
         <v>45528</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="11">
         <v>44196</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H62" s="9" t="str">
+      <c r="H62" s="18" t="str">
         <f ca="1">IF(F62&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I62" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="11" t="s">
+      <c r="I62" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K62" s="14">
+      <c r="K62" s="12">
         <v>44981</v>
       </c>
-      <c r="L62" s="14"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="19">
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="14">
+      <c r="C63" s="12">
         <v>45962</v>
       </c>
-      <c r="D63" s="13">
+      <c r="D63" s="11">
         <v>44196</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-2030</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H63" s="9" t="str">
+      <c r="H63" s="18" t="str">
         <f ca="1">IF(F63&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I63" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="11" t="s">
+      <c r="I63" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K63" s="14">
+      <c r="K63" s="12">
         <v>41421</v>
       </c>
-      <c r="L63" s="14"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="19">
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="13">
         <v>45962</v>
       </c>
-      <c r="D64" s="25">
-        <v>46082</v>
-      </c>
-      <c r="E64" s="26">
+      <c r="D64" s="13">
+        <v>46082</v>
+      </c>
+      <c r="E64" s="23">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F64" s="27">
+      <c r="F64" s="24">
         <f t="shared" ca="1" si="5"/>
         <v>-144</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H64" s="9" t="str">
+      <c r="H64" s="18" t="str">
         <f ca="1">IF(F64&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I64" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="27" t="s">
+      <c r="I64" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K64" s="25">
+      <c r="K64" s="13">
         <v>45492</v>
       </c>
-      <c r="L64" s="25"/>
-      <c r="M64" s="34"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="19">
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="14">
+      <c r="C65" s="12">
         <v>45992</v>
       </c>
-      <c r="D65" s="14">
+      <c r="D65" s="12">
         <v>46203</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="15">
         <f t="shared" ca="1" si="5"/>
         <v>-23</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="G65" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I65" s="9" t="s">
+      <c r="I65" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K65" s="14">
+      <c r="K65" s="12">
         <v>42082</v>
       </c>
-      <c r="L65" s="14"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="19">
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
+      <c r="O65" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="14">
+      <c r="C66" s="12">
         <v>44777</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66" s="11">
         <v>44196</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F66" s="11">
-        <f t="shared" ref="F66:F68" ca="1" si="7">D66-E66</f>
+      <c r="F66" s="15">
+        <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
         <v>-2030</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="G66" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H66" s="9" t="str">
+      <c r="H66" s="18" t="str">
         <f ca="1">IF(F66&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="11" t="s">
+      <c r="I66" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K66" s="14">
+      <c r="K66" s="12">
         <v>41066</v>
       </c>
-      <c r="L66" s="14"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="19">
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C67" s="14">
+      <c r="C67" s="12">
         <v>45929</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67" s="11">
         <v>44196</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F67" s="11">
-        <f t="shared" ca="1" si="7"/>
+      <c r="F67" s="15">
+        <f t="shared" ca="1" si="9"/>
         <v>-2030</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H67" s="9" t="str">
+      <c r="H67" s="18" t="str">
         <f ca="1">IF(F67&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="11" t="s">
+      <c r="I67" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K67" s="14">
+      <c r="K67" s="12">
         <v>45198</v>
       </c>
-      <c r="L67" s="14"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="14">
+      <c r="C68" s="12">
         <v>45719</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68" s="11">
         <v>44196</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>46226</v>
       </c>
-      <c r="F68" s="11">
-        <f t="shared" ca="1" si="7"/>
+      <c r="F68" s="15">
+        <f t="shared" ca="1" si="9"/>
         <v>-2030</v>
       </c>
-      <c r="G68" s="12" t="s">
+      <c r="G68" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="9" t="str">
+      <c r="H68" s="18" t="str">
         <f ca="1">IF(F68&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I68" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="11" t="s">
+      <c r="I68" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K68" s="14">
+      <c r="K68" s="12">
         <v>43661</v>
       </c>
-      <c r="L68" s="14"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="29">
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="32">
         <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="11"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="19">
+      <c r="B69" s="14"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="15"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="13">
         <v>46054</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="23">
         <v>44196</v>
       </c>
-      <c r="E70" s="25">
-        <f t="shared" ref="E70:E103" ca="1" si="8">TODAY()</f>
-        <v>46226</v>
-      </c>
-      <c r="F70" s="27">
-        <f t="shared" ref="F70:F103" ca="1" si="9">D70-E70</f>
+      <c r="E70" s="13">
+        <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
+        <v>46226</v>
+      </c>
+      <c r="F70" s="24">
+        <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
         <v>-2030</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="28" t="str">
+      <c r="H70" s="26" t="str">
         <f ca="1">IF(F70&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I70" s="28"/>
-      <c r="J70" s="27" t="s">
+      <c r="I70" s="26"/>
+      <c r="J70" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K70" s="25">
+      <c r="K70" s="13">
         <v>44036</v>
       </c>
-      <c r="L70" s="25"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="25"/>
-      <c r="O70" s="19">
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="14">
+      <c r="C71" s="12">
         <v>45992</v>
       </c>
-      <c r="D71" s="14">
+      <c r="D71" s="12">
         <v>46326</v>
       </c>
-      <c r="E71" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F71" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E71" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F71" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>100</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H71" s="9" t="s">
+      <c r="H71" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I71" s="9" t="s">
+      <c r="I71" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K71" s="14">
+      <c r="K71" s="12">
         <v>44841</v>
       </c>
-      <c r="L71" s="14" t="s">
+      <c r="L71" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="M71" s="15"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="19">
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="29">
         <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="14">
+      <c r="C72" s="12">
         <v>45962</v>
       </c>
-      <c r="D72" s="14">
+      <c r="D72" s="12">
         <v>46265</v>
       </c>
-      <c r="E72" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F72" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E72" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F72" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>39</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H72" s="9" t="str">
+      <c r="H72" s="18" t="str">
         <f ca="1">IF(F72&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I72" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="11" t="s">
+      <c r="I72" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K72" s="14">
+      <c r="K72" s="12">
         <v>42040</v>
       </c>
-      <c r="L72" s="14"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="14"/>
-      <c r="O72" s="19"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="29"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C73" s="14">
+      <c r="C73" s="12">
         <v>45962</v>
       </c>
-      <c r="D73" s="14">
+      <c r="D73" s="12">
         <v>46265</v>
       </c>
-      <c r="E73" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F73" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E73" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F73" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>39</v>
       </c>
-      <c r="G73" s="12" t="s">
+      <c r="G73" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="9" t="str">
+      <c r="H73" s="18" t="str">
         <f ca="1">IF(F73&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="11" t="s">
+      <c r="I73" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K73" s="14">
+      <c r="K73" s="12">
         <v>43733</v>
       </c>
-      <c r="L73" s="14"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="14"/>
-      <c r="O73" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="L73" s="12"/>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="J74" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="32"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B75" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="14">
+      <c r="C75" s="12">
         <v>46204</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D75" s="11">
         <v>46568</v>
       </c>
-      <c r="E74" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F74" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E75" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F75" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>342</v>
       </c>
-      <c r="G74" s="12" t="s">
+      <c r="G75" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="9" t="str">
-        <f ca="1">IF(F74&lt;=0, "VENDA","CAREPACK")</f>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K74" s="14">
-        <v>45999</v>
-      </c>
-      <c r="L74" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="M74" s="15"/>
-      <c r="N74" s="14"/>
-      <c r="O74" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" s="14">
-        <v>45555</v>
-      </c>
-      <c r="D75" s="14">
-        <v>46465</v>
-      </c>
-      <c r="E75" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F75" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>239</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H75" s="9" t="str">
+      <c r="H75" s="18" t="str">
         <f ca="1">IF(F75&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I75" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="11" t="s">
+      <c r="I75" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75" s="12">
+        <v>45999</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A76" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="12">
+        <v>45555</v>
+      </c>
+      <c r="D76" s="12">
+        <v>46465</v>
+      </c>
+      <c r="E76" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F76" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>239</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H76" s="18" t="str">
+        <f ca="1">IF(F76&lt;=0, "VENDA","CAREPACK")</f>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K75" s="14">
+      <c r="K76" s="12">
         <v>45371</v>
       </c>
-      <c r="L75" s="14" t="s">
+      <c r="L76" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="M75" s="15"/>
-      <c r="N75" s="14"/>
-      <c r="O75" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A77" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C76" s="14">
+      <c r="C77" s="12">
         <v>45639</v>
       </c>
-      <c r="D76" s="13">
+      <c r="D77" s="11">
         <v>44196</v>
       </c>
-      <c r="E76" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F76" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E77" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F77" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G77" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H76" s="9" t="str">
-        <f ca="1">IF(F76&lt;=0, "VENDA","CAREPACK")</f>
+      <c r="H77" s="18" t="str">
+        <f ca="1">IF(F77&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I76" s="9" t="s">
+      <c r="I77" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J77" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K76" s="14">
+      <c r="K77" s="12">
         <v>45273</v>
       </c>
-      <c r="L76" s="14" t="s">
+      <c r="L77" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="M76" s="15"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="M77" s="12"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A78" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B78" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C77" s="14">
+      <c r="C78" s="12">
         <v>45989</v>
       </c>
-      <c r="D77" s="14">
+      <c r="D78" s="12">
         <v>47449</v>
       </c>
-      <c r="E77" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F77" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E78" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F78" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>1223</v>
       </c>
-      <c r="G77" s="12" t="s">
+      <c r="G78" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="H78" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I77" s="9" t="s">
+      <c r="I78" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J78" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K77" s="14">
+      <c r="K78" s="12">
         <v>45989</v>
       </c>
-      <c r="L77" s="14" t="s">
+      <c r="L78" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="M77" s="15"/>
-      <c r="N77" s="14"/>
-      <c r="O77" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B79" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="14">
+      <c r="C79" s="12">
         <v>45039</v>
       </c>
-      <c r="D78" s="13">
+      <c r="D79" s="11">
         <v>44196</v>
       </c>
-      <c r="E78" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F78" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E79" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F79" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G78" s="12" t="s">
+      <c r="G79" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H78" s="9" t="str">
-        <f t="shared" ref="H78:H83" ca="1" si="10">IF(F78&lt;=0, "VENDA","CAREPACK")</f>
+      <c r="H79" s="18" t="str">
+        <f t="shared" ref="H79:H84" ca="1" si="12">IF(F79&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I78" s="9" t="s">
+      <c r="I79" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J79" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K78" s="14">
+      <c r="K79" s="12">
         <v>43984</v>
       </c>
-      <c r="L78" s="14"/>
-      <c r="M78" s="15"/>
-      <c r="N78" s="14"/>
-      <c r="O78" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
+      <c r="N79" s="12"/>
+      <c r="O79" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="14">
+      <c r="C80" s="12">
         <v>43749</v>
       </c>
-      <c r="D79" s="13">
+      <c r="D80" s="11">
         <v>44196</v>
       </c>
-      <c r="E79" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F79" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E80" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F80" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G80" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H79" s="9" t="str">
+      <c r="H80" s="18" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I80" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80" s="12">
+        <v>41866</v>
+      </c>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="12">
+        <v>43749</v>
+      </c>
+      <c r="D81" s="11">
+        <v>44196</v>
+      </c>
+      <c r="E81" s="11">
         <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F81" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>-2030</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="18" t="str">
+        <f t="shared" ca="1" si="12"/>
         <v>VENDA</v>
       </c>
-      <c r="I79" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="11" t="s">
+      <c r="I81" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K79" s="14">
-        <v>41866</v>
-      </c>
-      <c r="L79" s="14"/>
-      <c r="M79" s="15"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="K81" s="12">
+        <v>42670</v>
+      </c>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A82" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B82" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="14">
-        <v>43749</v>
-      </c>
-      <c r="D80" s="13">
+      <c r="C82" s="12">
+        <v>43641</v>
+      </c>
+      <c r="D82" s="11">
         <v>44196</v>
       </c>
-      <c r="E80" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F80" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E82" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F82" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="G82" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H80" s="9" t="str">
+      <c r="H82" s="18" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K82" s="12">
+        <v>43276</v>
+      </c>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A83" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="12">
+        <v>45870</v>
+      </c>
+      <c r="D83" s="12">
+        <v>46418</v>
+      </c>
+      <c r="E83" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="11" t="s">
+        <v>46226</v>
+      </c>
+      <c r="F83" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>192</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="18" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K80" s="14">
-        <v>42670</v>
-      </c>
-      <c r="L80" s="14"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="14"/>
-      <c r="O80" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A81" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B81" s="2" t="s">
+      <c r="K83" s="12">
+        <v>43672</v>
+      </c>
+      <c r="L83" s="12"/>
+      <c r="M83" s="12"/>
+      <c r="N83" s="12"/>
+      <c r="O83" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="12">
+        <v>46054</v>
+      </c>
+      <c r="D84" s="12">
+        <v>46418</v>
+      </c>
+      <c r="E84" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F84" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>192</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="18" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I84" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84" s="12">
+        <v>45870</v>
+      </c>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
+      <c r="O84" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="12">
+        <v>46203</v>
+      </c>
+      <c r="D85" s="12">
+        <v>46751</v>
+      </c>
+      <c r="E85" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F85" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>525</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="J85" s="15"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D86" s="12">
+        <v>46446</v>
+      </c>
+      <c r="E86" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F86" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>220</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J86" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86" s="12">
+        <v>43476</v>
+      </c>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="12">
+        <v>46082</v>
+      </c>
+      <c r="D87" s="12">
+        <v>46446</v>
+      </c>
+      <c r="E87" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F87" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>220</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K87" s="12">
+        <v>45691</v>
+      </c>
+      <c r="L87" s="12"/>
+      <c r="M87" s="12"/>
+      <c r="N87" s="12"/>
+      <c r="O87" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A88" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B88" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="14">
-        <v>43641</v>
-      </c>
-      <c r="D81" s="13">
+      <c r="C88" s="12">
+        <v>45173</v>
+      </c>
+      <c r="D88" s="11">
         <v>44196</v>
       </c>
-      <c r="E81" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F81" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E88" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F88" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G81" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K81" s="14">
-        <v>43276</v>
-      </c>
-      <c r="L81" s="14"/>
-      <c r="M81" s="15"/>
-      <c r="N81" s="14"/>
-      <c r="O81" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A82" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C82" s="14">
-        <v>45870</v>
-      </c>
-      <c r="D82" s="14">
-        <v>46418</v>
-      </c>
-      <c r="E82" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F82" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>192</v>
-      </c>
-      <c r="G82" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H82" s="9" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K82" s="14">
-        <v>43672</v>
-      </c>
-      <c r="L82" s="14"/>
-      <c r="M82" s="15"/>
-      <c r="N82" s="14"/>
-      <c r="O82" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A83" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="14">
-        <v>46054</v>
-      </c>
-      <c r="D83" s="14">
-        <v>46418</v>
-      </c>
-      <c r="E83" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F83" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>192</v>
-      </c>
-      <c r="G83" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H83" s="9" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K83" s="14">
-        <v>45870</v>
-      </c>
-      <c r="L83" s="14"/>
-      <c r="M83" s="15"/>
-      <c r="N83" s="14"/>
-      <c r="O83" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A84" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" s="14">
-        <v>46203</v>
-      </c>
-      <c r="D84" s="14">
-        <v>46751</v>
-      </c>
-      <c r="E84" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F84" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>525</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="J84" s="11"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="M84" s="15"/>
-      <c r="N84" s="14"/>
-      <c r="O84" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A85" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C85" s="14">
-        <v>46082</v>
-      </c>
-      <c r="D85" s="14">
-        <v>46446</v>
-      </c>
-      <c r="E85" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F85" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>220</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K85" s="14">
-        <v>43476</v>
-      </c>
-      <c r="L85" s="14"/>
-      <c r="M85" s="15"/>
-      <c r="N85" s="14"/>
-      <c r="O85" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A86" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="14">
-        <v>46082</v>
-      </c>
-      <c r="D86" s="14">
-        <v>46446</v>
-      </c>
-      <c r="E86" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F86" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>220</v>
-      </c>
-      <c r="G86" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J86" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K86" s="14">
-        <v>45691</v>
-      </c>
-      <c r="L86" s="14"/>
-      <c r="M86" s="15"/>
-      <c r="N86" s="14"/>
-      <c r="O86" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A87" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="15">
-        <v>45173</v>
-      </c>
-      <c r="D87" s="33">
-        <v>44196</v>
-      </c>
-      <c r="E87" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F87" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
-      </c>
-      <c r="G87" s="12" t="s">
+      <c r="G88" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H87" s="9" t="str">
-        <f ca="1">IF(F87&lt;=0, "VENDA","CAREPACK")</f>
-        <v>VENDA</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K87" s="14">
-        <v>42692</v>
-      </c>
-      <c r="L87" s="14"/>
-      <c r="M87" s="15"/>
-      <c r="N87" s="14"/>
-      <c r="O87" s="19"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A88" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B88" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="15">
-        <v>44798</v>
-      </c>
-      <c r="D88" s="33">
-        <v>44196</v>
-      </c>
-      <c r="E88" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F88" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
-      </c>
-      <c r="G88" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H88" s="9" t="str">
+      <c r="H88" s="18" t="str">
         <f ca="1">IF(F88&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I88" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="11" t="s">
+      <c r="I88" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K88" s="14">
+      <c r="K88" s="12">
+        <v>42692</v>
+      </c>
+      <c r="L88" s="12"/>
+      <c r="M88" s="12"/>
+      <c r="N88" s="12"/>
+      <c r="O88" s="29"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A89" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="12">
+        <v>44798</v>
+      </c>
+      <c r="D89" s="11">
+        <v>44196</v>
+      </c>
+      <c r="E89" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F89" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>-2030</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H89" s="18" t="str">
+        <f ca="1">IF(F89&lt;=0, "VENDA","CAREPACK")</f>
+        <v>VENDA</v>
+      </c>
+      <c r="I89" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K89" s="12">
         <v>40534</v>
       </c>
-      <c r="L88" s="14"/>
-      <c r="M88" s="15"/>
-      <c r="N88" s="14"/>
-      <c r="O88" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A89" s="10" t="s">
+      <c r="L89" s="12"/>
+      <c r="M89" s="12"/>
+      <c r="N89" s="12"/>
+      <c r="O89" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A90" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B90" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C90" s="12">
         <v>46199</v>
       </c>
-      <c r="D89" s="33">
+      <c r="D90" s="11">
         <v>46594</v>
       </c>
-      <c r="E89" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F89" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E90" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F90" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>368</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="G90" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H89" s="9" t="s">
+      <c r="H90" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I89" s="9" t="s">
+      <c r="I90" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J90" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K89" s="14"/>
-      <c r="L89" s="14"/>
-      <c r="M89" s="15"/>
-      <c r="N89" s="14"/>
-      <c r="O89" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A90" s="8" t="s">
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="12"/>
+      <c r="N90" s="12"/>
+      <c r="O90" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A91" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B91" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C90" s="14">
+      <c r="C91" s="12">
         <v>45822</v>
       </c>
-      <c r="D90" s="14">
+      <c r="D91" s="12">
         <v>46551</v>
       </c>
-      <c r="E90" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F90" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E91" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F91" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>325</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G91" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H90" s="9" t="str">
-        <f t="shared" ref="H90:H103" ca="1" si="11">IF(F90&lt;=0, "VENDA","CAREPACK")</f>
+      <c r="H91" s="18" t="str">
+        <f t="shared" ref="H91:H104" ca="1" si="13">IF(F91&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I90" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="11" t="s">
+      <c r="I91" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K90" s="14">
+      <c r="K91" s="12">
         <v>43913</v>
       </c>
-      <c r="L90" s="14"/>
-      <c r="M90" s="15"/>
-      <c r="N90" s="14"/>
-      <c r="O90" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A91" s="8" t="s">
+      <c r="L91" s="12"/>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
+      <c r="O91" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B91" s="36" t="s">
+      <c r="B92" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C91" s="14">
+      <c r="C92" s="12">
         <v>45993</v>
       </c>
-      <c r="D91" s="14">
+      <c r="D92" s="12">
         <v>46539</v>
       </c>
-      <c r="E91" s="13">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F91" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E92" s="11">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F92" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>313</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G92" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H91" s="9" t="str">
+      <c r="H92" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I92" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" s="12">
+        <v>45809</v>
+      </c>
+      <c r="L92" s="12"/>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
+      <c r="O92" s="29"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A93" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="12">
+        <v>44197</v>
+      </c>
+      <c r="D93" s="11">
+        <v>44196</v>
+      </c>
+      <c r="E93" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F93" s="15">
         <f t="shared" ca="1" si="11"/>
+        <v>-2030</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H93" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I93" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" s="12">
+        <v>42937</v>
+      </c>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
+      <c r="O93" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C94" s="13">
+        <v>45908</v>
+      </c>
+      <c r="D94" s="13">
+        <v>46454</v>
+      </c>
+      <c r="E94" s="23">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F94" s="24">
+        <f t="shared" ca="1" si="11"/>
+        <v>228</v>
+      </c>
+      <c r="G94" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I91" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="11" t="s">
+      <c r="I94" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="J94" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K91" s="14">
-        <v>45809</v>
-      </c>
-      <c r="L91" s="14"/>
-      <c r="M91" s="15"/>
-      <c r="N91" s="14"/>
-      <c r="O91" s="19"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A92" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B92" s="2" t="s">
+      <c r="K94" s="13">
+        <v>45055</v>
+      </c>
+      <c r="L94" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M94" s="13"/>
+      <c r="N94" s="13"/>
+      <c r="O94" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C95" s="13">
+        <v>45908</v>
+      </c>
+      <c r="D95" s="13">
+        <v>46454</v>
+      </c>
+      <c r="E95" s="23">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F95" s="24">
+        <f t="shared" ca="1" si="11"/>
+        <v>228</v>
+      </c>
+      <c r="G95" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I95" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="J95" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" s="13">
+        <v>45908</v>
+      </c>
+      <c r="L95" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M95" s="13"/>
+      <c r="N95" s="13"/>
+      <c r="O95" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="14">
-        <v>44197</v>
-      </c>
-      <c r="D92" s="13">
+      <c r="C96" s="12">
+        <v>44909</v>
+      </c>
+      <c r="D96" s="11">
         <v>44196</v>
       </c>
-      <c r="E92" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F92" s="11">
-        <f t="shared" ca="1" si="9"/>
+      <c r="E96" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F96" s="15">
+        <f t="shared" ca="1" si="11"/>
         <v>-2030</v>
       </c>
-      <c r="G92" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="H92" s="9" t="str">
+      <c r="G96" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H96" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" s="12">
+        <v>41320</v>
+      </c>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="13">
+        <v>45962</v>
+      </c>
+      <c r="D97" s="13">
+        <v>46537</v>
+      </c>
+      <c r="E97" s="13">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F97" s="24">
         <f t="shared" ca="1" si="11"/>
+        <v>311</v>
+      </c>
+      <c r="G97" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I97" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" s="13">
+        <v>43301</v>
+      </c>
+      <c r="L97" s="13"/>
+      <c r="M97" s="13"/>
+      <c r="N97" s="13"/>
+      <c r="O97" s="32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="12">
+        <v>43070</v>
+      </c>
+      <c r="D98" s="11">
+        <v>44196</v>
+      </c>
+      <c r="E98" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F98" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>-2030</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I92" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="11" t="s">
+      <c r="I98" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K92" s="14">
-        <v>42937</v>
-      </c>
-      <c r="L92" s="14"/>
-      <c r="M92" s="15"/>
-      <c r="N92" s="14"/>
-      <c r="O92" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A93" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B93" s="23" t="s">
+      <c r="K98" s="12">
+        <v>40605</v>
+      </c>
+      <c r="L98" s="12"/>
+      <c r="M98" s="12"/>
+      <c r="N98" s="12"/>
+      <c r="O98" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A99" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B99" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C93" s="25">
-        <v>45908</v>
-      </c>
-      <c r="D93" s="25">
-        <v>46454</v>
-      </c>
-      <c r="E93" s="26">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F93" s="27">
-        <f t="shared" ca="1" si="9"/>
-        <v>228</v>
-      </c>
-      <c r="G93" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="28" t="str">
+      <c r="C99" s="12">
+        <v>45874</v>
+      </c>
+      <c r="D99" s="12">
+        <v>46422</v>
+      </c>
+      <c r="E99" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F99" s="15">
         <f t="shared" ca="1" si="11"/>
+        <v>196</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H99" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I93" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="J93" s="27" t="s">
+      <c r="I99" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K99" s="12">
+        <v>45692</v>
+      </c>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A100" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="12">
+        <v>45689</v>
+      </c>
+      <c r="D100" s="11">
+        <v>44196</v>
+      </c>
+      <c r="E100" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F100" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>-2030</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H100" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I100" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K93" s="25">
-        <v>45055</v>
-      </c>
-      <c r="L93" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="M93" s="34"/>
-      <c r="N93" s="25"/>
-      <c r="O93" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A94" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B94" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C94" s="25">
-        <v>45908</v>
-      </c>
-      <c r="D94" s="25">
-        <v>46454</v>
-      </c>
-      <c r="E94" s="26">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F94" s="27">
-        <f t="shared" ca="1" si="9"/>
-        <v>228</v>
-      </c>
-      <c r="G94" s="31" t="s">
+      <c r="K100" s="12">
+        <v>40868</v>
+      </c>
+      <c r="L100" s="12"/>
+      <c r="M100" s="12"/>
+      <c r="N100" s="12"/>
+      <c r="O100" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A101" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C101" s="12">
+        <v>45315</v>
+      </c>
+      <c r="D101" s="12">
+        <v>46226</v>
+      </c>
+      <c r="E101" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F101" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H101" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I101" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" s="12">
+        <v>45131</v>
+      </c>
+      <c r="L101" s="12"/>
+      <c r="M101" s="12"/>
+      <c r="N101" s="12"/>
+      <c r="O101" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A102" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="12">
+        <v>45658</v>
+      </c>
+      <c r="D102" s="12">
+        <v>46532</v>
+      </c>
+      <c r="E102" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F102" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>306</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H102" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I102" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" s="12">
+        <v>44694</v>
+      </c>
+      <c r="L102" s="12"/>
+      <c r="M102" s="12"/>
+      <c r="N102" s="12"/>
+      <c r="O102" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A103" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C103" s="12">
+        <v>45928</v>
+      </c>
+      <c r="D103" s="12">
+        <v>46473</v>
+      </c>
+      <c r="E103" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F103" s="15">
+        <f t="shared" ca="1" si="11"/>
+        <v>247</v>
+      </c>
+      <c r="G103" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H94" s="28" t="str">
+      <c r="H103" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I103" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" s="12">
+        <v>45744</v>
+      </c>
+      <c r="L103" s="12"/>
+      <c r="M103" s="12"/>
+      <c r="N103" s="12"/>
+      <c r="O103" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104" s="12">
+        <v>45757</v>
+      </c>
+      <c r="D104" s="12">
+        <v>46669</v>
+      </c>
+      <c r="E104" s="12">
+        <f t="shared" ca="1" si="10"/>
+        <v>46226</v>
+      </c>
+      <c r="F104" s="15">
         <f t="shared" ca="1" si="11"/>
+        <v>443</v>
+      </c>
+      <c r="G104" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H104" s="18" t="str">
+        <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I94" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="J94" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K94" s="25">
-        <v>45908</v>
-      </c>
-      <c r="L94" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="M94" s="34"/>
-      <c r="N94" s="25"/>
-      <c r="O94" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A95" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B95" s="2" t="s">
+      <c r="I104" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K104" s="12">
+        <v>45575</v>
+      </c>
+      <c r="L104" s="12"/>
+      <c r="M104" s="12"/>
+      <c r="N104" s="12"/>
+      <c r="O104" s="32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A105" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="14">
-        <v>44909</v>
-      </c>
-      <c r="D95" s="13">
-        <v>44196</v>
-      </c>
-      <c r="E95" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F95" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
-      </c>
-      <c r="G95" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H95" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K95" s="14">
-        <v>41320</v>
-      </c>
-      <c r="L95" s="14"/>
-      <c r="M95" s="15"/>
-      <c r="N95" s="14"/>
-      <c r="O95" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B96" s="23" t="s">
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="15"/>
+      <c r="G105" s="16"/>
+      <c r="H105" s="18"/>
+      <c r="I105" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="15"/>
+      <c r="K105" s="12"/>
+      <c r="L105" s="12"/>
+      <c r="M105" s="12"/>
+      <c r="N105" s="12"/>
+      <c r="O105" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A106" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B106" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C96" s="25">
-        <v>45962</v>
-      </c>
-      <c r="D96" s="25">
-        <v>46537</v>
-      </c>
-      <c r="E96" s="25">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F96" s="27">
-        <f t="shared" ca="1" si="9"/>
-        <v>311</v>
-      </c>
-      <c r="G96" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="H96" s="28" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I96" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K96" s="25">
-        <v>43301</v>
-      </c>
-      <c r="L96" s="25"/>
-      <c r="M96" s="34"/>
-      <c r="N96" s="25"/>
-      <c r="O96" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" s="14">
-        <v>43070</v>
-      </c>
-      <c r="D97" s="13">
-        <v>44196</v>
-      </c>
-      <c r="E97" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F97" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
-      </c>
-      <c r="G97" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H97" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K97" s="14">
-        <v>40605</v>
-      </c>
-      <c r="L97" s="14"/>
-      <c r="M97" s="15"/>
-      <c r="N97" s="14"/>
-      <c r="O97" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A98" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C98" s="14">
-        <v>45874</v>
-      </c>
-      <c r="D98" s="14">
-        <v>46422</v>
-      </c>
-      <c r="E98" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F98" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>196</v>
-      </c>
-      <c r="G98" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H98" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K98" s="14">
-        <v>45692</v>
-      </c>
-      <c r="L98" s="14"/>
-      <c r="M98" s="15"/>
-      <c r="N98" s="14"/>
-      <c r="O98" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A99" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C99" s="14">
-        <v>45689</v>
-      </c>
-      <c r="D99" s="13">
-        <v>44196</v>
-      </c>
-      <c r="E99" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F99" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
-      </c>
-      <c r="G99" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H99" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I99" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K99" s="14">
-        <v>40868</v>
-      </c>
-      <c r="L99" s="14"/>
-      <c r="M99" s="15"/>
-      <c r="N99" s="14"/>
-      <c r="O99" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A100" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C100" s="14">
-        <v>45315</v>
-      </c>
-      <c r="D100" s="14">
-        <v>46226</v>
-      </c>
-      <c r="E100" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F100" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H100" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I100" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K100" s="14">
-        <v>45131</v>
-      </c>
-      <c r="L100" s="14"/>
-      <c r="M100" s="15"/>
-      <c r="N100" s="14"/>
-      <c r="O100" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A101" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" s="14">
-        <v>45658</v>
-      </c>
-      <c r="D101" s="14">
-        <v>46532</v>
-      </c>
-      <c r="E101" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F101" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>306</v>
-      </c>
-      <c r="G101" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H101" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I101" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K101" s="14">
-        <v>44694</v>
-      </c>
-      <c r="L101" s="14"/>
-      <c r="M101" s="15"/>
-      <c r="N101" s="14"/>
-      <c r="O101" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A102" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C102" s="14">
-        <v>45928</v>
-      </c>
-      <c r="D102" s="14">
-        <v>46473</v>
-      </c>
-      <c r="E102" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F102" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>247</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H102" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I102" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K102" s="14">
-        <v>45744</v>
-      </c>
-      <c r="L102" s="14"/>
-      <c r="M102" s="15"/>
-      <c r="N102" s="14"/>
-      <c r="O102" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C103" s="14">
-        <v>45757</v>
-      </c>
-      <c r="D103" s="14">
-        <v>46669</v>
-      </c>
-      <c r="E103" s="14">
-        <f t="shared" ca="1" si="8"/>
-        <v>46226</v>
-      </c>
-      <c r="F103" s="11">
-        <f t="shared" ca="1" si="9"/>
-        <v>443</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="H103" s="9" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I103" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K103" s="14">
-        <v>45575</v>
-      </c>
-      <c r="L103" s="14"/>
-      <c r="M103" s="15"/>
-      <c r="N103" s="14"/>
-      <c r="O103" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A104" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C104" s="14"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="11"/>
-      <c r="K104" s="14"/>
-      <c r="L104" s="14"/>
-      <c r="M104" s="15"/>
-      <c r="N104" s="14"/>
-      <c r="O104" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A105" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" s="14">
+      <c r="C106" s="12">
         <v>45536</v>
       </c>
-      <c r="D105" s="14">
+      <c r="D106" s="12">
         <v>46265</v>
       </c>
-      <c r="E105" s="14">
+      <c r="E106" s="12">
         <f ca="1">TODAY()</f>
         <v>46226</v>
       </c>
-      <c r="F105" s="11">
-        <f ca="1">D105-E105</f>
+      <c r="F106" s="15">
+        <f ca="1">D106-E106</f>
         <v>39</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="G106" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H105" s="9" t="str">
-        <f ca="1">IF(F105&lt;=0, "VENDA","CAREPACK")</f>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I105" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K105" s="14">
-        <v>44755</v>
-      </c>
-      <c r="L105" s="14"/>
-      <c r="M105" s="15"/>
-      <c r="N105" s="14"/>
-      <c r="O105" s="19"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A106" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C106" s="14">
-        <v>46226</v>
-      </c>
-      <c r="D106" s="14">
-        <v>47140</v>
-      </c>
-      <c r="E106" s="14">
-        <f ca="1">TODAY()</f>
-        <v>46226</v>
-      </c>
-      <c r="F106" s="11">
-        <f ca="1">D106-E106</f>
-        <v>914</v>
-      </c>
-      <c r="G106" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H106" s="9" t="str">
+      <c r="H106" s="18" t="str">
         <f ca="1">IF(F106&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I106" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="11" t="s">
+      <c r="I106" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K106" s="14">
-        <v>46043</v>
-      </c>
-      <c r="L106" s="14"/>
-      <c r="M106" s="15"/>
-      <c r="N106" s="14"/>
-      <c r="O106" s="19">
-        <v>90</v>
-      </c>
+      <c r="K106" s="12">
+        <v>44755</v>
+      </c>
+      <c r="L106" s="12"/>
+      <c r="M106" s="12"/>
+      <c r="N106" s="12"/>
+      <c r="O106" s="29"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A107" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B107" s="8" t="s">
+      <c r="A107" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B107" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C107" s="14">
-        <v>45839</v>
-      </c>
-      <c r="D107" s="14">
-        <v>46477</v>
-      </c>
-      <c r="E107" s="14">
+      <c r="C107" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D107" s="12">
+        <v>47140</v>
+      </c>
+      <c r="E107" s="12">
         <f ca="1">TODAY()</f>
         <v>46226</v>
       </c>
-      <c r="F107" s="11">
+      <c r="F107" s="15">
         <f ca="1">D107-E107</f>
-        <v>251</v>
-      </c>
-      <c r="G107" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H107" s="9" t="str">
+        <v>914</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H107" s="18" t="str">
         <f ca="1">IF(F107&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I107" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="11" t="s">
+      <c r="I107" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K107" s="14">
+      <c r="K107" s="12">
+        <v>46043</v>
+      </c>
+      <c r="L107" s="12"/>
+      <c r="M107" s="12"/>
+      <c r="N107" s="12"/>
+      <c r="O107" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="12">
+        <v>45839</v>
+      </c>
+      <c r="D108" s="12">
+        <v>46477</v>
+      </c>
+      <c r="E108" s="12">
+        <f ca="1">TODAY()</f>
+        <v>46226</v>
+      </c>
+      <c r="F108" s="15">
+        <f ca="1">D108-E108</f>
+        <v>251</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" s="18" t="str">
+        <f ca="1">IF(F108&lt;=0, "VENDA","CAREPACK")</f>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I108" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K108" s="12">
         <v>45639</v>
       </c>
-      <c r="L107" s="14"/>
-      <c r="M107" s="15"/>
-      <c r="N107" s="14"/>
-      <c r="O107" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A108" s="8" t="s">
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B109" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="14">
+      <c r="C109" s="12">
         <v>44861</v>
       </c>
-      <c r="D108" s="13">
+      <c r="D109" s="11">
         <v>44196</v>
       </c>
-      <c r="E108" s="14">
+      <c r="E109" s="12">
         <f ca="1">TODAY()</f>
         <v>46226</v>
       </c>
-      <c r="F108" s="11">
-        <f ca="1">D108-E108</f>
-        <v>-2030</v>
-      </c>
-      <c r="G108" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="H108" s="9" t="str">
-        <f ca="1">IF(F108&lt;=0, "VENDA","CAREPACK")</f>
-        <v>VENDA</v>
-      </c>
-      <c r="I108" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J108" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K108" s="14">
-        <v>40801</v>
-      </c>
-      <c r="L108" s="14"/>
-      <c r="M108" s="15"/>
-      <c r="N108" s="14"/>
-      <c r="O108" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A109" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C109" s="14">
-        <v>44861</v>
-      </c>
-      <c r="D109" s="13">
-        <v>44196</v>
-      </c>
-      <c r="E109" s="14">
-        <f ca="1">TODAY()</f>
-        <v>46226</v>
-      </c>
-      <c r="F109" s="11">
+      <c r="F109" s="15">
         <f ca="1">D109-E109</f>
         <v>-2030</v>
       </c>
-      <c r="G109" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H109" s="9" t="str">
+      <c r="G109" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H109" s="18" t="str">
         <f ca="1">IF(F109&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I109" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J109" s="11" t="s">
+      <c r="I109" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K109" s="14">
+      <c r="K109" s="12">
+        <v>40801</v>
+      </c>
+      <c r="L109" s="12"/>
+      <c r="M109" s="12"/>
+      <c r="N109" s="12"/>
+      <c r="O109" s="29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B110" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="35">
+        <v>44861</v>
+      </c>
+      <c r="D110" s="36">
+        <v>44196</v>
+      </c>
+      <c r="E110" s="35">
+        <f ca="1">TODAY()</f>
+        <v>46226</v>
+      </c>
+      <c r="F110" s="37">
+        <f ca="1">D110-E110</f>
+        <v>-2030</v>
+      </c>
+      <c r="G110" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H110" s="39" t="str">
+        <f ca="1">IF(F110&lt;=0, "VENDA","CAREPACK")</f>
+        <v>VENDA</v>
+      </c>
+      <c r="I110" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" s="35">
         <v>40634</v>
       </c>
-      <c r="L109" s="14"/>
-      <c r="M109" s="15"/>
-      <c r="N109" s="14"/>
-      <c r="O109" s="19">
+      <c r="L110" s="35"/>
+      <c r="M110" s="35"/>
+      <c r="N110" s="35"/>
+      <c r="O110" s="40">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N109" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N109">
-      <sortCondition ref="A1:A109"/>
+  <autoFilter ref="A1:N110" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N110">
+      <sortCondition ref="A1:A110"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
@@ -328,6 +328,12 @@
     <t>IPSIS</t>
   </si>
   <si>
+    <t>HP INDIGO 18K</t>
+  </si>
+  <si>
+    <t>03 MESES DE MÃO DE OBRA (ATÉ 31/10/26)</t>
+  </si>
+  <si>
     <t>JM EMBALAGENS</t>
   </si>
   <si>
@@ -385,6 +391,12 @@
     <t>OUTLABEL</t>
   </si>
   <si>
+    <t>03 MESES DE MÃO DE OBRA</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ENTREGA</t>
+  </si>
+  <si>
     <t xml:space="preserve">P+E </t>
   </si>
   <si>
@@ -400,9 +412,6 @@
     <t xml:space="preserve">PIGMA    </t>
   </si>
   <si>
-    <t>HP INDIGO 18K</t>
-  </si>
-  <si>
     <t>SERVIÇOS ATÉ 27/11/27</t>
   </si>
   <si>
@@ -650,15 +659,6 @@
   </si>
   <si>
     <t>ULTRAPRESS EDITORA E GRAFICA</t>
-  </si>
-  <si>
-    <t>03 MESES DE MÃO DE OBRA (ATÉ 31/10/26)</t>
-  </si>
-  <si>
-    <t>03 MESES DE MÃO DE OBRA</t>
-  </si>
-  <si>
-    <t>AGUARDANDO ENTREGA</t>
   </si>
 </sst>
 </file>
@@ -669,7 +669,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1395,26 +1395,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
   <dimension ref="A1:O110"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15">
       <c r="A2" s="41" t="s">
         <v>14</v>
       </c>
@@ -1476,11 +1476,11 @@
       </c>
       <c r="E2" s="43">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F2" s="44">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>16</v>
@@ -1505,7 +1505,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" s="28" t="s">
         <v>19</v>
       </c>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>21</v>
@@ -1549,7 +1549,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>22</v>
@@ -1593,7 +1593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15">
       <c r="A5" s="28" t="s">
         <v>19</v>
       </c>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>23</v>
@@ -1637,7 +1637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15">
       <c r="A6" s="28" t="s">
         <v>25</v>
       </c>
@@ -1652,11 +1652,11 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>26</v>
@@ -1681,7 +1681,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="A7" s="28" t="s">
         <v>25</v>
       </c>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="A8" s="28" t="s">
         <v>27</v>
       </c>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>29</v>
@@ -1769,7 +1769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="A9" s="28" t="s">
         <v>27</v>
       </c>
@@ -1784,11 +1784,11 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-402</v>
+        <v>-403</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>22</v>
@@ -1811,7 +1811,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="A10" s="28" t="s">
         <v>30</v>
       </c>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>31</v>
@@ -1853,7 +1853,7 @@
       <c r="N10" s="11"/>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="A11" s="30" t="s">
         <v>30</v>
       </c>
@@ -1868,11 +1868,11 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>32</v>
@@ -1897,7 +1897,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15">
       <c r="A12" s="30" t="s">
         <v>33</v>
       </c>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>34</v>
@@ -1942,7 +1942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="A13" s="30" t="s">
         <v>37</v>
       </c>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>38</v>
@@ -1987,7 +1987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15">
       <c r="A14" s="30" t="s">
         <v>40</v>
       </c>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>16</v>
@@ -2030,7 +2030,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15">
       <c r="A15" s="30" t="s">
         <v>42</v>
       </c>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>26</v>
@@ -2075,7 +2075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15">
       <c r="A16" s="30" t="s">
         <v>45</v>
       </c>
@@ -2090,11 +2090,11 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>46</v>
@@ -2118,7 +2118,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15">
       <c r="A17" s="30" t="s">
         <v>48</v>
       </c>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F17" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>49</v>
@@ -2161,7 +2161,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15">
       <c r="A18" s="30" t="s">
         <v>50</v>
       </c>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F18" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>16</v>
@@ -2204,7 +2204,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15">
       <c r="A19" s="30" t="s">
         <v>52</v>
       </c>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F19" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>26</v>
@@ -2247,7 +2247,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15">
       <c r="A20" s="30" t="s">
         <v>53</v>
       </c>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F20" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>16</v>
@@ -2290,7 +2290,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15">
       <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F21" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>31</v>
@@ -2334,7 +2334,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15">
       <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
@@ -2349,11 +2349,11 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F22" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>32</v>
@@ -2378,7 +2378,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15">
       <c r="A23" s="30" t="s">
         <v>56</v>
       </c>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F23" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>38</v>
@@ -2422,7 +2422,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15">
       <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F24" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G24" s="25" t="s">
         <v>59</v>
@@ -2468,7 +2468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15">
       <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>59</v>
@@ -2514,7 +2514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15">
       <c r="A26" s="30" t="s">
         <v>58</v>
       </c>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="E26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F26" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>34</v>
@@ -2560,7 +2560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15">
       <c r="A27" s="30" t="s">
         <v>61</v>
       </c>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F27" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>34</v>
@@ -2606,7 +2606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" s="9" customFormat="1">
       <c r="A28" s="30" t="s">
         <v>62</v>
       </c>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="E28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F28" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>63</v>
@@ -2649,7 +2649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" s="9" customFormat="1">
       <c r="A29" s="30" t="s">
         <v>62</v>
       </c>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="E29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F29" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>32</v>
@@ -2693,7 +2693,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15">
       <c r="A30" s="30" t="s">
         <v>65</v>
       </c>
@@ -2708,11 +2708,11 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F30" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>66</v>
@@ -2737,7 +2737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15">
       <c r="A31" s="31" t="s">
         <v>67</v>
       </c>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G31" s="25" t="s">
         <v>16</v>
@@ -2781,7 +2781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1">
       <c r="A32" s="30" t="s">
         <v>68</v>
       </c>
@@ -2796,11 +2796,11 @@
       </c>
       <c r="E32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F32" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>31</v>
@@ -2825,7 +2825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15">
       <c r="A33" s="28" t="s">
         <v>69</v>
       </c>
@@ -2840,11 +2840,11 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F33" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>22</v>
@@ -2869,7 +2869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15">
       <c r="A34" s="30" t="s">
         <v>70</v>
       </c>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="E34" s="11">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F34" s="15">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>21</v>
@@ -2913,7 +2913,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15">
       <c r="A35" s="30" t="s">
         <v>71</v>
       </c>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="E35" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F35" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="30" t="s">
         <v>72</v>
       </c>
@@ -2972,11 +2972,11 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>73</v>
@@ -3000,7 +3000,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15">
       <c r="A37" s="30" t="s">
         <v>72</v>
       </c>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>75</v>
@@ -3043,7 +3043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15">
       <c r="A38" s="30" t="s">
         <v>76</v>
       </c>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>73</v>
@@ -3087,7 +3087,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15">
       <c r="A39" s="30" t="s">
         <v>77</v>
       </c>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="E39" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>31</v>
@@ -3131,7 +3131,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15">
       <c r="A40" s="30" t="s">
         <v>77</v>
       </c>
@@ -3146,11 +3146,11 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>78</v>
@@ -3175,7 +3175,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15">
       <c r="A41" s="31" t="s">
         <v>79</v>
       </c>
@@ -3190,11 +3190,11 @@
       </c>
       <c r="E41" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F41" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>80</v>
@@ -3218,7 +3218,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15">
       <c r="A42" s="30" t="s">
         <v>83</v>
       </c>
@@ -3233,11 +3233,11 @@
       </c>
       <c r="E42" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -3262,7 +3262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15">
       <c r="A43" s="30" t="s">
         <v>83</v>
       </c>
@@ -3277,11 +3277,11 @@
       </c>
       <c r="E43" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>32</v>
@@ -3306,7 +3306,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" s="9" customFormat="1">
       <c r="A44" s="30" t="s">
         <v>84</v>
       </c>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="E44" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>85</v>
@@ -3350,7 +3350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15">
       <c r="A45" s="30" t="s">
         <v>86</v>
       </c>
@@ -3365,11 +3365,11 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F45" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>31</v>
@@ -3394,7 +3394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15">
       <c r="A46" s="30" t="s">
         <v>87</v>
       </c>
@@ -3409,11 +3409,11 @@
       </c>
       <c r="E46" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F46" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>16</v>
@@ -3438,7 +3438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15">
       <c r="A47" s="30" t="s">
         <v>88</v>
       </c>
@@ -3453,11 +3453,11 @@
       </c>
       <c r="E47" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F47" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>21</v>
@@ -3482,7 +3482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15">
       <c r="A48" s="30" t="s">
         <v>89</v>
       </c>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F48" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>63</v>
@@ -3528,7 +3528,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15">
       <c r="A49" s="30" t="s">
         <v>90</v>
       </c>
@@ -3543,11 +3543,11 @@
       </c>
       <c r="E49" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F49" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>63</v>
@@ -3572,7 +3572,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15">
       <c r="A50" s="30" t="s">
         <v>91</v>
       </c>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="E50" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F50" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>26</v>
@@ -3618,7 +3618,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15">
       <c r="A51" s="30" t="s">
         <v>91</v>
       </c>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="E51" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F51" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>22</v>
@@ -3664,7 +3664,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15">
       <c r="A52" s="30" t="s">
         <v>91</v>
       </c>
@@ -3679,11 +3679,11 @@
       </c>
       <c r="E52" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F52" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>16</v>
@@ -3710,7 +3710,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" s="9" customFormat="1">
       <c r="A53" s="30" t="s">
         <v>93</v>
       </c>
@@ -3725,11 +3725,11 @@
       </c>
       <c r="E53" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F53" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>78</v>
@@ -3754,7 +3754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" s="9" customFormat="1">
       <c r="A54" s="30" t="s">
         <v>94</v>
       </c>
@@ -3769,21 +3769,21 @@
       </c>
       <c r="E54" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F54" s="15">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H54" s="18" t="str">
         <f t="shared" ref="H54" ca="1" si="8">IF(F54&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>24</v>
@@ -3798,9 +3798,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15">
       <c r="A55" s="30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>15</v>
@@ -3813,11 +3813,11 @@
       </c>
       <c r="E55" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>22</v>
@@ -3842,9 +3842,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15">
       <c r="A56" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>15</v>
@@ -3857,14 +3857,14 @@
       </c>
       <c r="E56" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H56" s="18" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -3886,9 +3886,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15">
       <c r="A57" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>15</v>
@@ -3901,11 +3901,11 @@
       </c>
       <c r="E57" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>63</v>
@@ -3930,9 +3930,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15">
       <c r="A58" s="30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>15</v>
@@ -3945,11 +3945,11 @@
       </c>
       <c r="E58" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>31</v>
@@ -3974,9 +3974,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15">
       <c r="A59" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>20</v>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="E59" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>34</v>
@@ -4002,7 +4002,7 @@
         <v>35</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J59" s="15" t="s">
         <v>24</v>
@@ -4017,9 +4017,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15">
       <c r="A60" s="30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>15</v>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="E60" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>32</v>
@@ -4061,9 +4061,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15">
       <c r="A61" s="30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>20</v>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E61" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>66</v>
@@ -4105,9 +4105,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15">
       <c r="A62" s="30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>15</v>
@@ -4120,14 +4120,14 @@
       </c>
       <c r="E62" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H62" s="18" t="str">
         <f ca="1">IF(F62&lt;=0, "VENDA","CAREPACK")</f>
@@ -4149,9 +4149,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15">
       <c r="A63" s="30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>15</v>
@@ -4164,11 +4164,11 @@
       </c>
       <c r="E63" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>66</v>
@@ -4193,9 +4193,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15">
       <c r="A64" s="31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B64" s="27" t="s">
         <v>15</v>
@@ -4208,11 +4208,11 @@
       </c>
       <c r="E64" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F64" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>16</v>
@@ -4237,9 +4237,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15">
       <c r="A65" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>20</v>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="E65" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>63</v>
@@ -4280,9 +4280,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15">
       <c r="A66" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>15</v>
@@ -4295,11 +4295,11 @@
       </c>
       <c r="E66" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>31</v>
@@ -4324,9 +4324,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15">
       <c r="A67" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>15</v>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="E67" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>63</v>
@@ -4368,9 +4368,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" s="9" customFormat="1">
       <c r="A68" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>15</v>
@@ -4383,11 +4383,11 @@
       </c>
       <c r="E68" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>32</v>
@@ -4412,9 +4412,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15">
       <c r="A69" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B69" s="14"/>
       <c r="C69" s="12"/>
@@ -4435,9 +4435,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15">
       <c r="A70" s="31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B70" s="27" t="s">
         <v>15</v>
@@ -4450,11 +4450,11 @@
       </c>
       <c r="E70" s="13">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F70" s="24">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G70" s="25" t="s">
         <v>22</v>
@@ -4477,9 +4477,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15">
       <c r="A71" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>20</v>
@@ -4492,11 +4492,11 @@
       </c>
       <c r="E71" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>34</v>
@@ -4505,7 +4505,7 @@
         <v>35</v>
       </c>
       <c r="I71" s="18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J71" s="15" t="s">
         <v>24</v>
@@ -4514,7 +4514,7 @@
         <v>44841</v>
       </c>
       <c r="L71" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
@@ -4522,9 +4522,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15">
       <c r="A72" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B72" s="20" t="s">
         <v>20</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="E72" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>66</v>
@@ -4564,9 +4564,9 @@
       <c r="N72" s="12"/>
       <c r="O72" s="29"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15">
       <c r="A73" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B73" s="20" t="s">
         <v>20</v>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="E73" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>22</v>
@@ -4608,9 +4608,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" s="9" customFormat="1">
       <c r="A74" s="31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B74" s="22" t="s">
         <v>20</v>
@@ -4624,22 +4624,22 @@
       </c>
       <c r="H74" s="26"/>
       <c r="I74" s="26" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="J74" s="24" t="s">
         <v>18</v>
       </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="M74" s="13"/>
       <c r="N74" s="13"/>
       <c r="O74" s="32"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15">
       <c r="A75" s="30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>15</v>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E75" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F75" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>32</v>
@@ -4675,7 +4675,7 @@
         <v>45999</v>
       </c>
       <c r="L75" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
@@ -4683,9 +4683,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15">
       <c r="A76" s="30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>57</v>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="E76" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F76" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>85</v>
@@ -4721,7 +4721,7 @@
         <v>45371</v>
       </c>
       <c r="L76" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
@@ -4729,9 +4729,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15">
       <c r="A77" s="30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>15</v>
@@ -4744,11 +4744,11 @@
       </c>
       <c r="E77" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F77" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>23</v>
@@ -4767,7 +4767,7 @@
         <v>45273</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M77" s="12"/>
       <c r="N77" s="12"/>
@@ -4775,9 +4775,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15">
       <c r="A78" s="30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>51</v>
@@ -4790,20 +4790,20 @@
       </c>
       <c r="E78" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F78" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H78" s="18" t="s">
         <v>35</v>
       </c>
       <c r="I78" s="18" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J78" s="15" t="s">
         <v>24</v>
@@ -4812,7 +4812,7 @@
         <v>45989</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
@@ -4820,9 +4820,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15">
       <c r="A79" s="30" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>15</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="E79" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F79" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>34</v>
@@ -4849,7 +4849,7 @@
         <v>VENDA</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J79" s="15" t="s">
         <v>24</v>
@@ -4864,9 +4864,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15">
       <c r="A80" s="30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>15</v>
@@ -4879,11 +4879,11 @@
       </c>
       <c r="E80" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F80" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>66</v>
@@ -4908,9 +4908,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15">
       <c r="A81" s="30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>15</v>
@@ -4923,11 +4923,11 @@
       </c>
       <c r="E81" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F81" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>26</v>
@@ -4952,9 +4952,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15">
       <c r="A82" s="30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>15</v>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="E82" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F82" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>26</v>
@@ -4996,9 +4996,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15">
       <c r="A83" s="30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>57</v>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="E83" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F83" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>22</v>
@@ -5040,9 +5040,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15">
       <c r="A84" s="30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>57</v>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="E84" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F84" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>16</v>
@@ -5084,9 +5084,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15">
       <c r="A85" s="30" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>28</v>
@@ -5099,11 +5099,11 @@
       </c>
       <c r="E85" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F85" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>75</v>
@@ -5117,7 +5117,7 @@
       <c r="J85" s="15"/>
       <c r="K85" s="12"/>
       <c r="L85" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
@@ -5125,12 +5125,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15">
       <c r="A86" s="30" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C86" s="12">
         <v>46082</v>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="E86" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F86" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>34</v>
@@ -5153,7 +5153,7 @@
         <v>35</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J86" s="15" t="s">
         <v>24</v>
@@ -5168,9 +5168,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15">
       <c r="A87" s="30" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>20</v>
@@ -5183,11 +5183,11 @@
       </c>
       <c r="E87" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F87" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>73</v>
@@ -5196,7 +5196,7 @@
         <v>35</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J87" s="16" t="s">
         <v>74</v>
@@ -5211,9 +5211,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15">
       <c r="A88" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>15</v>
@@ -5226,11 +5226,11 @@
       </c>
       <c r="E88" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F88" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>21</v>
@@ -5253,9 +5253,9 @@
       <c r="N88" s="12"/>
       <c r="O88" s="29"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15">
       <c r="A89" s="30" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>15</v>
@@ -5268,11 +5268,11 @@
       </c>
       <c r="E89" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F89" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>31</v>
@@ -5297,12 +5297,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15">
       <c r="A90" s="30" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C90" s="12">
         <v>46199</v>
@@ -5312,20 +5312,20 @@
       </c>
       <c r="E90" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F90" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H90" s="18" t="s">
         <v>35</v>
       </c>
       <c r="I90" s="18" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J90" s="15" t="s">
         <v>18</v>
@@ -5338,9 +5338,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15">
       <c r="A91" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>57</v>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="E91" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F91" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>22</v>
@@ -5382,9 +5382,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15">
       <c r="A92" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>57</v>
@@ -5397,11 +5397,11 @@
       </c>
       <c r="E92" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F92" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>16</v>
@@ -5424,9 +5424,9 @@
       <c r="N92" s="12"/>
       <c r="O92" s="29"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15">
       <c r="A93" s="30" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>15</v>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="E93" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F93" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H93" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5468,9 +5468,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15">
       <c r="A94" s="31" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B94" s="22" t="s">
         <v>57</v>
@@ -5483,11 +5483,11 @@
       </c>
       <c r="E94" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F94" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>26</v>
@@ -5506,7 +5506,7 @@
         <v>45055</v>
       </c>
       <c r="L94" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M94" s="13"/>
       <c r="N94" s="13"/>
@@ -5514,9 +5514,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15">
       <c r="A95" s="31" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B95" s="22" t="s">
         <v>51</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="E95" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F95" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>16</v>
@@ -5552,7 +5552,7 @@
         <v>45908</v>
       </c>
       <c r="L95" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M95" s="13"/>
       <c r="N95" s="13"/>
@@ -5560,9 +5560,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15">
       <c r="A96" s="30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>15</v>
@@ -5575,11 +5575,11 @@
       </c>
       <c r="E96" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>31</v>
@@ -5604,9 +5604,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" s="9" customFormat="1">
       <c r="A97" s="31" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B97" s="22" t="s">
         <v>20</v>
@@ -5619,11 +5619,11 @@
       </c>
       <c r="E97" s="13">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F97" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>32</v>
@@ -5648,9 +5648,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1">
       <c r="A98" s="30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>15</v>
@@ -5663,11 +5663,11 @@
       </c>
       <c r="E98" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>21</v>
@@ -5692,9 +5692,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15">
       <c r="A99" s="30" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B99" s="20" t="s">
         <v>57</v>
@@ -5707,11 +5707,11 @@
       </c>
       <c r="E99" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>85</v>
@@ -5736,9 +5736,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15">
       <c r="A100" s="30" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>15</v>
@@ -5751,11 +5751,11 @@
       </c>
       <c r="E100" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>31</v>
@@ -5780,9 +5780,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15">
       <c r="A101" s="30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B101" s="20" t="s">
         <v>57</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="E101" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H101" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5824,9 +5824,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15">
       <c r="A102" s="30" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B102" s="20" t="s">
         <v>20</v>
@@ -5839,21 +5839,21 @@
       </c>
       <c r="E102" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H102" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>18</v>
@@ -5868,9 +5868,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15">
       <c r="A103" s="30" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B103" s="20" t="s">
         <v>57</v>
@@ -5883,11 +5883,11 @@
       </c>
       <c r="E103" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>16</v>
@@ -5912,9 +5912,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" s="9" customFormat="1">
       <c r="A104" s="30" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B104" s="20" t="s">
         <v>57</v>
@@ -5927,14 +5927,14 @@
       </c>
       <c r="E104" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H104" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5956,9 +5956,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15">
       <c r="A105" s="30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>15</v>
@@ -5981,9 +5981,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15">
       <c r="A106" s="30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B106" s="20" t="s">
         <v>20</v>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="E106" s="12">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F106" s="15">
         <f ca="1">D106-E106</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>38</v>
@@ -6023,9 +6023,9 @@
       <c r="N106" s="12"/>
       <c r="O106" s="29"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15">
       <c r="A107" s="30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B107" s="20" t="s">
         <v>20</v>
@@ -6038,11 +6038,11 @@
       </c>
       <c r="E107" s="12">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F107" s="15">
         <f ca="1">D107-E107</f>
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>29</v>
@@ -6067,9 +6067,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15">
       <c r="A108" s="30" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B108" s="20" t="s">
         <v>20</v>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="E108" s="12">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F108" s="15">
         <f ca="1">D108-E108</f>
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>34</v>
@@ -6111,9 +6111,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15">
       <c r="A109" s="30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>15</v>
@@ -6126,14 +6126,14 @@
       </c>
       <c r="E109" s="12">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F109" s="15">
         <f ca="1">D109-E109</f>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H109" s="18" t="str">
         <f ca="1">IF(F109&lt;=0, "VENDA","CAREPACK")</f>
@@ -6155,9 +6155,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:15" ht="15" thickBot="1">
       <c r="A110" s="33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>15</v>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="E110" s="35">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F110" s="37">
         <f ca="1">D110-E110</f>
-        <v>-2030</v>
+        <v>-2031</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>31</v>
@@ -6212,25 +6212,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="4" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6238,10 +6238,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -6259,27 +6259,27 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3">
         <v>45670</v>
@@ -6290,14 +6290,14 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K2" s="3">
         <v>45670</v>
@@ -6312,12 +6312,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3">
         <v>45670</v>
@@ -6328,14 +6328,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K3" s="3">
         <v>45685</v>
@@ -6350,12 +6350,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C4" s="3">
         <v>45670</v>
@@ -6366,14 +6366,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K4" s="3">
         <v>45670</v>
@@ -6388,12 +6388,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C5" s="3">
         <v>45670</v>
@@ -6404,14 +6404,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K5" s="3">
         <v>45670</v>
@@ -6426,12 +6426,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3">
         <v>44866</v>
@@ -6442,14 +6442,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K6" s="3">
         <v>42867</v>
@@ -6464,12 +6464,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C7" s="3">
         <v>45670</v>
@@ -6480,14 +6480,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K7" s="3">
         <v>45670</v>
@@ -6502,12 +6502,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C8" s="3">
         <v>45670</v>
@@ -6518,14 +6518,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K8" s="3">
         <v>45670</v>
@@ -6540,12 +6540,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C9" s="3">
         <v>45670</v>
@@ -6556,14 +6556,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K9" s="3">
         <v>45670</v>
@@ -6578,12 +6578,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C10" s="3">
         <v>44501</v>
@@ -6594,14 +6594,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K10" s="3">
         <v>42949</v>
@@ -6616,12 +6616,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C11" s="3">
         <v>45670</v>
@@ -6632,14 +6632,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K11" s="3">
         <v>45670</v>
@@ -6654,12 +6654,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C12" s="3">
         <v>45670</v>
@@ -6670,14 +6670,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K12" s="3">
         <v>45670</v>
@@ -6692,12 +6692,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C13" s="3">
         <v>45658</v>
@@ -6708,14 +6708,14 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K13" s="3">
         <v>42972</v>
@@ -6730,12 +6730,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="3">
         <v>45670</v>
@@ -6746,14 +6746,14 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K14" s="3">
         <v>45670</v>
@@ -6768,12 +6768,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C15" s="3">
         <v>44911</v>
@@ -6784,14 +6784,14 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K15" s="3">
         <v>41417</v>
@@ -6806,12 +6806,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C16" s="3">
         <v>45670</v>
@@ -6822,14 +6822,14 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K16" s="3">
         <v>45670</v>
@@ -6844,12 +6844,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C17" s="3">
         <v>45670</v>
@@ -6860,14 +6860,14 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K17" s="3">
         <v>45670</v>
@@ -6882,12 +6882,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C18" s="3">
         <v>45670</v>
@@ -6898,14 +6898,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K18" s="3">
         <v>45670</v>
@@ -6920,12 +6920,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C19" s="3">
         <v>45670</v>
@@ -6936,14 +6936,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K19" s="3">
         <v>45670</v>
@@ -6958,12 +6958,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C20" s="3">
         <v>45670</v>
@@ -6974,14 +6974,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K20" s="3">
         <v>45670</v>
@@ -6996,12 +6996,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C21" s="3">
         <v>45658</v>
@@ -7012,14 +7012,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K21" s="3">
         <v>40396</v>
@@ -7034,12 +7034,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C22" s="3">
         <v>45658</v>
@@ -7050,14 +7050,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K22" s="3">
         <v>43783</v>
@@ -7072,12 +7072,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C23" s="3">
         <v>44501</v>
@@ -7088,14 +7088,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K23" s="3">
         <v>42119</v>
@@ -7110,12 +7110,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3">
         <v>45670</v>
@@ -7126,14 +7126,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K24" s="3">
         <v>45670</v>
@@ -7148,12 +7148,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3">
         <v>45670</v>
@@ -7164,14 +7164,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K25" s="3">
         <v>45670</v>
@@ -7186,12 +7186,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3">
         <v>45670</v>
@@ -7202,14 +7202,14 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K26" s="3">
         <v>45670</v>
@@ -7224,12 +7224,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C27" s="3">
         <v>45670</v>
@@ -7240,14 +7240,14 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K27" s="3">
         <v>45670</v>
@@ -7262,12 +7262,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C28" s="3">
         <v>45658</v>
@@ -7278,14 +7278,14 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K28" s="3">
         <v>39766</v>
@@ -7300,12 +7300,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C29" s="3">
         <v>45658</v>
@@ -7316,14 +7316,14 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K29" s="3">
         <v>41075</v>
@@ -7338,12 +7338,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C30" s="3">
         <v>45670</v>
@@ -7354,14 +7354,14 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K30" s="3">
         <v>45670</v>
@@ -7376,12 +7376,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3">
         <v>45670</v>
@@ -7392,14 +7392,14 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K31" s="3">
         <v>45670</v>
@@ -7414,12 +7414,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C32" s="3">
         <v>45016</v>
@@ -7430,14 +7430,14 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K32" s="3">
         <v>45016</v>
@@ -7452,12 +7452,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C33" s="3">
         <v>44743</v>
@@ -7468,14 +7468,14 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K33" s="3">
         <v>42886</v>
@@ -7490,12 +7490,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C34" s="3">
         <v>45670</v>
@@ -7506,14 +7506,14 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K34" s="3">
         <v>45670</v>
@@ -7528,12 +7528,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C35" s="3">
         <v>45009</v>
@@ -7544,14 +7544,14 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K35" s="3">
         <v>45009</v>
@@ -7566,12 +7566,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C36" s="3">
         <v>45658</v>
@@ -7582,14 +7582,14 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K36" s="3">
         <v>43021</v>
@@ -7604,12 +7604,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C37" s="3">
         <v>45670</v>
@@ -7620,14 +7620,14 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K37" s="3">
         <v>45670</v>
@@ -7642,12 +7642,12 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C38" s="3">
         <v>44866</v>
@@ -7658,14 +7658,14 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K38" s="3">
         <v>40389</v>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="490" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDCFAA8D-43D9-44C4-93F2-FFC716E9E06E}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956E0204-0911-4159-B5F5-3AA726E550DF}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1476,11 +1476,11 @@
       </c>
       <c r="E2" s="43">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F2" s="44">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>16</v>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>21</v>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>22</v>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>23</v>
@@ -1652,11 +1652,11 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>26</v>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-166</v>
+        <v>-169</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>29</v>
@@ -1784,11 +1784,11 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-403</v>
+        <v>-406</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>22</v>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>31</v>
@@ -1868,11 +1868,11 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>32</v>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>34</v>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>38</v>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>16</v>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>26</v>
@@ -2090,11 +2090,11 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>46</v>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F17" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>49</v>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F18" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>16</v>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F19" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>26</v>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F20" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>16</v>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F21" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>31</v>
@@ -2349,11 +2349,11 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F22" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>32</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F23" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>38</v>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F24" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G24" s="25" t="s">
         <v>59</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>59</v>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="E26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F26" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>34</v>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F27" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>34</v>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="E28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F28" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5274</v>
+        <v>5271</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>63</v>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="E29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F29" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>32</v>
@@ -2708,11 +2708,11 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F30" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>66</v>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G31" s="25" t="s">
         <v>16</v>
@@ -2796,11 +2796,11 @@
       </c>
       <c r="E32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F32" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>31</v>
@@ -2840,11 +2840,11 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F33" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>22</v>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="E34" s="11">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F34" s="15">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>21</v>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="E35" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F35" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>16</v>
@@ -2972,11 +2972,11 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>73</v>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>75</v>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>73</v>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="E39" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>31</v>
@@ -3146,11 +3146,11 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>78</v>
@@ -3190,11 +3190,11 @@
       </c>
       <c r="E41" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F41" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>80</v>
@@ -3233,11 +3233,11 @@
       </c>
       <c r="E42" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -3277,11 +3277,11 @@
       </c>
       <c r="E43" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>32</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="E44" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>85</v>
@@ -3365,11 +3365,11 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F45" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>31</v>
@@ -3409,11 +3409,11 @@
       </c>
       <c r="E46" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F46" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>16</v>
@@ -3453,11 +3453,11 @@
       </c>
       <c r="E47" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F47" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>21</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F48" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>63</v>
@@ -3543,11 +3543,11 @@
       </c>
       <c r="E49" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F49" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>63</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="E50" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F50" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>26</v>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="E51" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F51" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>22</v>
@@ -3679,11 +3679,11 @@
       </c>
       <c r="E52" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F52" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>16</v>
@@ -3725,11 +3725,11 @@
       </c>
       <c r="E53" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F53" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>78</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="E54" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F54" s="15">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>95</v>
@@ -3813,11 +3813,11 @@
       </c>
       <c r="E55" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>22</v>
@@ -3857,11 +3857,11 @@
       </c>
       <c r="E56" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>99</v>
@@ -3901,11 +3901,11 @@
       </c>
       <c r="E57" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>63</v>
@@ -3945,11 +3945,11 @@
       </c>
       <c r="E58" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>31</v>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="E59" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>34</v>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="E60" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>32</v>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E61" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-205</v>
+        <v>-208</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>66</v>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="E62" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>106</v>
@@ -4164,11 +4164,11 @@
       </c>
       <c r="E63" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>66</v>
@@ -4208,11 +4208,11 @@
       </c>
       <c r="E64" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F64" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>-145</v>
+        <v>-148</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>16</v>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="E65" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>63</v>
@@ -4295,11 +4295,11 @@
       </c>
       <c r="E66" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>31</v>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="E67" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>63</v>
@@ -4383,11 +4383,11 @@
       </c>
       <c r="E68" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>32</v>
@@ -4450,11 +4450,11 @@
       </c>
       <c r="E70" s="13">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F70" s="24">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G70" s="25" t="s">
         <v>22</v>
@@ -4492,11 +4492,11 @@
       </c>
       <c r="E71" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>34</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="E72" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>66</v>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="E73" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>22</v>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E75" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F75" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>32</v>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="E76" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F76" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>85</v>
@@ -4744,11 +4744,11 @@
       </c>
       <c r="E77" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F77" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>23</v>
@@ -4790,11 +4790,11 @@
       </c>
       <c r="E78" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F78" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>95</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="E79" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F79" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>34</v>
@@ -4879,11 +4879,11 @@
       </c>
       <c r="E80" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F80" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>66</v>
@@ -4923,11 +4923,11 @@
       </c>
       <c r="E81" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F81" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>26</v>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="E82" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F82" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>26</v>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="E83" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F83" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>22</v>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="E84" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F84" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>16</v>
@@ -5099,11 +5099,11 @@
       </c>
       <c r="E85" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F85" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>75</v>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="E86" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F86" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>34</v>
@@ -5183,11 +5183,11 @@
       </c>
       <c r="E87" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F87" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>73</v>
@@ -5226,11 +5226,11 @@
       </c>
       <c r="E88" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F88" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>21</v>
@@ -5268,11 +5268,11 @@
       </c>
       <c r="E89" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F89" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>31</v>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="E90" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F90" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>106</v>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="E91" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F91" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>22</v>
@@ -5397,11 +5397,11 @@
       </c>
       <c r="E92" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F92" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>16</v>
@@ -5439,11 +5439,11 @@
       </c>
       <c r="E93" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F93" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>139</v>
@@ -5483,11 +5483,11 @@
       </c>
       <c r="E94" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F94" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>26</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="E95" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F95" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>16</v>
@@ -5575,11 +5575,11 @@
       </c>
       <c r="E96" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>31</v>
@@ -5619,11 +5619,11 @@
       </c>
       <c r="E97" s="13">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F97" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>32</v>
@@ -5663,11 +5663,11 @@
       </c>
       <c r="E98" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>21</v>
@@ -5707,11 +5707,11 @@
       </c>
       <c r="E99" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>85</v>
@@ -5751,11 +5751,11 @@
       </c>
       <c r="E100" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>31</v>
@@ -5795,11 +5795,11 @@
       </c>
       <c r="E101" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="G101" s="16" t="s">
         <v>106</v>
@@ -5839,11 +5839,11 @@
       </c>
       <c r="E102" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G102" s="16" t="s">
         <v>106</v>
@@ -5883,11 +5883,11 @@
       </c>
       <c r="E103" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>16</v>
@@ -5927,11 +5927,11 @@
       </c>
       <c r="E104" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>151</v>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="E106" s="12">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F106" s="15">
         <f ca="1">D106-E106</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>38</v>
@@ -6038,11 +6038,11 @@
       </c>
       <c r="E107" s="12">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F107" s="15">
         <f ca="1">D107-E107</f>
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>29</v>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="E108" s="12">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F108" s="15">
         <f ca="1">D108-E108</f>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>34</v>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="E109" s="12">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F109" s="15">
         <f ca="1">D109-E109</f>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G109" s="16" t="s">
         <v>139</v>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="E110" s="35">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F110" s="37">
         <f ca="1">D110-E110</f>
-        <v>-2031</v>
+        <v>-2034</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>31</v>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956E0204-0911-4159-B5F5-3AA726E550DF}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F30C9610-B584-4B3C-8112-A199CDFEC0B2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1395,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
   <dimension ref="A1:O110"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -1414,7 +1414,7 @@
     <col min="15" max="15" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>14</v>
       </c>
@@ -1476,11 +1476,11 @@
       </c>
       <c r="E2" s="43">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F2" s="44">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>16</v>
@@ -1505,7 +1505,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>19</v>
       </c>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>21</v>
@@ -1549,7 +1549,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>22</v>
@@ -1593,7 +1593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>19</v>
       </c>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>23</v>
@@ -1637,7 +1637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>25</v>
       </c>
@@ -1652,11 +1652,11 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>26</v>
@@ -1681,7 +1681,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>25</v>
       </c>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>27</v>
       </c>
@@ -1733,25 +1733,25 @@
         <v>28</v>
       </c>
       <c r="C8" s="11">
-        <v>45999</v>
+        <v>46061</v>
       </c>
       <c r="D8" s="11">
-        <v>46061</v>
+        <v>46242</v>
       </c>
       <c r="E8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-169</v>
+        <v>11</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="17" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>17</v>
@@ -1769,7 +1769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>27</v>
       </c>
@@ -1784,11 +1784,11 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-406</v>
+        <v>-407</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>22</v>
@@ -1811,7 +1811,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>30</v>
       </c>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>31</v>
@@ -1853,7 +1853,7 @@
       <c r="N10" s="11"/>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>30</v>
       </c>
@@ -1868,11 +1868,11 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>32</v>
@@ -1897,7 +1897,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>33</v>
       </c>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>34</v>
@@ -1942,7 +1942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>37</v>
       </c>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>38</v>
@@ -1987,7 +1987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>40</v>
       </c>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>16</v>
@@ -2030,7 +2030,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>42</v>
       </c>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>26</v>
@@ -2075,7 +2075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>45</v>
       </c>
@@ -2090,11 +2090,11 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>46</v>
@@ -2118,7 +2118,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>48</v>
       </c>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F17" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>49</v>
@@ -2161,7 +2161,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>50</v>
       </c>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F18" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>16</v>
@@ -2204,7 +2204,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
         <v>52</v>
       </c>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F19" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>26</v>
@@ -2247,7 +2247,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>53</v>
       </c>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F20" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>16</v>
@@ -2290,7 +2290,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F21" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>31</v>
@@ -2334,7 +2334,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
@@ -2349,11 +2349,11 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F22" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>32</v>
@@ -2378,7 +2378,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>56</v>
       </c>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F23" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>38</v>
@@ -2422,7 +2422,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F24" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="G24" s="25" t="s">
         <v>59</v>
@@ -2468,7 +2468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>59</v>
@@ -2514,7 +2514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>58</v>
       </c>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="E26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F26" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>34</v>
@@ -2560,7 +2560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>61</v>
       </c>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F27" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>34</v>
@@ -2606,7 +2606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="9" customFormat="1">
+    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
         <v>62</v>
       </c>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="E28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F28" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>63</v>
@@ -2649,7 +2649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="9" customFormat="1">
+    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
         <v>62</v>
       </c>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="E29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F29" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>32</v>
@@ -2693,7 +2693,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>65</v>
       </c>
@@ -2708,11 +2708,11 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F30" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>66</v>
@@ -2737,7 +2737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>67</v>
       </c>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G31" s="25" t="s">
         <v>16</v>
@@ -2781,7 +2781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>68</v>
       </c>
@@ -2796,11 +2796,11 @@
       </c>
       <c r="E32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F32" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>31</v>
@@ -2825,7 +2825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
         <v>69</v>
       </c>
@@ -2840,11 +2840,11 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F33" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>22</v>
@@ -2869,7 +2869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
         <v>70</v>
       </c>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="E34" s="11">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F34" s="15">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>21</v>
@@ -2913,7 +2913,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
         <v>71</v>
       </c>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="E35" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F35" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
         <v>72</v>
       </c>
@@ -2972,11 +2972,11 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>73</v>
@@ -3000,7 +3000,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="30" t="s">
         <v>72</v>
       </c>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>75</v>
@@ -3043,7 +3043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="30" t="s">
         <v>76</v>
       </c>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>73</v>
@@ -3087,7 +3087,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
         <v>77</v>
       </c>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="E39" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>31</v>
@@ -3131,7 +3131,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="30" t="s">
         <v>77</v>
       </c>
@@ -3146,11 +3146,11 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>78</v>
@@ -3175,7 +3175,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>79</v>
       </c>
@@ -3190,11 +3190,11 @@
       </c>
       <c r="E41" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F41" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>80</v>
@@ -3218,7 +3218,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="30" t="s">
         <v>83</v>
       </c>
@@ -3233,11 +3233,11 @@
       </c>
       <c r="E42" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -3262,7 +3262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="30" t="s">
         <v>83</v>
       </c>
@@ -3277,11 +3277,11 @@
       </c>
       <c r="E43" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>32</v>
@@ -3306,7 +3306,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="9" customFormat="1">
+    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
         <v>84</v>
       </c>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="E44" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>85</v>
@@ -3350,7 +3350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="30" t="s">
         <v>86</v>
       </c>
@@ -3365,11 +3365,11 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F45" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>31</v>
@@ -3394,7 +3394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="30" t="s">
         <v>87</v>
       </c>
@@ -3409,11 +3409,11 @@
       </c>
       <c r="E46" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F46" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>16</v>
@@ -3438,7 +3438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
         <v>88</v>
       </c>
@@ -3453,11 +3453,11 @@
       </c>
       <c r="E47" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F47" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>21</v>
@@ -3482,7 +3482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="30" t="s">
         <v>89</v>
       </c>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F48" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>63</v>
@@ -3528,7 +3528,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
         <v>90</v>
       </c>
@@ -3543,11 +3543,11 @@
       </c>
       <c r="E49" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F49" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>63</v>
@@ -3572,7 +3572,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="30" t="s">
         <v>91</v>
       </c>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="E50" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F50" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>26</v>
@@ -3618,7 +3618,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
         <v>91</v>
       </c>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="E51" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F51" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>22</v>
@@ -3664,7 +3664,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="30" t="s">
         <v>91</v>
       </c>
@@ -3679,11 +3679,11 @@
       </c>
       <c r="E52" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F52" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>16</v>
@@ -3710,7 +3710,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="9" customFormat="1">
+    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="30" t="s">
         <v>93</v>
       </c>
@@ -3725,11 +3725,11 @@
       </c>
       <c r="E53" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F53" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>78</v>
@@ -3754,7 +3754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="9" customFormat="1">
+    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>94</v>
       </c>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="E54" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F54" s="15">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>95</v>
@@ -3798,7 +3798,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
         <v>97</v>
       </c>
@@ -3813,11 +3813,11 @@
       </c>
       <c r="E55" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>22</v>
@@ -3842,7 +3842,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
         <v>98</v>
       </c>
@@ -3857,11 +3857,11 @@
       </c>
       <c r="E56" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>99</v>
@@ -3886,7 +3886,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
         <v>98</v>
       </c>
@@ -3901,11 +3901,11 @@
       </c>
       <c r="E57" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>63</v>
@@ -3930,7 +3930,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
         <v>100</v>
       </c>
@@ -3945,11 +3945,11 @@
       </c>
       <c r="E58" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>31</v>
@@ -3974,7 +3974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="30" t="s">
         <v>101</v>
       </c>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="E59" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>34</v>
@@ -4017,7 +4017,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="30" t="s">
         <v>103</v>
       </c>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="E60" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>32</v>
@@ -4061,7 +4061,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="30" t="s">
         <v>104</v>
       </c>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E61" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-208</v>
+        <v>-209</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>66</v>
@@ -4105,7 +4105,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="30" t="s">
         <v>105</v>
       </c>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="E62" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>106</v>
@@ -4149,7 +4149,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="30" t="s">
         <v>107</v>
       </c>
@@ -4164,11 +4164,11 @@
       </c>
       <c r="E63" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>66</v>
@@ -4193,7 +4193,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="31" t="s">
         <v>107</v>
       </c>
@@ -4208,11 +4208,11 @@
       </c>
       <c r="E64" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F64" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>16</v>
@@ -4237,7 +4237,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="30" t="s">
         <v>108</v>
       </c>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="E65" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>63</v>
@@ -4280,7 +4280,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="30" t="s">
         <v>109</v>
       </c>
@@ -4295,11 +4295,11 @@
       </c>
       <c r="E66" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>31</v>
@@ -4324,7 +4324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="30" t="s">
         <v>109</v>
       </c>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="E67" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>63</v>
@@ -4368,7 +4368,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="9" customFormat="1">
+    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="30" t="s">
         <v>110</v>
       </c>
@@ -4383,11 +4383,11 @@
       </c>
       <c r="E68" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>32</v>
@@ -4412,7 +4412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="30" t="s">
         <v>111</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
         <v>111</v>
       </c>
@@ -4450,11 +4450,11 @@
       </c>
       <c r="E70" s="13">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F70" s="24">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G70" s="25" t="s">
         <v>22</v>
@@ -4477,7 +4477,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
         <v>112</v>
       </c>
@@ -4492,11 +4492,11 @@
       </c>
       <c r="E71" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>34</v>
@@ -4522,7 +4522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
         <v>115</v>
       </c>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="E72" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>66</v>
@@ -4564,7 +4564,7 @@
       <c r="N72" s="12"/>
       <c r="O72" s="29"/>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
         <v>115</v>
       </c>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="E73" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>22</v>
@@ -4608,7 +4608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="9" customFormat="1">
+    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="31" t="s">
         <v>115</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="N74" s="13"/>
       <c r="O74" s="32"/>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
         <v>118</v>
       </c>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E75" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F75" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>32</v>
@@ -4683,7 +4683,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="30" t="s">
         <v>118</v>
       </c>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="E76" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F76" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>85</v>
@@ -4729,7 +4729,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="30" t="s">
         <v>120</v>
       </c>
@@ -4744,11 +4744,11 @@
       </c>
       <c r="E77" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F77" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>23</v>
@@ -4775,7 +4775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="30" t="s">
         <v>122</v>
       </c>
@@ -4790,11 +4790,11 @@
       </c>
       <c r="E78" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F78" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>95</v>
@@ -4820,7 +4820,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="30" t="s">
         <v>125</v>
       </c>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="E79" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F79" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>34</v>
@@ -4864,7 +4864,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="30" t="s">
         <v>127</v>
       </c>
@@ -4879,11 +4879,11 @@
       </c>
       <c r="E80" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F80" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>66</v>
@@ -4908,7 +4908,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="30" t="s">
         <v>127</v>
       </c>
@@ -4923,11 +4923,11 @@
       </c>
       <c r="E81" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F81" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>26</v>
@@ -4952,7 +4952,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="30" t="s">
         <v>127</v>
       </c>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="E82" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F82" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>26</v>
@@ -4996,7 +4996,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="30" t="s">
         <v>128</v>
       </c>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="E83" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F83" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>22</v>
@@ -5040,7 +5040,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="30" t="s">
         <v>128</v>
       </c>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="E84" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F84" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>16</v>
@@ -5084,7 +5084,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="30" t="s">
         <v>129</v>
       </c>
@@ -5099,11 +5099,11 @@
       </c>
       <c r="E85" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F85" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>75</v>
@@ -5125,7 +5125,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="30" t="s">
         <v>129</v>
       </c>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="E86" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F86" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>34</v>
@@ -5168,7 +5168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="30" t="s">
         <v>129</v>
       </c>
@@ -5183,11 +5183,11 @@
       </c>
       <c r="E87" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F87" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>73</v>
@@ -5211,7 +5211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="30" t="s">
         <v>133</v>
       </c>
@@ -5226,11 +5226,11 @@
       </c>
       <c r="E88" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F88" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>21</v>
@@ -5253,7 +5253,7 @@
       <c r="N88" s="12"/>
       <c r="O88" s="29"/>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="30" t="s">
         <v>134</v>
       </c>
@@ -5268,11 +5268,11 @@
       </c>
       <c r="E89" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F89" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>31</v>
@@ -5297,7 +5297,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
         <v>135</v>
       </c>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="E90" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F90" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>106</v>
@@ -5338,7 +5338,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="30" t="s">
         <v>137</v>
       </c>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="E91" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F91" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>22</v>
@@ -5382,7 +5382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="30" t="s">
         <v>137</v>
       </c>
@@ -5397,11 +5397,11 @@
       </c>
       <c r="E92" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F92" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>16</v>
@@ -5424,7 +5424,7 @@
       <c r="N92" s="12"/>
       <c r="O92" s="29"/>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="30" t="s">
         <v>138</v>
       </c>
@@ -5439,11 +5439,11 @@
       </c>
       <c r="E93" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F93" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>139</v>
@@ -5468,7 +5468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="31" t="s">
         <v>140</v>
       </c>
@@ -5483,11 +5483,11 @@
       </c>
       <c r="E94" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F94" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>26</v>
@@ -5514,7 +5514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="31" t="s">
         <v>140</v>
       </c>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="E95" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F95" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>16</v>
@@ -5560,7 +5560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="30" t="s">
         <v>141</v>
       </c>
@@ -5575,11 +5575,11 @@
       </c>
       <c r="E96" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>31</v>
@@ -5604,7 +5604,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="9" customFormat="1">
+    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="31" t="s">
         <v>142</v>
       </c>
@@ -5619,11 +5619,11 @@
       </c>
       <c r="E97" s="13">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F97" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>32</v>
@@ -5648,7 +5648,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.25" customHeight="1">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="30" t="s">
         <v>143</v>
       </c>
@@ -5663,11 +5663,11 @@
       </c>
       <c r="E98" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>21</v>
@@ -5692,7 +5692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="30" t="s">
         <v>144</v>
       </c>
@@ -5707,11 +5707,11 @@
       </c>
       <c r="E99" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>85</v>
@@ -5736,7 +5736,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="30" t="s">
         <v>145</v>
       </c>
@@ -5751,11 +5751,11 @@
       </c>
       <c r="E100" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>31</v>
@@ -5780,7 +5780,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="30" t="s">
         <v>146</v>
       </c>
@@ -5795,11 +5795,11 @@
       </c>
       <c r="E101" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G101" s="16" t="s">
         <v>106</v>
@@ -5824,7 +5824,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="30" t="s">
         <v>147</v>
       </c>
@@ -5839,11 +5839,11 @@
       </c>
       <c r="E102" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G102" s="16" t="s">
         <v>106</v>
@@ -5868,7 +5868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="30" t="s">
         <v>149</v>
       </c>
@@ -5883,11 +5883,11 @@
       </c>
       <c r="E103" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>16</v>
@@ -5912,7 +5912,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="9" customFormat="1">
+    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="30" t="s">
         <v>150</v>
       </c>
@@ -5927,11 +5927,11 @@
       </c>
       <c r="E104" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>151</v>
@@ -5956,7 +5956,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="30" t="s">
         <v>152</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="30" t="s">
         <v>153</v>
       </c>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="E106" s="12">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F106" s="15">
         <f ca="1">D106-E106</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>38</v>
@@ -6023,7 +6023,7 @@
       <c r="N106" s="12"/>
       <c r="O106" s="29"/>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="30" t="s">
         <v>153</v>
       </c>
@@ -6038,11 +6038,11 @@
       </c>
       <c r="E107" s="12">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F107" s="15">
         <f ca="1">D107-E107</f>
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>29</v>
@@ -6067,7 +6067,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="30" t="s">
         <v>154</v>
       </c>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="E108" s="12">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F108" s="15">
         <f ca="1">D108-E108</f>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>34</v>
@@ -6111,7 +6111,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="30" t="s">
         <v>155</v>
       </c>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="E109" s="12">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F109" s="15">
         <f ca="1">D109-E109</f>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G109" s="16" t="s">
         <v>139</v>
@@ -6155,7 +6155,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15" thickBot="1">
+    <row r="110" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>155</v>
       </c>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="E110" s="35">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F110" s="37">
         <f ca="1">D110-E110</f>
-        <v>-2034</v>
+        <v>-2035</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>31</v>
@@ -6212,7 +6212,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -6230,7 +6230,7 @@
     <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>161</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>166</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>168</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>170</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>171</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>172</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>174</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>175</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>176</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>177</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>178</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>179</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>181</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>182</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>184</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>185</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>186</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>187</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>189</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>191</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>192</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>193</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>194</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>196</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>197</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>110</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>198</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>199</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>200</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>202</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>203</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>204</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>205</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>205</v>
       </c>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F30C9610-B584-4B3C-8112-A199CDFEC0B2}"/>
+  <xr:revisionPtr revIDLastSave="497" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC272EF4-9DFF-47F7-9B60-DAA69C8007BE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -1395,26 +1395,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
   <dimension ref="A1:O110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.26953125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="41" t="s">
         <v>14</v>
       </c>
@@ -1476,11 +1476,11 @@
       </c>
       <c r="E2" s="43">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F2" s="44">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>16</v>
@@ -1505,7 +1505,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
         <v>19</v>
       </c>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>21</v>
@@ -1549,7 +1549,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>22</v>
@@ -1593,7 +1593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>19</v>
       </c>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>23</v>
@@ -1637,7 +1637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>25</v>
       </c>
@@ -1652,11 +1652,11 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>26</v>
@@ -1681,7 +1681,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>25</v>
       </c>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>23</v>
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
         <v>27</v>
       </c>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>29</v>
@@ -1769,7 +1769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
         <v>27</v>
       </c>
@@ -1784,11 +1784,11 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-407</v>
+        <v>-408</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>22</v>
@@ -1811,7 +1811,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
         <v>30</v>
       </c>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>31</v>
@@ -1853,7 +1853,7 @@
       <c r="N10" s="11"/>
       <c r="O10" s="29"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="s">
         <v>30</v>
       </c>
@@ -1868,11 +1868,11 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>32</v>
@@ -1897,7 +1897,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="30" t="s">
         <v>33</v>
       </c>
@@ -1912,11 +1912,11 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>34</v>
@@ -1942,7 +1942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
         <v>37</v>
       </c>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>38</v>
@@ -1987,7 +1987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
         <v>40</v>
       </c>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>16</v>
@@ -2030,7 +2030,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="30" t="s">
         <v>42</v>
       </c>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>26</v>
@@ -2075,7 +2075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
         <v>45</v>
       </c>
@@ -2090,11 +2090,11 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>46</v>
@@ -2118,7 +2118,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="30" t="s">
         <v>48</v>
       </c>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F17" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>49</v>
@@ -2161,7 +2161,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="30" t="s">
         <v>50</v>
       </c>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F18" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>16</v>
@@ -2204,7 +2204,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="30" t="s">
         <v>52</v>
       </c>
@@ -2215,21 +2215,21 @@
         <v>42564</v>
       </c>
       <c r="D19" s="12">
-        <v>51501</v>
+        <v>46022</v>
       </c>
       <c r="E19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F19" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>-210</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>17</v>
@@ -2247,7 +2247,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="s">
         <v>53</v>
       </c>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F20" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>16</v>
@@ -2290,7 +2290,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F21" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>31</v>
@@ -2334,7 +2334,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
@@ -2349,11 +2349,11 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F22" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>32</v>
@@ -2378,7 +2378,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
         <v>56</v>
       </c>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F23" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>38</v>
@@ -2422,7 +2422,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F24" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G24" s="25" t="s">
         <v>59</v>
@@ -2468,7 +2468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>59</v>
@@ -2514,7 +2514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="30" t="s">
         <v>58</v>
       </c>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="E26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F26" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>34</v>
@@ -2560,7 +2560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="30" t="s">
         <v>61</v>
       </c>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F27" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>34</v>
@@ -2606,7 +2606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
         <v>62</v>
       </c>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="E28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F28" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>63</v>
@@ -2649,7 +2649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="30" t="s">
         <v>62</v>
       </c>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="E29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F29" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>32</v>
@@ -2693,7 +2693,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="30" t="s">
         <v>65</v>
       </c>
@@ -2708,11 +2708,11 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F30" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>66</v>
@@ -2737,7 +2737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="31" t="s">
         <v>67</v>
       </c>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G31" s="25" t="s">
         <v>16</v>
@@ -2781,7 +2781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="30" t="s">
         <v>68</v>
       </c>
@@ -2796,11 +2796,11 @@
       </c>
       <c r="E32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F32" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>31</v>
@@ -2825,7 +2825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
         <v>69</v>
       </c>
@@ -2840,11 +2840,11 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F33" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>22</v>
@@ -2869,7 +2869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="30" t="s">
         <v>70</v>
       </c>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="E34" s="11">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F34" s="15">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>21</v>
@@ -2913,7 +2913,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="30" t="s">
         <v>71</v>
       </c>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="E35" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F35" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="s">
         <v>72</v>
       </c>
@@ -2972,11 +2972,11 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>73</v>
@@ -3000,7 +3000,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="30" t="s">
         <v>72</v>
       </c>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>75</v>
@@ -3043,7 +3043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="30" t="s">
         <v>76</v>
       </c>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>73</v>
@@ -3087,7 +3087,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="30" t="s">
         <v>77</v>
       </c>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="E39" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>31</v>
@@ -3131,7 +3131,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="s">
         <v>77</v>
       </c>
@@ -3146,11 +3146,11 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F40" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>78</v>
@@ -3175,7 +3175,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="31" t="s">
         <v>79</v>
       </c>
@@ -3190,11 +3190,11 @@
       </c>
       <c r="E41" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F41" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>80</v>
@@ -3218,7 +3218,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="30" t="s">
         <v>83</v>
       </c>
@@ -3233,11 +3233,11 @@
       </c>
       <c r="E42" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F42" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -3262,7 +3262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="30" t="s">
         <v>83</v>
       </c>
@@ -3277,11 +3277,11 @@
       </c>
       <c r="E43" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F43" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>32</v>
@@ -3306,7 +3306,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="s">
         <v>84</v>
       </c>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="E44" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F44" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>85</v>
@@ -3350,7 +3350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="30" t="s">
         <v>86</v>
       </c>
@@ -3365,11 +3365,11 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F45" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>31</v>
@@ -3394,7 +3394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="30" t="s">
         <v>87</v>
       </c>
@@ -3409,11 +3409,11 @@
       </c>
       <c r="E46" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F46" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>16</v>
@@ -3438,7 +3438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="s">
         <v>88</v>
       </c>
@@ -3453,11 +3453,11 @@
       </c>
       <c r="E47" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F47" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>21</v>
@@ -3482,7 +3482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="30" t="s">
         <v>89</v>
       </c>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F48" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>63</v>
@@ -3528,7 +3528,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="30" t="s">
         <v>90</v>
       </c>
@@ -3543,11 +3543,11 @@
       </c>
       <c r="E49" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F49" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>63</v>
@@ -3572,7 +3572,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="30" t="s">
         <v>91</v>
       </c>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="E50" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F50" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>26</v>
@@ -3618,7 +3618,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="30" t="s">
         <v>91</v>
       </c>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="E51" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F51" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>22</v>
@@ -3664,7 +3664,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="30" t="s">
         <v>91</v>
       </c>
@@ -3679,11 +3679,11 @@
       </c>
       <c r="E52" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F52" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>16</v>
@@ -3710,7 +3710,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="s">
         <v>93</v>
       </c>
@@ -3725,11 +3725,11 @@
       </c>
       <c r="E53" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F53" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>78</v>
@@ -3754,7 +3754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="s">
         <v>94</v>
       </c>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="E54" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F54" s="15">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>95</v>
@@ -3798,7 +3798,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="30" t="s">
         <v>97</v>
       </c>
@@ -3813,11 +3813,11 @@
       </c>
       <c r="E55" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>22</v>
@@ -3842,7 +3842,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="s">
         <v>98</v>
       </c>
@@ -3857,11 +3857,11 @@
       </c>
       <c r="E56" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>99</v>
@@ -3886,7 +3886,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="s">
         <v>98</v>
       </c>
@@ -3901,11 +3901,11 @@
       </c>
       <c r="E57" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>63</v>
@@ -3930,7 +3930,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="s">
         <v>100</v>
       </c>
@@ -3945,11 +3945,11 @@
       </c>
       <c r="E58" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>31</v>
@@ -3974,7 +3974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="30" t="s">
         <v>101</v>
       </c>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="E59" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>34</v>
@@ -4017,7 +4017,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="30" t="s">
         <v>103</v>
       </c>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="E60" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>32</v>
@@ -4061,7 +4061,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="30" t="s">
         <v>104</v>
       </c>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="E61" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>66</v>
@@ -4105,7 +4105,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="30" t="s">
         <v>105</v>
       </c>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="E62" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>106</v>
@@ -4149,7 +4149,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="s">
         <v>107</v>
       </c>
@@ -4164,11 +4164,11 @@
       </c>
       <c r="E63" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>66</v>
@@ -4193,7 +4193,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="31" t="s">
         <v>107</v>
       </c>
@@ -4208,11 +4208,11 @@
       </c>
       <c r="E64" s="23">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F64" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>16</v>
@@ -4237,7 +4237,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="30" t="s">
         <v>108</v>
       </c>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="E65" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>63</v>
@@ -4280,7 +4280,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="30" t="s">
         <v>109</v>
       </c>
@@ -4295,11 +4295,11 @@
       </c>
       <c r="E66" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>31</v>
@@ -4324,7 +4324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="30" t="s">
         <v>109</v>
       </c>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="E67" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>63</v>
@@ -4368,7 +4368,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="30" t="s">
         <v>110</v>
       </c>
@@ -4383,11 +4383,11 @@
       </c>
       <c r="E68" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" ca="1" si="9"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>32</v>
@@ -4412,7 +4412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="30" t="s">
         <v>111</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="31" t="s">
         <v>111</v>
       </c>
@@ -4450,11 +4450,11 @@
       </c>
       <c r="E70" s="13">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F70" s="24">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G70" s="25" t="s">
         <v>22</v>
@@ -4477,7 +4477,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="30" t="s">
         <v>112</v>
       </c>
@@ -4492,11 +4492,11 @@
       </c>
       <c r="E71" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>34</v>
@@ -4522,7 +4522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="30" t="s">
         <v>115</v>
       </c>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="E72" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>66</v>
@@ -4564,7 +4564,7 @@
       <c r="N72" s="12"/>
       <c r="O72" s="29"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="30" t="s">
         <v>115</v>
       </c>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="E73" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>22</v>
@@ -4608,7 +4608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="31" t="s">
         <v>115</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="N74" s="13"/>
       <c r="O74" s="32"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="s">
         <v>118</v>
       </c>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E75" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F75" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>32</v>
@@ -4683,7 +4683,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="30" t="s">
         <v>118</v>
       </c>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="E76" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F76" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>85</v>
@@ -4729,7 +4729,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="30" t="s">
         <v>120</v>
       </c>
@@ -4744,11 +4744,11 @@
       </c>
       <c r="E77" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F77" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>23</v>
@@ -4775,7 +4775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="30" t="s">
         <v>122</v>
       </c>
@@ -4790,11 +4790,11 @@
       </c>
       <c r="E78" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F78" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>95</v>
@@ -4820,7 +4820,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="30" t="s">
         <v>125</v>
       </c>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="E79" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F79" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>34</v>
@@ -4864,7 +4864,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="30" t="s">
         <v>127</v>
       </c>
@@ -4879,11 +4879,11 @@
       </c>
       <c r="E80" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F80" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>66</v>
@@ -4908,7 +4908,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="30" t="s">
         <v>127</v>
       </c>
@@ -4923,11 +4923,11 @@
       </c>
       <c r="E81" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F81" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>26</v>
@@ -4952,7 +4952,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="30" t="s">
         <v>127</v>
       </c>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="E82" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F82" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>26</v>
@@ -4996,7 +4996,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="30" t="s">
         <v>128</v>
       </c>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="E83" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F83" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>22</v>
@@ -5040,7 +5040,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="30" t="s">
         <v>128</v>
       </c>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="E84" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F84" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>16</v>
@@ -5084,7 +5084,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="30" t="s">
         <v>129</v>
       </c>
@@ -5099,11 +5099,11 @@
       </c>
       <c r="E85" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F85" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>75</v>
@@ -5125,7 +5125,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="30" t="s">
         <v>129</v>
       </c>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="E86" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F86" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>34</v>
@@ -5168,7 +5168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="30" t="s">
         <v>129</v>
       </c>
@@ -5183,11 +5183,11 @@
       </c>
       <c r="E87" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F87" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>73</v>
@@ -5211,7 +5211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="30" t="s">
         <v>133</v>
       </c>
@@ -5226,11 +5226,11 @@
       </c>
       <c r="E88" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F88" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>21</v>
@@ -5253,7 +5253,7 @@
       <c r="N88" s="12"/>
       <c r="O88" s="29"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="30" t="s">
         <v>134</v>
       </c>
@@ -5268,11 +5268,11 @@
       </c>
       <c r="E89" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F89" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>31</v>
@@ -5297,7 +5297,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="30" t="s">
         <v>135</v>
       </c>
@@ -5312,11 +5312,11 @@
       </c>
       <c r="E90" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F90" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>106</v>
@@ -5338,7 +5338,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="30" t="s">
         <v>137</v>
       </c>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="E91" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F91" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>22</v>
@@ -5382,7 +5382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="30" t="s">
         <v>137</v>
       </c>
@@ -5397,11 +5397,11 @@
       </c>
       <c r="E92" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F92" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>16</v>
@@ -5424,7 +5424,7 @@
       <c r="N92" s="12"/>
       <c r="O92" s="29"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="30" t="s">
         <v>138</v>
       </c>
@@ -5439,11 +5439,11 @@
       </c>
       <c r="E93" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F93" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>139</v>
@@ -5468,7 +5468,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="31" t="s">
         <v>140</v>
       </c>
@@ -5483,11 +5483,11 @@
       </c>
       <c r="E94" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F94" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>26</v>
@@ -5514,7 +5514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="31" t="s">
         <v>140</v>
       </c>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="E95" s="23">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F95" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>16</v>
@@ -5560,7 +5560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="30" t="s">
         <v>141</v>
       </c>
@@ -5575,11 +5575,11 @@
       </c>
       <c r="E96" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>31</v>
@@ -5604,7 +5604,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="31" t="s">
         <v>142</v>
       </c>
@@ -5619,11 +5619,11 @@
       </c>
       <c r="E97" s="13">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F97" s="24">
         <f t="shared" ca="1" si="11"/>
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G97" s="25" t="s">
         <v>32</v>
@@ -5648,7 +5648,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="30" t="s">
         <v>143</v>
       </c>
@@ -5663,11 +5663,11 @@
       </c>
       <c r="E98" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>21</v>
@@ -5692,7 +5692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="30" t="s">
         <v>144</v>
       </c>
@@ -5707,11 +5707,11 @@
       </c>
       <c r="E99" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>85</v>
@@ -5736,7 +5736,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="30" t="s">
         <v>145</v>
       </c>
@@ -5751,11 +5751,11 @@
       </c>
       <c r="E100" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>31</v>
@@ -5780,7 +5780,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="30" t="s">
         <v>146</v>
       </c>
@@ -5795,11 +5795,11 @@
       </c>
       <c r="E101" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G101" s="16" t="s">
         <v>106</v>
@@ -5824,7 +5824,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="30" t="s">
         <v>147</v>
       </c>
@@ -5839,11 +5839,11 @@
       </c>
       <c r="E102" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G102" s="16" t="s">
         <v>106</v>
@@ -5868,7 +5868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="30" t="s">
         <v>149</v>
       </c>
@@ -5883,11 +5883,11 @@
       </c>
       <c r="E103" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>16</v>
@@ -5912,7 +5912,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="30" t="s">
         <v>150</v>
       </c>
@@ -5927,11 +5927,11 @@
       </c>
       <c r="E104" s="12">
         <f t="shared" ca="1" si="10"/>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" ca="1" si="11"/>
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>151</v>
@@ -5956,7 +5956,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="30" t="s">
         <v>152</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="30" t="s">
         <v>153</v>
       </c>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="E106" s="12">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F106" s="15">
         <f ca="1">D106-E106</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>38</v>
@@ -6023,7 +6023,7 @@
       <c r="N106" s="12"/>
       <c r="O106" s="29"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="30" t="s">
         <v>153</v>
       </c>
@@ -6038,11 +6038,11 @@
       </c>
       <c r="E107" s="12">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F107" s="15">
         <f ca="1">D107-E107</f>
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>29</v>
@@ -6067,7 +6067,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="30" t="s">
         <v>154</v>
       </c>
@@ -6082,11 +6082,11 @@
       </c>
       <c r="E108" s="12">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F108" s="15">
         <f ca="1">D108-E108</f>
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>34</v>
@@ -6111,7 +6111,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="30" t="s">
         <v>155</v>
       </c>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="E109" s="12">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F109" s="15">
         <f ca="1">D109-E109</f>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G109" s="16" t="s">
         <v>139</v>
@@ -6155,7 +6155,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="33" t="s">
         <v>155</v>
       </c>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="E110" s="35">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F110" s="37">
         <f ca="1">D110-E110</f>
-        <v>-2035</v>
+        <v>-2036</v>
       </c>
       <c r="G110" s="38" t="s">
         <v>31</v>
@@ -6212,25 +6212,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0B4294-6308-408D-A7E0-6148B7D61ACB}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>161</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>166</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>168</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>170</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>171</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>172</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>174</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>175</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>176</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>177</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>178</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>179</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>181</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>182</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>184</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>185</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>186</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>187</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>189</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>191</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>192</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>193</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>194</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>196</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>197</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>110</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>198</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>199</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>200</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>202</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>203</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>204</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>205</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>205</v>
       </c>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="497" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC272EF4-9DFF-47F7-9B60-DAA69C8007BE}"/>
+  <xr:revisionPtr revIDLastSave="500" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FDB390-5F37-4771-8021-65F5BC8C77A7}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
@@ -3054,7 +3054,7 @@
         <v>45661</v>
       </c>
       <c r="D38" s="12">
-        <v>46206</v>
+        <v>46234</v>
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="F38" s="15">
         <f t="shared" ca="1" si="5"/>
-        <v>-26</v>
+        <v>2</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>73</v>
       </c>
       <c r="H38" s="18" t="str">
         <f ca="1">IF(F38&lt;=0, "VENDA","CAREPACK")</f>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>17</v>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="500" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FDB390-5F37-4771-8021-65F5BC8C77A7}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AE2008C-C62A-47A0-93AE-71B451950982}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
     <sheet name="SÉRIE2" sheetId="3" r:id="rId2"/>
+    <sheet name="COBRANÇAS" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$N$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BASE!$A$1:$N$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SÉRIE2!$A$1:$N$38</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="221">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -499,9 +500,6 @@
     <t>HP INDIGO 200K</t>
   </si>
   <si>
-    <t>VITAFOR</t>
-  </si>
-  <si>
     <t>VR LABEL</t>
   </si>
   <si>
@@ -659,6 +657,54 @@
   </si>
   <si>
     <t>ULTRAPRESS EDITORA E GRAFICA</t>
+  </si>
+  <si>
+    <t>15 HRS MENSAIS. EXTRATO MENSAL. FECHAMENTO TRIMESTRAL</t>
+  </si>
+  <si>
+    <t>OBS: LASER/CILINDROS E CORONA ENVIAR ORÇAMETO DE VENDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR </t>
+  </si>
+  <si>
+    <t>DATA FAT.</t>
+  </si>
+  <si>
+    <t>JULHO</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SETEMBRO</t>
+  </si>
+  <si>
+    <t>OUTUBRO</t>
+  </si>
+  <si>
+    <t>NOVEMBRO</t>
+  </si>
+  <si>
+    <t>FEVEREIRO</t>
+  </si>
+  <si>
+    <t>MARÇO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAIO</t>
+  </si>
+  <si>
+    <t>JUNHO</t>
+  </si>
+  <si>
+    <t>DEZEMBRO</t>
+  </si>
+  <si>
+    <t>JANEIRO</t>
   </si>
 </sst>
 </file>
@@ -669,7 +715,7 @@
     <numFmt numFmtId="164" formatCode="#,###,###,##0.00###"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,8 +751,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -725,8 +787,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -906,11 +974,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -936,12 +1019,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -949,22 +1028,10 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -976,25 +1043,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1003,22 +1055,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1027,31 +1067,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1059,6 +1078,78 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1394,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -1403,9 +1494,9 @@
     <col min="4" max="4" width="10" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.26953125" style="7" customWidth="1"/>
     <col min="10" max="10" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="35.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -1415,1350 +1506,1352 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="50" t="s">
+      <c r="M1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="50" t="s">
+      <c r="N1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="42">
         <v>46046</v>
       </c>
-      <c r="D2" s="43">
-        <v>46234</v>
-      </c>
-      <c r="E2" s="43">
+      <c r="D2" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E2" s="42">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F2" s="44">
+        <v>46234</v>
+      </c>
+      <c r="F2" s="25">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>2</v>
-      </c>
-      <c r="G2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="46" t="str">
+      <c r="H2" s="26" t="str">
         <f t="shared" ref="H2:H11" ca="1" si="2">IF(F2&lt;=0,"VENDA","CAREPACK")</f>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I2" s="47" t="s">
+        <v>VENDA</v>
+      </c>
+      <c r="I2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="43">
+      <c r="K2" s="42">
         <v>45315</v>
       </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="48">
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="43">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="19" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>45717</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>51501</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F3" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G3" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="17" t="str">
+      <c r="H3" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <v>40368</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="29">
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="19" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>45292</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>51501</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F4" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G4" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="17" t="str">
+      <c r="H4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>43627</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="29">
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="19" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>45627</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>51501</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F5" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G5" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="17" t="str">
+      <c r="H5" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>45385</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="29">
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="19" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>45962</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>46265</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F6" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="17" t="str">
+      <c r="H6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>42118</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="29">
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="19" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>45992</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>46265</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F7" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <v>42755</v>
       </c>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="29">
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>46061</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>46242</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F8" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="17" t="str">
+      <c r="H8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <v>45965</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="29">
+      <c r="L8" s="31"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>45999</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>45824</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F9" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-408</v>
-      </c>
-      <c r="G9" s="16" t="s">
+        <v>-410</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="17" t="str">
+      <c r="H9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="29">
+      <c r="K9" s="10"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="19" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>45670</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>44196</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F10" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G10" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="17" t="str">
+      <c r="H10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="10">
         <v>45670</v>
       </c>
-      <c r="L10" s="19"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="29"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="44">
+        <v>90</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="19" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="10">
         <v>44909</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>44196</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F11" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G11" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="17" t="str">
+      <c r="H11" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>VENDA</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="10">
         <v>43581</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="29">
+      <c r="L11" s="31"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="10">
         <v>45992</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="10">
         <v>46356</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F12" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F12" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>124</v>
-      </c>
-      <c r="G12" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="10">
         <v>43224</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="29">
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="10">
         <v>45566</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="10">
         <v>46326</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F13" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="G13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="10">
         <v>45149</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="29">
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>45890</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>46619</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F14" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>387</v>
-      </c>
-      <c r="G14" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="10">
         <v>45890</v>
       </c>
-      <c r="L14" s="19"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="29">
+      <c r="L14" s="31"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <v>45962</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="10">
         <v>51501</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F15" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G15" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="10">
         <v>41969</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="29">
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="10">
         <v>46082</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>46446</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F16" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>214</v>
-      </c>
-      <c r="G16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="10">
         <v>42353</v>
       </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="29">
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="10">
         <v>46082</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="10">
         <v>46446</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F17" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>214</v>
-      </c>
-      <c r="G17" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="10">
         <v>45524</v>
       </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="29">
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="10">
         <v>45950</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>46863</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F18" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>631</v>
-      </c>
-      <c r="G18" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="18" t="s">
+      <c r="I18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="10">
         <v>45950</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="29">
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="19" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="10">
         <v>42564</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="10">
         <v>46022</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F19" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-210</v>
-      </c>
-      <c r="G19" s="16" t="s">
+        <v>-212</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="I19" s="18" t="s">
+      <c r="H19" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="10">
         <v>42198</v>
       </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="29">
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="10">
         <v>46028</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="10">
         <v>51501</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F20" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G20" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="10">
         <v>45602</v>
       </c>
-      <c r="L20" s="21"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="29">
+      <c r="L20" s="15"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="19" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10">
         <v>44911</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>44196</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F21" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G21" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="18" t="str">
+      <c r="H21" s="13" t="str">
         <f t="shared" ref="H21:H27" ca="1" si="3">IF(F21&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="10">
         <v>40801</v>
       </c>
-      <c r="L21" s="21"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="29">
+      <c r="L21" s="15"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="19" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="10">
         <v>45352</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>44196</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F22" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G22" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="18" t="str">
+      <c r="H22" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="10">
         <v>44089</v>
       </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="29">
+      <c r="L22" s="15"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="12">
-        <v>45444</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="C23" s="10">
+        <v>46235</v>
+      </c>
+      <c r="D23" s="10">
+        <v>46599</v>
+      </c>
+      <c r="E23" s="10">
+        <f t="shared" ca="1" si="0"/>
+        <v>46234</v>
+      </c>
+      <c r="F23" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>365</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="13" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="10">
+        <v>45261</v>
+      </c>
+      <c r="L23" s="15"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="11">
+        <v>45962</v>
+      </c>
+      <c r="D24" s="11">
         <v>46203</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F23" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F24" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-29</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="18" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>VENDA</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="12">
-        <v>45261</v>
-      </c>
-      <c r="L23" s="21"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="13">
-        <v>45962</v>
-      </c>
-      <c r="D24" s="12">
-        <v>46203</v>
-      </c>
-      <c r="E24" s="23">
-        <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F24" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>-29</v>
-      </c>
-      <c r="G24" s="25" t="s">
+        <v>-31</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>59</v>
       </c>
       <c r="H24" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I24" s="26" t="s">
+      <c r="I24" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="J24" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="11">
         <v>41290</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="29">
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="11">
         <v>45962</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <v>46203</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F25" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F25" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-29</v>
-      </c>
-      <c r="G25" s="25" t="s">
+        <v>-31</v>
+      </c>
+      <c r="G25" s="17" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I25" s="26" t="s">
+      <c r="I25" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J25" s="24" t="s">
+      <c r="J25" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="11">
         <v>42989</v>
       </c>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="29">
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="19" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="10">
         <v>45383</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>44196</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F26" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G26" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="18" t="str">
+      <c r="H26" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="10">
         <v>43186</v>
       </c>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="29">
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="10">
         <v>45992</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="10">
         <v>46477</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F27" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
-      </c>
-      <c r="G27" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="18" t="str">
+      <c r="H27" s="13" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="10">
         <v>43923</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="35">
         <v>45689</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="35">
         <v>51501</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F28" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F28" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>5269</v>
-      </c>
-      <c r="G28" s="16" t="s">
+        <v>5267</v>
+      </c>
+      <c r="G28" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="35">
         <v>42347</v>
       </c>
-      <c r="L28" s="21"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="32">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="30" t="s">
+      <c r="L28" s="38"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="46">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="35">
         <v>43891</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="35">
         <v>44196</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F29" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F29" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G29" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G29" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="18" t="str">
+      <c r="H29" s="37" t="str">
         <f ca="1">IF(F29&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I29" s="18" t="s">
+      <c r="I29" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="35">
         <v>43283</v>
       </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="32">
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="19" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="10">
         <v>45925</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>44196</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F30" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G30" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="18" t="str">
+      <c r="H30" s="13" t="str">
         <f ca="1">IF(F30&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="I30" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="10">
         <v>45925</v>
       </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="29">
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="11">
         <v>45928</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="11">
         <v>46473</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F31" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F31" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>241</v>
-      </c>
-      <c r="G31" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="18" t="str">
@@ -2768,303 +2861,303 @@
       <c r="I31" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="24" t="s">
+      <c r="J31" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="13">
+      <c r="K31" s="11">
         <v>45744</v>
       </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="29">
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="10">
         <v>45139</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <v>44196</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F32" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G32" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="18" t="str">
+      <c r="H32" s="13" t="str">
         <f ca="1">IF(F32&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I32" s="18" t="s">
+      <c r="I32" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="10">
         <v>40892</v>
       </c>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="29">
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>45017</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>44196</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F33" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2036</v>
-      </c>
-      <c r="G33" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="17" t="str">
+      <c r="H33" s="13" t="str">
         <f ca="1">IF(F33&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K33" s="11">
+      <c r="K33" s="10">
         <v>44682</v>
       </c>
-      <c r="L33" s="19"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="29">
+      <c r="L33" s="31"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="19" t="s">
         <v>70</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="10">
         <v>44165</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>44196</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F34" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F34" s="12">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2036</v>
-      </c>
-      <c r="G34" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H34" s="18" t="str">
+      <c r="H34" s="13" t="str">
         <f ca="1">IF(F34&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I34" s="18" t="s">
+      <c r="I34" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="J34" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="10">
         <v>40736</v>
       </c>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="29">
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="10">
         <v>45896</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="10">
         <v>46625</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F35" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F35" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>393</v>
-      </c>
-      <c r="G35" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="18" t="str">
+      <c r="H35" s="13" t="str">
         <f ca="1">IF(F35&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I35" s="18" t="s">
+      <c r="I35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="10">
         <v>45714</v>
       </c>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="30" t="s">
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="35">
         <v>45870</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="35">
         <v>46477</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="35">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F36" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F36" s="36">
         <f t="shared" ca="1" si="5"/>
-        <v>245</v>
-      </c>
-      <c r="G36" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G36" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H36" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="18" t="s">
+      <c r="I36" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="J36" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="35">
         <v>44896</v>
       </c>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="32">
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="10">
         <v>46090</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="10">
         <v>46455</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F37" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F37" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>223</v>
-      </c>
-      <c r="G37" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I37" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="10">
         <v>46455</v>
       </c>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="30" t="s">
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="12">
-        <v>45661</v>
-      </c>
-      <c r="D38" s="12">
-        <v>46234</v>
+      <c r="C38" s="11">
+        <v>46235</v>
+      </c>
+      <c r="D38" s="11">
+        <v>46599</v>
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F38" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F38" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="G38" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="G38" s="17" t="s">
         <v>73</v>
       </c>
       <c r="H38" s="18" t="str">
@@ -3072,1149 +3165,1149 @@
         <v>CAREPACK</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="J38" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="11">
         <v>45477</v>
       </c>
-      <c r="L38" s="21"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="29">
+      <c r="L38" s="29"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="10">
         <v>44909</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>44196</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F39" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F39" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G39" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G39" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="18" t="str">
+      <c r="H39" s="13" t="str">
         <f ca="1">IF(F39&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I39" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="J39" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="10">
         <v>40711</v>
       </c>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="29">
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="10">
         <v>44909</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <v>44196</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F40" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F40" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G40" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G40" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="18" t="str">
+      <c r="H40" s="13" t="str">
         <f ca="1">IF(F40&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I40" s="18" t="s">
+      <c r="I40" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="J40" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="10">
         <v>41809</v>
       </c>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="29">
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="11">
         <v>46114</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="11">
         <v>47579</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F41" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F41" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>1347</v>
-      </c>
-      <c r="G41" s="25" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G41" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="26" t="s">
+      <c r="H41" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I41" s="26" t="s">
+      <c r="I41" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="J41" s="24" t="s">
+      <c r="J41" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="13">
+      <c r="K41" s="11">
         <v>45959</v>
       </c>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="29">
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="19" t="s">
         <v>83</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="10">
         <v>44909</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <v>44196</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F42" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F42" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G42" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G42" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="17" t="str">
+      <c r="H42" s="13" t="str">
         <f ca="1">IF(F42&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I42" s="18" t="s">
+      <c r="I42" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="15" t="s">
+      <c r="J42" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="10">
         <v>41166</v>
       </c>
-      <c r="L42" s="19"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="29">
+      <c r="L42" s="31"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="19" t="s">
         <v>83</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="10">
         <v>45625</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>44196</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F43" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F43" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G43" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="17" t="str">
+      <c r="H43" s="13" t="str">
         <f ca="1">IF(F43&lt;=0,"VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I43" s="18" t="s">
+      <c r="I43" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="J43" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="10">
         <v>45625</v>
       </c>
-      <c r="L43" s="19"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="30" t="s">
+      <c r="L43" s="31"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="35">
         <v>45783</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="35">
         <v>46331</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="35">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F44" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F44" s="36">
         <f t="shared" ca="1" si="5"/>
-        <v>99</v>
-      </c>
-      <c r="G44" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G44" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="H44" s="18" t="str">
+      <c r="H44" s="37" t="str">
         <f t="shared" ref="H44:H58" ca="1" si="6">IF(F44&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I44" s="18" t="s">
+      <c r="I44" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="15" t="s">
+      <c r="J44" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K44" s="35">
         <v>45602</v>
       </c>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="32">
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="19" t="s">
         <v>86</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="10">
         <v>45583</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>44196</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F45" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F45" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G45" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G45" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H45" s="18" t="str">
+      <c r="H45" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I45" s="18" t="s">
+      <c r="I45" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="15" t="s">
+      <c r="J45" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="10">
         <v>45583</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="29">
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="10">
         <v>45541</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="10">
         <v>46573</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F46" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F46" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>341</v>
-      </c>
-      <c r="G46" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="G46" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="18" t="str">
+      <c r="H46" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I46" s="18" t="s">
+      <c r="I46" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J46" s="15" t="s">
+      <c r="J46" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="10">
         <v>44810</v>
       </c>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="29">
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="19" t="s">
         <v>88</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="10">
         <v>45505</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>44196</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F47" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F47" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G47" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="18" t="str">
+      <c r="H47" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I47" s="18" t="s">
+      <c r="I47" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="15" t="s">
+      <c r="J47" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="10">
         <v>44655</v>
       </c>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="29">
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="10">
         <v>45992</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="10">
         <v>46265</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F48" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F48" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
-      </c>
-      <c r="G48" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H48" s="18" t="str">
+      <c r="H48" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I48" s="18" t="s">
+      <c r="I48" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J48" s="15" t="s">
+      <c r="J48" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="10">
         <v>42781</v>
       </c>
-      <c r="L48" s="19" t="s">
+      <c r="L48" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="29">
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="19" t="s">
         <v>90</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="10">
         <v>44946</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>44196</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F49" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F49" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G49" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G49" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H49" s="18" t="str">
+      <c r="H49" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I49" s="18" t="s">
+      <c r="I49" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="15" t="s">
+      <c r="J49" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="12">
+      <c r="K49" s="10">
         <v>44946</v>
       </c>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="29">
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="10">
         <v>45870</v>
       </c>
-      <c r="D50" s="12">
-        <v>46234</v>
-      </c>
-      <c r="E50" s="11">
+      <c r="D50" s="10">
+        <v>46234</v>
+      </c>
+      <c r="E50" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F50" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F50" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="G50" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H50" s="18" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I50" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K50" s="12">
-        <v>42744</v>
-      </c>
-      <c r="L50" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A51" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="12">
-        <v>45870</v>
-      </c>
-      <c r="D51" s="12">
-        <v>46234</v>
-      </c>
-      <c r="E51" s="11">
-        <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F51" s="15">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="18" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K51" s="12">
-        <v>43733</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="12">
-        <v>46033</v>
-      </c>
-      <c r="D52" s="12">
-        <v>46213</v>
-      </c>
-      <c r="E52" s="11">
-        <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F52" s="15">
-        <f t="shared" ca="1" si="5"/>
-        <v>-19</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52" s="18" t="str">
+      <c r="H50" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I52" s="18" t="s">
+      <c r="I50" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J52" s="15" t="s">
+      <c r="J50" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K52" s="12">
-        <v>45849</v>
-      </c>
-      <c r="L52" s="19" t="s">
+      <c r="K50" s="10">
+        <v>42744</v>
+      </c>
+      <c r="L50" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53" s="12">
-        <v>44902</v>
-      </c>
-      <c r="D53" s="11">
-        <v>44196</v>
-      </c>
-      <c r="E53" s="11">
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="10">
+        <v>45870</v>
+      </c>
+      <c r="D51" s="10">
+        <v>46234</v>
+      </c>
+      <c r="E51" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F53" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F51" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H53" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I53" s="18" t="s">
+      <c r="I51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" s="10">
+        <v>43733</v>
+      </c>
+      <c r="L51" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="10">
+        <v>46033</v>
+      </c>
+      <c r="D52" s="10">
+        <v>46213</v>
+      </c>
+      <c r="E52" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>46234</v>
+      </c>
+      <c r="F52" s="12">
+        <f t="shared" ca="1" si="5"/>
+        <v>-21</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="13" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K52" s="10">
+        <v>45849</v>
+      </c>
+      <c r="L52" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="35">
+        <v>44902</v>
+      </c>
+      <c r="D53" s="35">
+        <v>44196</v>
+      </c>
+      <c r="E53" s="35">
+        <f t="shared" ca="1" si="4"/>
+        <v>46234</v>
+      </c>
+      <c r="F53" s="36">
+        <f t="shared" ca="1" si="5"/>
+        <v>-2038</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" s="37" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v>VENDA</v>
+      </c>
+      <c r="I53" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="15" t="s">
+      <c r="J53" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="12">
+      <c r="K53" s="35">
         <v>41320</v>
       </c>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
-      <c r="N53" s="12"/>
-      <c r="O53" s="32">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="30" t="s">
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="46">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="12">
-        <v>46234</v>
-      </c>
-      <c r="D54" s="12">
+      <c r="C54" s="35">
+        <v>46234</v>
+      </c>
+      <c r="D54" s="35">
         <v>47330</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="35">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F54" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F54" s="36">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1098</v>
-      </c>
-      <c r="G54" s="16" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G54" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="H54" s="18" t="str">
+      <c r="H54" s="37" t="str">
         <f t="shared" ref="H54" ca="1" si="8">IF(F54&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I54" s="18" t="s">
+      <c r="I54" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="J54" s="15" t="s">
+      <c r="J54" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="12">
-        <v>46234</v>
-      </c>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="32">
+      <c r="K54" s="35">
+        <v>46234</v>
+      </c>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="19" t="s">
         <v>97</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="10">
         <v>44835</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>44196</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F55" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F55" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G55" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G55" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="18" t="str">
+      <c r="H55" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I55" s="18" t="s">
+      <c r="I55" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="15" t="s">
+      <c r="J55" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="10">
         <v>43693</v>
       </c>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="29">
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="19" t="s">
         <v>98</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="10">
         <v>44841</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <v>44196</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F56" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F56" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G56" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G56" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="H56" s="18" t="str">
+      <c r="H56" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I56" s="18" t="s">
+      <c r="I56" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="15" t="s">
+      <c r="J56" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K56" s="12">
+      <c r="K56" s="10">
         <v>41887</v>
       </c>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="29">
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="19" t="s">
         <v>98</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="10">
         <v>44841</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>44196</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E57" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F57" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F57" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G57" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G57" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H57" s="18" t="str">
+      <c r="H57" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I57" s="18" t="s">
+      <c r="I57" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="15" t="s">
+      <c r="J57" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K57" s="12">
+      <c r="K57" s="10">
         <v>42216</v>
       </c>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="29">
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="10">
         <v>45566</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <v>44196</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F58" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F58" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G58" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G58" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="18" t="str">
+      <c r="H58" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I58" s="18" t="s">
+      <c r="I58" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="15" t="s">
+      <c r="J58" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K58" s="12">
+      <c r="K58" s="10">
         <v>45566</v>
       </c>
-      <c r="L58" s="12"/>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
-      <c r="O58" s="29">
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="10">
         <v>45992</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="10">
         <v>46295</v>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F59" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F59" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>63</v>
-      </c>
-      <c r="G59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="18" t="s">
+      <c r="H59" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I59" s="18" t="s">
+      <c r="I59" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="J59" s="15" t="s">
+      <c r="J59" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="10">
         <v>43262</v>
       </c>
-      <c r="L59" s="12"/>
-      <c r="M59" s="12"/>
-      <c r="N59" s="12"/>
-      <c r="O59" s="29">
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="19" t="s">
         <v>103</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="10">
         <v>44621</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <v>44196</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F60" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F60" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G60" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G60" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="18" t="str">
+      <c r="H60" s="13" t="str">
         <f ca="1">IF(F60&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I60" s="18" t="s">
+      <c r="I60" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K60" s="12">
+      <c r="K60" s="10">
         <v>43693</v>
       </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="12"/>
-      <c r="N60" s="12"/>
-      <c r="O60" s="29">
+      <c r="L60" s="15"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="30" t="s">
+      <c r="A61" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="10">
         <v>45962</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="10">
         <v>46022</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F61" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F61" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-210</v>
-      </c>
-      <c r="G61" s="16" t="s">
+        <v>-212</v>
+      </c>
+      <c r="G61" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H61" s="18" t="str">
+      <c r="H61" s="13" t="str">
         <f ca="1">IF(F61&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I61" s="18" t="s">
+      <c r="I61" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J61" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="10">
         <v>40924</v>
       </c>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="29">
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="10">
         <v>45528</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <v>44196</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F62" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F62" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G62" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G62" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H62" s="18" t="str">
+      <c r="H62" s="13" t="str">
         <f ca="1">IF(F62&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I62" s="18" t="s">
+      <c r="I62" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="15" t="s">
+      <c r="J62" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K62" s="12">
+      <c r="K62" s="10">
         <v>44981</v>
       </c>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="29">
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="19" t="s">
         <v>107</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="10">
         <v>45962</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>44196</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F63" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F63" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2036</v>
-      </c>
-      <c r="G63" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G63" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H63" s="18" t="str">
+      <c r="H63" s="13" t="str">
         <f ca="1">IF(F63&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I63" s="18" t="s">
+      <c r="I63" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="15" t="s">
+      <c r="J63" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K63" s="12">
+      <c r="K63" s="10">
         <v>41421</v>
       </c>
-      <c r="L63" s="12"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="12"/>
-      <c r="O63" s="29">
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="11">
         <v>45962</v>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="11">
         <v>46082</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F64" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F64" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>-150</v>
-      </c>
-      <c r="G64" s="25" t="s">
+        <v>-152</v>
+      </c>
+      <c r="G64" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H64" s="18" t="str">
@@ -4224,1985 +4317,1968 @@
       <c r="I64" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="24" t="s">
+      <c r="J64" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K64" s="13">
+      <c r="K64" s="11">
         <v>45492</v>
       </c>
-      <c r="L64" s="13"/>
-      <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="29">
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="11"/>
+      <c r="O64" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="10">
         <v>45992</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="10">
         <v>46203</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F65" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F65" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-29</v>
-      </c>
-      <c r="G65" s="16" t="s">
+        <v>-31</v>
+      </c>
+      <c r="G65" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I65" s="18" t="s">
+      <c r="I65" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K65" s="12">
+      <c r="K65" s="10">
         <v>42082</v>
       </c>
-      <c r="L65" s="12"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12"/>
-      <c r="O65" s="29">
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="19" t="s">
         <v>109</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="10">
         <v>44777</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <v>44196</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F66" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F66" s="12">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2036</v>
-      </c>
-      <c r="G66" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G66" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H66" s="18" t="str">
+      <c r="H66" s="13" t="str">
         <f ca="1">IF(F66&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I66" s="18" t="s">
+      <c r="I66" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K66" s="12">
+      <c r="K66" s="10">
         <v>41066</v>
       </c>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-      <c r="O66" s="29">
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="19" t="s">
         <v>109</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="10">
         <v>45929</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <v>44196</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F67" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F67" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2036</v>
-      </c>
-      <c r="G67" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G67" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="H67" s="18" t="str">
+      <c r="H67" s="13" t="str">
         <f ca="1">IF(F67&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I67" s="18" t="s">
+      <c r="I67" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J67" s="15" t="s">
+      <c r="J67" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="10">
         <v>45198</v>
       </c>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-      <c r="O67" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="30" t="s">
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="35">
         <v>45719</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="35">
         <v>44196</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="35">
         <f t="shared" ca="1" si="4"/>
-        <v>46232</v>
-      </c>
-      <c r="F68" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F68" s="36">
         <f t="shared" ca="1" si="9"/>
-        <v>-2036</v>
-      </c>
-      <c r="G68" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G68" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="18" t="str">
+      <c r="H68" s="37" t="str">
         <f ca="1">IF(F68&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I68" s="18" t="s">
+      <c r="I68" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="15" t="s">
+      <c r="J68" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="K68" s="12">
+      <c r="K68" s="35">
         <v>43661</v>
       </c>
-      <c r="L68" s="12"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12"/>
-      <c r="O68" s="32">
+      <c r="L68" s="35"/>
+      <c r="M68" s="35"/>
+      <c r="N68" s="35"/>
+      <c r="O68" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="19" t="s">
         <v>111</v>
       </c>
       <c r="B69" s="14"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18" t="s">
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J69" s="15"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-      <c r="O69" s="29">
+      <c r="J69" s="12"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C70" s="13">
+      <c r="C70" s="11">
         <v>46054</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D70" s="11">
         <v>44196</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="11">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F70" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F70" s="17">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2036</v>
-      </c>
-      <c r="G70" s="25" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G70" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="26" t="str">
+      <c r="H70" s="18" t="str">
         <f ca="1">IF(F70&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I70" s="26"/>
-      <c r="J70" s="24" t="s">
+      <c r="I70" s="18"/>
+      <c r="J70" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K70" s="13">
+      <c r="K70" s="11">
         <v>44036</v>
       </c>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="29">
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="10">
         <v>45992</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="10">
         <v>46326</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F71" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F71" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>94</v>
-      </c>
-      <c r="G71" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G71" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H71" s="18" t="s">
+      <c r="H71" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I71" s="18" t="s">
+      <c r="I71" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K71" s="12">
+      <c r="K71" s="10">
         <v>44841</v>
       </c>
-      <c r="L71" s="12" t="s">
+      <c r="L71" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12"/>
-      <c r="O71" s="29">
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="10">
         <v>45962</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="10">
         <v>46265</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F72" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F72" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>33</v>
-      </c>
-      <c r="G72" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H72" s="18" t="str">
+      <c r="H72" s="13" t="str">
         <f ca="1">IF(F72&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I72" s="18" t="s">
+      <c r="I72" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="15" t="s">
+      <c r="J72" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K72" s="12">
+      <c r="K72" s="10">
         <v>42040</v>
       </c>
-      <c r="L72" s="12"/>
-      <c r="M72" s="12"/>
-      <c r="N72" s="12"/>
-      <c r="O72" s="29"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="44">
+        <v>90</v>
+      </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A73" s="30" t="s">
+      <c r="A73" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="10">
         <v>45962</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="10">
         <v>46265</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F73" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F73" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>33</v>
-      </c>
-      <c r="G73" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="18" t="str">
+      <c r="H73" s="13" t="str">
         <f ca="1">IF(F73&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I73" s="18" t="s">
+      <c r="I73" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="15" t="s">
+      <c r="J73" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K73" s="12">
+      <c r="K73" s="10">
         <v>43733</v>
       </c>
-      <c r="L73" s="12"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12"/>
-      <c r="O73" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="31" t="s">
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="25" t="s">
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26" t="s">
+      <c r="H74" s="37"/>
+      <c r="I74" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="J74" s="24" t="s">
+      <c r="J74" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13" t="s">
+      <c r="K74" s="35"/>
+      <c r="L74" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="32"/>
+      <c r="M74" s="35"/>
+      <c r="N74" s="35"/>
+      <c r="O74" s="46"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A75" s="30" t="s">
+      <c r="A75" s="19" t="s">
         <v>118</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="10">
         <v>46204</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <v>46568</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F75" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F75" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>336</v>
-      </c>
-      <c r="G75" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H75" s="18" t="str">
+      <c r="H75" s="13" t="str">
         <f ca="1">IF(F75&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="15" t="s">
+      <c r="J75" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K75" s="12">
+      <c r="K75" s="10">
         <v>45999</v>
       </c>
-      <c r="L75" s="12" t="s">
+      <c r="L75" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12"/>
-      <c r="O75" s="29">
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A76" s="30" t="s">
+      <c r="A76" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="B76" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="10">
         <v>45555</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="10">
         <v>46465</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F76" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F76" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>233</v>
-      </c>
-      <c r="G76" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="G76" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H76" s="18" t="str">
+      <c r="H76" s="13" t="str">
         <f ca="1">IF(F76&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I76" s="18" t="s">
+      <c r="I76" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="15" t="s">
+      <c r="J76" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K76" s="12">
+      <c r="K76" s="10">
         <v>45371</v>
       </c>
-      <c r="L76" s="12" t="s">
+      <c r="L76" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="29">
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A77" s="30" t="s">
+      <c r="A77" s="19" t="s">
         <v>120</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="10">
         <v>45639</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <v>44196</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F77" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F77" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G77" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G77" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H77" s="18" t="str">
+      <c r="H77" s="13" t="str">
         <f ca="1">IF(F77&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I77" s="18" t="s">
+      <c r="I77" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J77" s="15" t="s">
+      <c r="J77" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K77" s="12">
+      <c r="K77" s="10">
         <v>45273</v>
       </c>
-      <c r="L77" s="12" t="s">
+      <c r="L77" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12"/>
-      <c r="O77" s="29">
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A78" s="30" t="s">
+      <c r="A78" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="10">
         <v>45989</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="10">
         <v>47449</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F78" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F78" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>1217</v>
-      </c>
-      <c r="G78" s="16" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G78" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H78" s="18" t="s">
+      <c r="H78" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I78" s="18" t="s">
+      <c r="I78" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="J78" s="15" t="s">
+      <c r="J78" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K78" s="12">
+      <c r="K78" s="10">
         <v>45989</v>
       </c>
-      <c r="L78" s="12" t="s">
+      <c r="L78" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="M78" s="12"/>
-      <c r="N78" s="12"/>
-      <c r="O78" s="29">
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A79" s="30" t="s">
+      <c r="A79" s="19" t="s">
         <v>125</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="10">
         <v>45039</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <v>44196</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F79" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F79" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G79" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G79" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H79" s="18" t="str">
+      <c r="H79" s="13" t="str">
         <f t="shared" ref="H79:H84" ca="1" si="12">IF(F79&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="I79" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J79" s="15" t="s">
+      <c r="J79" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K79" s="12">
+      <c r="K79" s="10">
         <v>43984</v>
       </c>
-      <c r="L79" s="12"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="12"/>
-      <c r="O79" s="29">
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A80" s="30" t="s">
+      <c r="A80" s="19" t="s">
         <v>127</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="10">
         <v>43749</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <v>44196</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F80" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F80" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G80" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H80" s="18" t="str">
+      <c r="H80" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>VENDA</v>
       </c>
-      <c r="I80" s="18" t="s">
+      <c r="I80" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="15" t="s">
+      <c r="J80" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K80" s="12">
+      <c r="K80" s="10">
         <v>41866</v>
       </c>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12"/>
-      <c r="O80" s="29">
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A81" s="30" t="s">
+      <c r="A81" s="19" t="s">
         <v>127</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="10">
         <v>43749</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <v>44196</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F81" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F81" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G81" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G81" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H81" s="18" t="str">
+      <c r="H81" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>VENDA</v>
       </c>
-      <c r="I81" s="18" t="s">
+      <c r="I81" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="15" t="s">
+      <c r="J81" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K81" s="12">
+      <c r="K81" s="10">
         <v>42670</v>
       </c>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12"/>
-      <c r="O81" s="29">
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A82" s="30" t="s">
+      <c r="A82" s="19" t="s">
         <v>127</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="10">
         <v>43641</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <v>44196</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F82" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F82" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G82" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G82" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H82" s="18" t="str">
+      <c r="H82" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>VENDA</v>
       </c>
-      <c r="I82" s="18" t="s">
+      <c r="I82" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="15" t="s">
+      <c r="J82" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K82" s="12">
+      <c r="K82" s="10">
         <v>43276</v>
       </c>
-      <c r="L82" s="12"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
-      <c r="O82" s="29">
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A83" s="30" t="s">
+      <c r="A83" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B83" s="20" t="s">
+      <c r="B83" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="10">
         <v>45870</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="10">
         <v>46418</v>
       </c>
-      <c r="E83" s="12">
+      <c r="E83" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F83" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F83" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
-      </c>
-      <c r="G83" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G83" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H83" s="18" t="str">
+      <c r="H83" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I83" s="18" t="s">
+      <c r="I83" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="15" t="s">
+      <c r="J83" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K83" s="12">
+      <c r="K83" s="10">
         <v>43672</v>
       </c>
-      <c r="L83" s="12"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12"/>
-      <c r="O83" s="29">
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A84" s="30" t="s">
+      <c r="A84" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B84" s="20" t="s">
+      <c r="B84" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="10">
         <v>46054</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="10">
         <v>46418</v>
       </c>
-      <c r="E84" s="12">
+      <c r="E84" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F84" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F84" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
-      </c>
-      <c r="G84" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G84" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H84" s="18" t="str">
+      <c r="H84" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I84" s="18" t="s">
+      <c r="I84" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="15" t="s">
+      <c r="J84" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K84" s="12">
+      <c r="K84" s="10">
         <v>45870</v>
       </c>
-      <c r="L84" s="12"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12"/>
-      <c r="O84" s="29">
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A85" s="30" t="s">
+      <c r="A85" s="19" t="s">
         <v>129</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="10">
         <v>46203</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="10">
         <v>46751</v>
       </c>
-      <c r="E85" s="12">
+      <c r="E85" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F85" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F85" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>519</v>
-      </c>
-      <c r="G85" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="G85" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="H85" s="18" t="s">
+      <c r="H85" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I85" s="18" t="s">
+      <c r="I85" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J85" s="15"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="12" t="s">
+      <c r="J85" s="12"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12"/>
-      <c r="O85" s="29">
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A86" s="30" t="s">
+      <c r="A86" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="10">
         <v>46082</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="10">
         <v>46446</v>
       </c>
-      <c r="E86" s="12">
+      <c r="E86" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F86" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F86" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>214</v>
-      </c>
-      <c r="G86" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G86" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="18" t="s">
+      <c r="H86" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I86" s="18" t="s">
+      <c r="I86" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J86" s="15" t="s">
+      <c r="J86" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K86" s="12">
+      <c r="K86" s="10">
         <v>43476</v>
       </c>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="29">
+      <c r="L86" s="10"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="10"/>
+      <c r="O86" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A87" s="30" t="s">
+      <c r="A87" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B87" s="20" t="s">
+      <c r="B87" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="10">
         <v>46082</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="10">
         <v>46446</v>
       </c>
-      <c r="E87" s="12">
+      <c r="E87" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F87" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F87" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>214</v>
-      </c>
-      <c r="G87" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G87" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="H87" s="18" t="s">
+      <c r="H87" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I87" s="18" t="s">
+      <c r="I87" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J87" s="16" t="s">
+      <c r="J87" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="K87" s="12">
+      <c r="K87" s="10">
         <v>45691</v>
       </c>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="29">
+      <c r="L87" s="10"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A88" s="30" t="s">
+      <c r="A88" s="19" t="s">
         <v>133</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="10">
         <v>45173</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <v>44196</v>
       </c>
-      <c r="E88" s="12">
+      <c r="E88" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F88" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F88" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G88" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H88" s="18" t="str">
+      <c r="H88" s="13" t="str">
         <f ca="1">IF(F88&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I88" s="18" t="s">
+      <c r="I88" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="15" t="s">
+      <c r="J88" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K88" s="12">
+      <c r="K88" s="10">
         <v>42692</v>
       </c>
-      <c r="L88" s="12"/>
-      <c r="M88" s="12"/>
-      <c r="N88" s="12"/>
-      <c r="O88" s="29"/>
+      <c r="L88" s="10"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="44">
+        <v>90</v>
+      </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A89" s="30" t="s">
+      <c r="A89" s="19" t="s">
         <v>134</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="10">
         <v>44798</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <v>44196</v>
       </c>
-      <c r="E89" s="12">
+      <c r="E89" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F89" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F89" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G89" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G89" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H89" s="18" t="str">
+      <c r="H89" s="13" t="str">
         <f ca="1">IF(F89&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I89" s="18" t="s">
+      <c r="I89" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="15" t="s">
+      <c r="J89" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K89" s="12">
+      <c r="K89" s="10">
         <v>40534</v>
       </c>
-      <c r="L89" s="12"/>
-      <c r="M89" s="12"/>
-      <c r="N89" s="12"/>
-      <c r="O89" s="29">
+      <c r="L89" s="10"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A90" s="30" t="s">
+      <c r="A90" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B90" s="20" t="s">
+      <c r="B90" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="10">
         <v>46199</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="10">
         <v>46594</v>
       </c>
-      <c r="E90" s="12">
+      <c r="E90" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F90" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F90" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>362</v>
-      </c>
-      <c r="G90" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="G90" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H90" s="18" t="s">
+      <c r="H90" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I90" s="18" t="s">
+      <c r="I90" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="J90" s="15" t="s">
+      <c r="J90" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K90" s="12"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="12"/>
-      <c r="O90" s="29">
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="10"/>
+      <c r="O90" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A91" s="30" t="s">
+      <c r="A91" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="20" t="s">
+      <c r="B91" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="10">
         <v>45822</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="10">
         <v>46551</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F91" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F91" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>319</v>
-      </c>
-      <c r="G91" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="G91" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H91" s="18" t="str">
+      <c r="H91" s="13" t="str">
         <f t="shared" ref="H91:H104" ca="1" si="13">IF(F91&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I91" s="18" t="s">
+      <c r="I91" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="15" t="s">
+      <c r="J91" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K91" s="12">
+      <c r="K91" s="10">
         <v>43913</v>
       </c>
-      <c r="L91" s="12"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="12"/>
-      <c r="O91" s="29">
+      <c r="L91" s="10"/>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10"/>
+      <c r="O91" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A92" s="30" t="s">
+      <c r="A92" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B92" s="20" t="s">
+      <c r="B92" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92" s="10">
         <v>45993</v>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="10">
         <v>46539</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F92" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F92" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>307</v>
-      </c>
-      <c r="G92" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="G92" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H92" s="18" t="str">
+      <c r="H92" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I92" s="18" t="s">
+      <c r="I92" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J92" s="15" t="s">
+      <c r="J92" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K92" s="12">
+      <c r="K92" s="10">
         <v>45809</v>
       </c>
-      <c r="L92" s="12"/>
-      <c r="M92" s="12"/>
-      <c r="N92" s="12"/>
-      <c r="O92" s="29"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="44">
+        <v>90</v>
+      </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A93" s="30" t="s">
+      <c r="A93" s="19" t="s">
         <v>138</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="10">
         <v>44197</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>44196</v>
       </c>
-      <c r="E93" s="12">
+      <c r="E93" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F93" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F93" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G93" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G93" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="H93" s="18" t="str">
+      <c r="H93" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I93" s="18" t="s">
+      <c r="I93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="15" t="s">
+      <c r="J93" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K93" s="12">
+      <c r="K93" s="10">
         <v>42937</v>
       </c>
-      <c r="L93" s="12"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12"/>
-      <c r="O93" s="29">
+      <c r="L93" s="10"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A94" s="31" t="s">
+      <c r="A94" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C94" s="13">
+      <c r="C94" s="11">
         <v>45908</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94" s="11">
         <v>46454</v>
       </c>
-      <c r="E94" s="23">
+      <c r="E94" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F94" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F94" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>222</v>
-      </c>
-      <c r="G94" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G94" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H94" s="26" t="str">
+      <c r="H94" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I94" s="26" t="s">
+      <c r="I94" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J94" s="24" t="s">
+      <c r="J94" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K94" s="13">
+      <c r="K94" s="11">
         <v>45055</v>
       </c>
-      <c r="L94" s="13" t="s">
+      <c r="L94" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="M94" s="13"/>
-      <c r="N94" s="13"/>
-      <c r="O94" s="29">
+      <c r="M94" s="11"/>
+      <c r="N94" s="11"/>
+      <c r="O94" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B95" s="22" t="s">
+      <c r="B95" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="13">
+      <c r="C95" s="11">
         <v>45908</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="11">
         <v>46454</v>
       </c>
-      <c r="E95" s="23">
+      <c r="E95" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F95" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F95" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>222</v>
-      </c>
-      <c r="G95" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G95" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H95" s="26" t="str">
+      <c r="H95" s="18" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I95" s="26" t="s">
+      <c r="I95" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J95" s="24" t="s">
+      <c r="J95" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K95" s="13">
+      <c r="K95" s="11">
         <v>45908</v>
       </c>
-      <c r="L95" s="13" t="s">
+      <c r="L95" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="M95" s="13"/>
-      <c r="N95" s="13"/>
-      <c r="O95" s="29">
+      <c r="M95" s="11"/>
+      <c r="N95" s="11"/>
+      <c r="O95" s="45">
         <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A96" s="30" t="s">
+      <c r="A96" s="19" t="s">
         <v>141</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="10">
         <v>44909</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="10">
         <v>44196</v>
       </c>
-      <c r="E96" s="12">
+      <c r="E96" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F96" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F96" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G96" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G96" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H96" s="18" t="str">
+      <c r="H96" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I96" s="18" t="s">
+      <c r="I96" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J96" s="15" t="s">
+      <c r="J96" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K96" s="12">
+      <c r="K96" s="10">
         <v>41320</v>
       </c>
-      <c r="L96" s="12"/>
-      <c r="M96" s="12"/>
-      <c r="N96" s="12"/>
-      <c r="O96" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="31" t="s">
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C97" s="13">
+      <c r="C97" s="35">
         <v>45962</v>
       </c>
-      <c r="D97" s="13">
+      <c r="D97" s="35">
         <v>46537</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="35">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F97" s="24">
+        <v>46234</v>
+      </c>
+      <c r="F97" s="36">
         <f t="shared" ca="1" si="11"/>
-        <v>305</v>
-      </c>
-      <c r="G97" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="G97" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="H97" s="26" t="str">
+      <c r="H97" s="37" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I97" s="26" t="s">
+      <c r="I97" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="24" t="s">
+      <c r="J97" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="K97" s="13">
+      <c r="K97" s="35">
         <v>43301</v>
       </c>
-      <c r="L97" s="13"/>
-      <c r="M97" s="13"/>
-      <c r="N97" s="13"/>
-      <c r="O97" s="32">
+      <c r="L97" s="35"/>
+      <c r="M97" s="35"/>
+      <c r="N97" s="35"/>
+      <c r="O97" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="30" t="s">
+      <c r="A98" s="19" t="s">
         <v>143</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C98" s="12">
+      <c r="C98" s="10">
         <v>43070</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="10">
         <v>44196</v>
       </c>
-      <c r="E98" s="12">
+      <c r="E98" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F98" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F98" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G98" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G98" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H98" s="18" t="str">
+      <c r="H98" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I98" s="18" t="s">
+      <c r="I98" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J98" s="15" t="s">
+      <c r="J98" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K98" s="12">
+      <c r="K98" s="10">
         <v>40605</v>
       </c>
-      <c r="L98" s="12"/>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12"/>
-      <c r="O98" s="29">
+      <c r="L98" s="10"/>
+      <c r="M98" s="10"/>
+      <c r="N98" s="10"/>
+      <c r="O98" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A99" s="30" t="s">
+      <c r="A99" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99" s="10">
         <v>45874</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="10">
         <v>46422</v>
       </c>
-      <c r="E99" s="12">
+      <c r="E99" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F99" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F99" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>190</v>
-      </c>
-      <c r="G99" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G99" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H99" s="18" t="str">
+      <c r="H99" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I99" s="18" t="s">
+      <c r="I99" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J99" s="15" t="s">
+      <c r="J99" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K99" s="12">
+      <c r="K99" s="10">
         <v>45692</v>
       </c>
-      <c r="L99" s="12"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12"/>
-      <c r="O99" s="29">
+      <c r="L99" s="10"/>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A100" s="30" t="s">
+      <c r="A100" s="19" t="s">
         <v>145</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="12">
+      <c r="C100" s="10">
         <v>45689</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <v>44196</v>
       </c>
-      <c r="E100" s="12">
+      <c r="E100" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F100" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F100" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2036</v>
-      </c>
-      <c r="G100" s="16" t="s">
+        <v>-2038</v>
+      </c>
+      <c r="G100" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H100" s="18" t="str">
+      <c r="H100" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I100" s="18" t="s">
+      <c r="I100" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="15" t="s">
+      <c r="J100" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K100" s="12">
+      <c r="K100" s="10">
         <v>40868</v>
       </c>
-      <c r="L100" s="12"/>
-      <c r="M100" s="12"/>
-      <c r="N100" s="12"/>
-      <c r="O100" s="29">
+      <c r="L100" s="10"/>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10"/>
+      <c r="O100" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A101" s="30" t="s">
+      <c r="A101" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B101" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101" s="10">
         <v>45315</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="10">
         <v>46226</v>
       </c>
-      <c r="E101" s="12">
+      <c r="E101" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F101" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F101" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-6</v>
-      </c>
-      <c r="G101" s="16" t="s">
+        <v>-8</v>
+      </c>
+      <c r="G101" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H101" s="18" t="str">
+      <c r="H101" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>VENDA</v>
       </c>
-      <c r="I101" s="18" t="s">
+      <c r="I101" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J101" s="15" t="s">
+      <c r="J101" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K101" s="12">
+      <c r="K101" s="10">
         <v>45131</v>
       </c>
-      <c r="L101" s="12"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12"/>
-      <c r="O101" s="29">
+      <c r="L101" s="10"/>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10"/>
+      <c r="O101" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A102" s="30" t="s">
+      <c r="A102" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C102" s="10">
         <v>45658</v>
       </c>
-      <c r="D102" s="12">
+      <c r="D102" s="10">
         <v>46532</v>
       </c>
-      <c r="E102" s="12">
+      <c r="E102" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F102" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F102" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
-      </c>
-      <c r="G102" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="G102" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H102" s="18" t="str">
+      <c r="H102" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I102" s="18" t="s">
+      <c r="I102" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="J102" s="15" t="s">
+      <c r="J102" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K102" s="12">
+      <c r="K102" s="10">
         <v>44694</v>
       </c>
-      <c r="L102" s="12"/>
-      <c r="M102" s="12"/>
-      <c r="N102" s="12"/>
-      <c r="O102" s="29">
+      <c r="L102" s="10"/>
+      <c r="M102" s="10"/>
+      <c r="N102" s="10"/>
+      <c r="O102" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A103" s="30" t="s">
+      <c r="A103" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B103" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103" s="10">
         <v>45928</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="10">
         <v>46473</v>
       </c>
-      <c r="E103" s="12">
+      <c r="E103" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F103" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F103" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>241</v>
-      </c>
-      <c r="G103" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="G103" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H103" s="18" t="str">
+      <c r="H103" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I103" s="18" t="s">
+      <c r="I103" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J103" s="15" t="s">
+      <c r="J103" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K103" s="12">
+      <c r="K103" s="10">
         <v>45744</v>
       </c>
-      <c r="L103" s="12"/>
-      <c r="M103" s="12"/>
-      <c r="N103" s="12"/>
-      <c r="O103" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="30" t="s">
+      <c r="L103" s="10"/>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10"/>
+      <c r="O103" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104" s="35">
         <v>45757</v>
       </c>
-      <c r="D104" s="12">
+      <c r="D104" s="35">
         <v>46669</v>
       </c>
-      <c r="E104" s="12">
+      <c r="E104" s="35">
         <f t="shared" ca="1" si="10"/>
-        <v>46232</v>
-      </c>
-      <c r="F104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F104" s="36">
         <f t="shared" ca="1" si="11"/>
-        <v>437</v>
-      </c>
-      <c r="G104" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="G104" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="H104" s="18" t="str">
+      <c r="H104" s="37" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I104" s="18" t="s">
+      <c r="I104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="J104" s="16" t="s">
+      <c r="J104" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="K104" s="12">
+      <c r="K104" s="35">
         <v>45575</v>
       </c>
-      <c r="L104" s="12"/>
-      <c r="M104" s="12"/>
-      <c r="N104" s="12"/>
-      <c r="O104" s="32">
+      <c r="L104" s="35"/>
+      <c r="M104" s="35"/>
+      <c r="N104" s="35"/>
+      <c r="O104" s="46">
         <v>90</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A105" s="30" t="s">
+      <c r="A105" s="19" t="s">
         <v>152</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="16"/>
-      <c r="H105" s="18"/>
-      <c r="I105" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="10">
+        <v>45536</v>
+      </c>
+      <c r="D105" s="10">
+        <v>46265</v>
+      </c>
+      <c r="E105" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46234</v>
+      </c>
+      <c r="F105" s="12">
+        <f ca="1">D105-E105</f>
+        <v>31</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H105" s="13" t="str">
+        <f ca="1">IF(F105&lt;=0, "VENDA","CAREPACK")</f>
+        <v>CAREPACK</v>
+      </c>
+      <c r="I105" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J105" s="15"/>
-      <c r="K105" s="12"/>
-      <c r="L105" s="12"/>
-      <c r="M105" s="12"/>
-      <c r="N105" s="12"/>
-      <c r="O105" s="29">
+      <c r="J105" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K105" s="10">
+        <v>44755</v>
+      </c>
+      <c r="L105" s="10"/>
+      <c r="M105" s="10"/>
+      <c r="N105" s="10"/>
+      <c r="O105" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A106" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="B106" s="20" t="s">
+      <c r="A106" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B106" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C106" s="12">
-        <v>45536</v>
-      </c>
-      <c r="D106" s="12">
-        <v>46265</v>
-      </c>
-      <c r="E106" s="12">
+      <c r="C106" s="10">
+        <v>46226</v>
+      </c>
+      <c r="D106" s="10">
+        <v>47140</v>
+      </c>
+      <c r="E106" s="10">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F106" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F106" s="12">
         <f ca="1">D106-E106</f>
-        <v>33</v>
-      </c>
-      <c r="G106" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H106" s="18" t="str">
+        <v>906</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H106" s="13" t="str">
         <f ca="1">IF(F106&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I106" s="18" t="s">
+      <c r="I106" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J106" s="15" t="s">
+      <c r="J106" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K106" s="12">
-        <v>44755</v>
-      </c>
-      <c r="L106" s="12"/>
-      <c r="M106" s="12"/>
-      <c r="N106" s="12"/>
-      <c r="O106" s="29"/>
+      <c r="K106" s="10">
+        <v>46043</v>
+      </c>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="44">
+        <v>90</v>
+      </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A107" s="30" t="s">
+      <c r="A107" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C107" s="12">
-        <v>46226</v>
-      </c>
-      <c r="D107" s="12">
-        <v>47140</v>
-      </c>
-      <c r="E107" s="12">
+      <c r="C107" s="10">
+        <v>45839</v>
+      </c>
+      <c r="D107" s="10">
+        <v>46477</v>
+      </c>
+      <c r="E107" s="10">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F107" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F107" s="12">
         <f ca="1">D107-E107</f>
-        <v>908</v>
-      </c>
-      <c r="G107" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H107" s="18" t="str">
+        <v>243</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" s="13" t="str">
         <f ca="1">IF(F107&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I107" s="18" t="s">
+      <c r="I107" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J107" s="15" t="s">
+      <c r="J107" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K107" s="12">
-        <v>46043</v>
-      </c>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="29">
+      <c r="K107" s="10">
+        <v>45639</v>
+      </c>
+      <c r="L107" s="10"/>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10"/>
+      <c r="O107" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A108" s="30" t="s">
+      <c r="A108" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="B108" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" s="12">
-        <v>45839</v>
-      </c>
-      <c r="D108" s="12">
-        <v>46477</v>
-      </c>
-      <c r="E108" s="12">
+      <c r="B108" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="10">
+        <v>44861</v>
+      </c>
+      <c r="D108" s="10">
+        <v>44196</v>
+      </c>
+      <c r="E108" s="10">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F108" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F108" s="12">
         <f ca="1">D108-E108</f>
-        <v>245</v>
-      </c>
-      <c r="G108" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H108" s="18" t="str">
+        <v>-2038</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="H108" s="13" t="str">
         <f ca="1">IF(F108&lt;=0, "VENDA","CAREPACK")</f>
-        <v>CAREPACK</v>
-      </c>
-      <c r="I108" s="18" t="s">
+        <v>VENDA</v>
+      </c>
+      <c r="I108" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J108" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K108" s="12">
-        <v>45639</v>
-      </c>
-      <c r="L108" s="12"/>
-      <c r="M108" s="12"/>
-      <c r="N108" s="12"/>
-      <c r="O108" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A109" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="B109" s="14" t="s">
+      <c r="J108" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" s="10">
+        <v>40801</v>
+      </c>
+      <c r="L108" s="10"/>
+      <c r="M108" s="10"/>
+      <c r="N108" s="10"/>
+      <c r="O108" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B109" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109" s="22">
         <v>44861</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="22">
         <v>44196</v>
       </c>
-      <c r="E109" s="12">
+      <c r="E109" s="22">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F109" s="15">
+        <v>46234</v>
+      </c>
+      <c r="F109" s="23">
         <f ca="1">D109-E109</f>
-        <v>-2036</v>
-      </c>
-      <c r="G109" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="H109" s="18" t="str">
+        <v>-2038</v>
+      </c>
+      <c r="G109" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H109" s="24" t="str">
         <f ca="1">IF(F109&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I109" s="18" t="s">
+      <c r="I109" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J109" s="15" t="s">
+      <c r="J109" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K109" s="12">
-        <v>40801</v>
-      </c>
-      <c r="L109" s="12"/>
-      <c r="M109" s="12"/>
-      <c r="N109" s="12"/>
-      <c r="O109" s="29">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="B110" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" s="35">
-        <v>44861</v>
-      </c>
-      <c r="D110" s="36">
-        <v>44196</v>
-      </c>
-      <c r="E110" s="35">
-        <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="F110" s="37">
-        <f ca="1">D110-E110</f>
-        <v>-2036</v>
-      </c>
-      <c r="G110" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H110" s="39" t="str">
-        <f ca="1">IF(F110&lt;=0, "VENDA","CAREPACK")</f>
-        <v>VENDA</v>
-      </c>
-      <c r="I110" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="J110" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="K110" s="35">
+      <c r="K109" s="22">
         <v>40634</v>
       </c>
-      <c r="L110" s="35"/>
-      <c r="M110" s="35"/>
-      <c r="N110" s="35"/>
-      <c r="O110" s="40">
+      <c r="L109" s="22"/>
+      <c r="M109" s="22"/>
+      <c r="N109" s="22"/>
+      <c r="O109" s="47">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N110" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N110">
-      <sortCondition ref="A1:A110"/>
+  <autoFilter ref="A1:N109" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N109">
+      <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6238,10 +6314,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -6259,16 +6335,16 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
@@ -6276,10 +6352,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="C2" s="3">
         <v>45670</v>
@@ -6290,14 +6366,14 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K2" s="3">
         <v>45670</v>
@@ -6314,10 +6390,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3">
         <v>45670</v>
@@ -6328,14 +6404,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K3" s="3">
         <v>45685</v>
@@ -6352,10 +6428,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3">
         <v>45670</v>
@@ -6366,14 +6442,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K4" s="3">
         <v>45670</v>
@@ -6390,10 +6466,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3">
         <v>45670</v>
@@ -6404,14 +6480,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K5" s="3">
         <v>45670</v>
@@ -6428,10 +6504,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C6" s="3">
         <v>44866</v>
@@ -6442,14 +6518,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K6" s="3">
         <v>42867</v>
@@ -6466,10 +6542,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" s="3">
         <v>45670</v>
@@ -6480,14 +6556,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="3">
         <v>45670</v>
@@ -6504,10 +6580,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" s="3">
         <v>45670</v>
@@ -6518,14 +6594,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="3">
         <v>45670</v>
@@ -6542,10 +6618,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C9" s="3">
         <v>45670</v>
@@ -6556,14 +6632,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K9" s="3">
         <v>45670</v>
@@ -6580,10 +6656,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" s="3">
         <v>44501</v>
@@ -6594,14 +6670,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K10" s="3">
         <v>42949</v>
@@ -6618,10 +6694,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" s="3">
         <v>45670</v>
@@ -6632,14 +6708,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K11" s="3">
         <v>45670</v>
@@ -6659,7 +6735,7 @@
         <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="3">
         <v>45670</v>
@@ -6670,14 +6746,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K12" s="3">
         <v>45670</v>
@@ -6697,7 +6773,7 @@
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="3">
         <v>45658</v>
@@ -6708,14 +6784,14 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K13" s="3">
         <v>42972</v>
@@ -6732,10 +6808,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C14" s="3">
         <v>45670</v>
@@ -6746,14 +6822,14 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K14" s="3">
         <v>45670</v>
@@ -6770,10 +6846,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C15" s="3">
         <v>44911</v>
@@ -6784,14 +6860,14 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K15" s="3">
         <v>41417</v>
@@ -6808,10 +6884,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="3">
         <v>45670</v>
@@ -6822,14 +6898,14 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K16" s="3">
         <v>45670</v>
@@ -6846,10 +6922,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="3">
         <v>45670</v>
@@ -6860,14 +6936,14 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K17" s="3">
         <v>45670</v>
@@ -6884,10 +6960,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="3">
         <v>45670</v>
@@ -6898,14 +6974,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K18" s="3">
         <v>45670</v>
@@ -6922,10 +6998,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C19" s="3">
         <v>45670</v>
@@ -6936,14 +7012,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K19" s="3">
         <v>45670</v>
@@ -6960,10 +7036,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C20" s="3">
         <v>45670</v>
@@ -6974,14 +7050,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K20" s="3">
         <v>45670</v>
@@ -6998,10 +7074,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="3">
         <v>45658</v>
@@ -7012,14 +7088,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K21" s="3">
         <v>40396</v>
@@ -7039,7 +7115,7 @@
         <v>87</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="3">
         <v>45658</v>
@@ -7050,14 +7126,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K22" s="3">
         <v>43783</v>
@@ -7074,10 +7150,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="3">
         <v>44501</v>
@@ -7088,14 +7164,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K23" s="3">
         <v>42119</v>
@@ -7112,10 +7188,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3">
         <v>45670</v>
@@ -7126,14 +7202,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K24" s="3">
         <v>45670</v>
@@ -7150,10 +7226,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3">
         <v>45670</v>
@@ -7164,14 +7240,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K25" s="3">
         <v>45670</v>
@@ -7188,10 +7264,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3">
         <v>45670</v>
@@ -7202,14 +7278,14 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K26" s="3">
         <v>45670</v>
@@ -7226,10 +7302,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C27" s="3">
         <v>45670</v>
@@ -7240,14 +7316,14 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K27" s="3">
         <v>45670</v>
@@ -7264,10 +7340,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="3">
         <v>45658</v>
@@ -7278,14 +7354,14 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K28" s="3">
         <v>39766</v>
@@ -7302,10 +7378,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C29" s="3">
         <v>45658</v>
@@ -7316,14 +7392,14 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K29" s="3">
         <v>41075</v>
@@ -7343,7 +7419,7 @@
         <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3">
         <v>45670</v>
@@ -7354,14 +7430,14 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K30" s="3">
         <v>45670</v>
@@ -7378,10 +7454,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C31" s="3">
         <v>45670</v>
@@ -7392,14 +7468,14 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K31" s="3">
         <v>45670</v>
@@ -7416,10 +7492,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C32" s="3">
         <v>45016</v>
@@ -7430,14 +7506,14 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K32" s="3">
         <v>45016</v>
@@ -7454,10 +7530,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" s="3">
         <v>44743</v>
@@ -7468,14 +7544,14 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K33" s="3">
         <v>42886</v>
@@ -7492,10 +7568,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C34" s="3">
         <v>45670</v>
@@ -7506,14 +7582,14 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K34" s="3">
         <v>45670</v>
@@ -7530,10 +7606,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C35" s="3">
         <v>45009</v>
@@ -7544,14 +7620,14 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K35" s="3">
         <v>45009</v>
@@ -7568,10 +7644,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C36" s="3">
         <v>45658</v>
@@ -7582,14 +7658,14 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K36" s="3">
         <v>43021</v>
@@ -7606,10 +7682,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" s="3">
         <v>45670</v>
@@ -7620,14 +7696,14 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K37" s="3">
         <v>45670</v>
@@ -7644,10 +7720,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" s="3">
         <v>44866</v>
@@ -7658,14 +7734,14 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K38" s="3">
         <v>40389</v>
@@ -7684,4 +7760,181 @@
   <autoFilter ref="A1:N38" xr:uid="{385B57CD-294C-4E76-82E5-66AB1487D8F3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F0E183-23BD-4E35-A5A4-8E836EB7CC84}">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="16" width="12.6328125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="48">
+        <v>2026</v>
+      </c>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="50"/>
+      <c r="E2" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="J2" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="L2" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="M2" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="N2" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="O2" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="P2" s="54" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="49"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D4" s="49"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D5" s="49"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D6" s="49"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D7" s="49"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D8" s="49"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D9" s="49"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D10" s="49"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D11" s="49"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D12" s="49"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D13" s="49"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D14" s="49"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D15" s="49"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D16" s="49"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D17" s="49"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D18" s="49"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D19" s="49"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D20" s="49"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D21" s="49"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D22" s="49"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D23" s="49"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D24" s="49"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D25" s="49"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D26" s="49"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D27" s="49"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D28" s="49"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D29" s="49"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D30" s="49"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D31" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D3:D31"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="594" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AE2008C-C62A-47A0-93AE-71B451950982}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -203,6 +203,9 @@
     <t xml:space="preserve">CCL LABEL </t>
   </si>
   <si>
+    <t>VENDA</t>
+  </si>
+  <si>
     <t>COMPRINT</t>
   </si>
   <si>
@@ -218,6 +221,9 @@
     <t>PREPAY PI HW</t>
   </si>
   <si>
+    <t>OBS: LASER/CILINDROS E CORONA ENVIAR ORÇAMETO DE VENDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIGIPIX   </t>
   </si>
   <si>
@@ -275,6 +281,9 @@
     <t>FTD</t>
   </si>
   <si>
+    <t>15 HRS MENSAIS. EXTRATO MENSAL. FECHAMENTO TRIMESTRAL</t>
+  </si>
+  <si>
     <t>FUTURA EXPRESS</t>
   </si>
   <si>
@@ -533,9 +542,6 @@
     <t>HP INDIGO R3050</t>
   </si>
   <si>
-    <t>VENDA</t>
-  </si>
-  <si>
     <t>SERIES2</t>
   </si>
   <si>
@@ -659,52 +665,46 @@
     <t>ULTRAPRESS EDITORA E GRAFICA</t>
   </si>
   <si>
-    <t>15 HRS MENSAIS. EXTRATO MENSAL. FECHAMENTO TRIMESTRAL</t>
-  </si>
-  <si>
-    <t>OBS: LASER/CILINDROS E CORONA ENVIAR ORÇAMETO DE VENDA</t>
-  </si>
-  <si>
     <t xml:space="preserve">VALOR </t>
   </si>
   <si>
     <t>DATA FAT.</t>
   </si>
   <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SETEMBRO</t>
+  </si>
+  <si>
+    <t>OUTUBRO</t>
+  </si>
+  <si>
+    <t>NOVEMBRO</t>
+  </si>
+  <si>
+    <t>DEZEMBRO</t>
+  </si>
+  <si>
+    <t>JANEIRO</t>
+  </si>
+  <si>
+    <t>FEVEREIRO</t>
+  </si>
+  <si>
+    <t>MARÇO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAIO</t>
+  </si>
+  <si>
+    <t>JUNHO</t>
+  </si>
+  <si>
     <t>JULHO</t>
-  </si>
-  <si>
-    <t>AGOSTO</t>
-  </si>
-  <si>
-    <t>SETEMBRO</t>
-  </si>
-  <si>
-    <t>OUTUBRO</t>
-  </si>
-  <si>
-    <t>NOVEMBRO</t>
-  </si>
-  <si>
-    <t>FEVEREIRO</t>
-  </si>
-  <si>
-    <t>MARÇO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MAIO</t>
-  </si>
-  <si>
-    <t>JUNHO</t>
-  </si>
-  <si>
-    <t>DEZEMBRO</t>
-  </si>
-  <si>
-    <t>JANEIRO</t>
   </si>
 </sst>
 </file>
@@ -993,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1082,29 +1082,10 @@
     <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1128,17 +1109,8 @@
     <xf numFmtId="1" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1149,6 +1121,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1553,25 +1531,25 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="35">
         <v>46046</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="35">
         <v>46234</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="35">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F2" s="25">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>16</v>
@@ -1586,13 +1564,13 @@
       <c r="J2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="42">
+      <c r="K2" s="35">
         <v>45315</v>
       </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="43">
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="36">
         <v>90</v>
       </c>
     </row>
@@ -1611,11 +1589,11 @@
       </c>
       <c r="E3" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1636,7 +1614,7 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
-      <c r="O3" s="44">
+      <c r="O3" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1655,11 +1633,11 @@
       </c>
       <c r="E4" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1680,7 +1658,7 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
-      <c r="O4" s="44">
+      <c r="O4" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1699,11 +1677,11 @@
       </c>
       <c r="E5" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1724,7 +1702,7 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
-      <c r="O5" s="44">
+      <c r="O5" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1743,11 +1721,11 @@
       </c>
       <c r="E6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1768,7 +1746,7 @@
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
-      <c r="O6" s="44">
+      <c r="O6" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1787,11 +1765,11 @@
       </c>
       <c r="E7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1812,7 +1790,7 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="44">
+      <c r="O7" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1831,11 +1809,11 @@
       </c>
       <c r="E8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1853,10 +1831,10 @@
       <c r="K8" s="10">
         <v>45965</v>
       </c>
-      <c r="L8" s="31"/>
+      <c r="L8" s="30"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
-      <c r="O8" s="44">
+      <c r="O8" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1875,11 +1853,11 @@
       </c>
       <c r="E9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-410</v>
+        <v>-413</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1895,10 +1873,10 @@
         <v>18</v>
       </c>
       <c r="K9" s="10"/>
-      <c r="L9" s="31"/>
+      <c r="L9" s="30"/>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="44">
+      <c r="O9" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1917,11 +1895,11 @@
       </c>
       <c r="E10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1939,10 +1917,10 @@
       <c r="K10" s="10">
         <v>45670</v>
       </c>
-      <c r="L10" s="31"/>
+      <c r="L10" s="30"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
-      <c r="O10" s="44">
+      <c r="O10" s="37">
         <v>90</v>
       </c>
     </row>
@@ -1961,11 +1939,11 @@
       </c>
       <c r="E11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1983,10 +1961,10 @@
       <c r="K11" s="10">
         <v>43581</v>
       </c>
-      <c r="L11" s="31"/>
+      <c r="L11" s="30"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="44">
+      <c r="O11" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2005,11 +1983,11 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F12" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -2026,12 +2004,12 @@
       <c r="K12" s="10">
         <v>43224</v>
       </c>
-      <c r="L12" s="31" t="s">
+      <c r="L12" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
-      <c r="O12" s="44">
+      <c r="O12" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2050,11 +2028,11 @@
       </c>
       <c r="E13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -2071,12 +2049,12 @@
       <c r="K13" s="10">
         <v>45149</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
-      <c r="O13" s="44">
+      <c r="O13" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2095,11 +2073,11 @@
       </c>
       <c r="E14" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -2116,10 +2094,10 @@
       <c r="K14" s="10">
         <v>45890</v>
       </c>
-      <c r="L14" s="31"/>
+      <c r="L14" s="30"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
-      <c r="O14" s="44">
+      <c r="O14" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2138,11 +2116,11 @@
       </c>
       <c r="E15" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -2159,12 +2137,12 @@
       <c r="K15" s="10">
         <v>41969</v>
       </c>
-      <c r="L15" s="31" t="s">
+      <c r="L15" s="30" t="s">
         <v>44</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
-      <c r="O15" s="44">
+      <c r="O15" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2183,11 +2161,11 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -2207,7 +2185,7 @@
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
-      <c r="O16" s="44">
+      <c r="O16" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2226,11 +2204,11 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -2250,7 +2228,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
-      <c r="O17" s="44">
+      <c r="O17" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2269,11 +2247,11 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2293,7 +2271,7 @@
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="44">
+      <c r="O18" s="37">
         <v>90</v>
       </c>
     </row>
@@ -2312,17 +2290,17 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>17</v>
@@ -2336,13 +2314,13 @@
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
-      <c r="O19" s="44">
+      <c r="O19" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>20</v>
@@ -2355,11 +2333,11 @@
       </c>
       <c r="E20" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
+        <v>5264</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2379,13 +2357,13 @@
       <c r="L20" s="15"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-      <c r="O20" s="44">
+      <c r="O20" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>15</v>
@@ -2398,11 +2376,11 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2423,13 +2401,13 @@
       <c r="L21" s="15"/>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
-      <c r="O21" s="44">
+      <c r="O21" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>15</v>
@@ -2442,11 +2420,11 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2467,16 +2445,16 @@
       <c r="L22" s="15"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
-      <c r="O22" s="44">
+      <c r="O22" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="10">
         <v>46235</v>
@@ -2486,11 +2464,11 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2500,7 +2478,7 @@
         <v>CAREPACK</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>206</v>
+        <v>59</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>24</v>
@@ -2511,13 +2489,13 @@
       <c r="L23" s="15"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
-      <c r="O23" s="44">
+      <c r="O23" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>20</v>
@@ -2530,21 +2508,21 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F24" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H24" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>18</v>
@@ -2552,18 +2530,18 @@
       <c r="K24" s="11">
         <v>41290</v>
       </c>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="31" t="s">
         <v>44</v>
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="45">
+      <c r="O24" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>20</v>
@@ -2576,21 +2554,21 @@
       </c>
       <c r="E25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H25" s="18" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>VENDA</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>18</v>
@@ -2598,18 +2576,18 @@
       <c r="K25" s="11">
         <v>42989</v>
       </c>
-      <c r="L25" s="32" t="s">
+      <c r="L25" s="31" t="s">
         <v>44</v>
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="45">
+      <c r="O25" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>15</v>
@@ -2622,11 +2600,11 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2636,7 +2614,7 @@
         <v>VENDA</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J26" s="12" t="s">
         <v>24</v>
@@ -2644,18 +2622,18 @@
       <c r="K26" s="10">
         <v>43186</v>
       </c>
-      <c r="L26" s="31" t="s">
+      <c r="L26" s="30" t="s">
         <v>44</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
-      <c r="O26" s="44">
+      <c r="O26" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
@@ -2668,11 +2646,11 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2690,105 +2668,105 @@
       <c r="K27" s="10">
         <v>43923</v>
       </c>
-      <c r="L27" s="31" t="s">
+      <c r="L27" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
-      <c r="O27" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="34" t="s">
+      <c r="O27" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="10">
         <v>45689</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="10">
         <v>51501</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
-      </c>
-      <c r="F28" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5267</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="37" t="s">
+        <v>5264</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="37" t="s">
+      <c r="I28" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="10">
+        <v>42347</v>
+      </c>
+      <c r="L28" s="15"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="J28" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="35">
-        <v>42347</v>
-      </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="46">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="10">
         <v>43891</v>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="10">
         <v>44196</v>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
-      </c>
-      <c r="F29" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
-      </c>
-      <c r="G29" s="36" t="s">
+        <v>-2041</v>
+      </c>
+      <c r="G29" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="37" t="str">
+      <c r="H29" s="13" t="str">
         <f ca="1">IF(F29&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I29" s="37" t="s">
+      <c r="I29" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="36" t="s">
+      <c r="J29" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="10">
         <v>43283</v>
       </c>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="46">
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>15</v>
@@ -2801,14 +2779,14 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H30" s="13" t="str">
         <f ca="1">IF(F30&lt;=0, "VENDA","CAREPACK")</f>
@@ -2826,16 +2804,16 @@
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
-      <c r="O30" s="44">
+      <c r="O30" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="11">
         <v>45928</v>
@@ -2845,11 +2823,11 @@
       </c>
       <c r="E31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F31" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>16</v>
@@ -2870,13 +2848,13 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="45">
+      <c r="O31" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>15</v>
@@ -2889,11 +2867,11 @@
       </c>
       <c r="E32" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2914,13 +2892,13 @@
       <c r="L32" s="10"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
-      <c r="O32" s="44">
+      <c r="O32" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>15</v>
@@ -2933,11 +2911,11 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2955,16 +2933,16 @@
       <c r="K33" s="10">
         <v>44682</v>
       </c>
-      <c r="L33" s="31"/>
+      <c r="L33" s="30"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
-      <c r="O33" s="44">
+      <c r="O33" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>15</v>
@@ -2977,11 +2955,11 @@
       </c>
       <c r="E34" s="10">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -3002,16 +2980,16 @@
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
-      <c r="O34" s="44">
+      <c r="O34" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" s="10">
         <v>45896</v>
@@ -3021,11 +2999,11 @@
       </c>
       <c r="E35" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -3046,56 +3024,56 @@
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
-      <c r="O35" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="34" t="s">
+      <c r="O35" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="10">
         <v>45870</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="10">
         <v>46477</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="F36" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F36" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>243</v>
-      </c>
-      <c r="G36" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="H36" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="37" t="s">
+      <c r="I36" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="K36" s="35">
+      <c r="J36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="10">
         <v>44896</v>
       </c>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="46">
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>20</v>
@@ -3108,14 +3086,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>35</v>
@@ -3124,7 +3102,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K37" s="10">
         <v>46455</v>
@@ -3132,16 +3110,16 @@
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
-      <c r="O37" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O37" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" s="11">
         <v>46235</v>
@@ -3151,24 +3129,24 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F38" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H38" s="18" t="str">
         <f ca="1">IF(F38&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K38" s="11">
         <v>45477</v>
@@ -3176,13 +3154,13 @@
       <c r="L38" s="29"/>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
-      <c r="O38" s="45">
+      <c r="O38" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>15</v>
@@ -3195,11 +3173,11 @@
       </c>
       <c r="E39" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F39" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -3220,13 +3198,13 @@
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
-      <c r="O39" s="44">
+      <c r="O39" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>15</v>
@@ -3239,14 +3217,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F40" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H40" s="13" t="str">
         <f ca="1">IF(F40&lt;=0, "VENDA","CAREPACK")</f>
@@ -3264,13 +3242,13 @@
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
-      <c r="O40" s="44">
+      <c r="O40" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>28</v>
@@ -3283,20 +3261,20 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F41" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>24</v>
@@ -3307,13 +3285,13 @@
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
-      <c r="O41" s="45">
+      <c r="O41" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>15</v>
@@ -3326,11 +3304,11 @@
       </c>
       <c r="E42" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3348,16 +3326,16 @@
       <c r="K42" s="10">
         <v>41166</v>
       </c>
-      <c r="L42" s="31"/>
+      <c r="L42" s="30"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
-      <c r="O42" s="44">
+      <c r="O42" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>15</v>
@@ -3370,11 +3348,11 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F43" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3392,60 +3370,60 @@
       <c r="K43" s="10">
         <v>45625</v>
       </c>
-      <c r="L43" s="31"/>
+      <c r="L43" s="30"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
-      <c r="O43" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="35">
+      <c r="O43" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="10">
         <v>45783</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="10">
         <v>46331</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="F44" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F44" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>97</v>
-      </c>
-      <c r="G44" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" s="37" t="str">
+        <v>94</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="13" t="str">
         <f t="shared" ref="H44:H58" ca="1" si="6">IF(F44&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I44" s="37" t="s">
+      <c r="I44" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="36" t="s">
+      <c r="J44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="10">
         <v>45602</v>
       </c>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="46">
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>15</v>
@@ -3458,11 +3436,11 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F45" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3483,16 +3461,16 @@
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
-      <c r="O45" s="44">
+      <c r="O45" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="10">
         <v>45541</v>
@@ -3502,11 +3480,11 @@
       </c>
       <c r="E46" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F46" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3527,13 +3505,13 @@
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
-      <c r="O46" s="44">
+      <c r="O46" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>15</v>
@@ -3546,11 +3524,11 @@
       </c>
       <c r="E47" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F47" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3571,13 +3549,13 @@
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
-      <c r="O47" s="44">
+      <c r="O47" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>20</v>
@@ -3590,14 +3568,14 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F48" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H48" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -3612,18 +3590,18 @@
       <c r="K48" s="10">
         <v>42781</v>
       </c>
-      <c r="L48" s="31" t="s">
+      <c r="L48" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
-      <c r="O48" s="44">
+      <c r="O48" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>15</v>
@@ -3636,14 +3614,14 @@
       </c>
       <c r="E49" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F49" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H49" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -3661,16 +3639,16 @@
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
-      <c r="O49" s="44">
+      <c r="O49" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" s="10">
         <v>45870</v>
@@ -3680,11 +3658,11 @@
       </c>
       <c r="E50" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F50" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3694,7 +3672,7 @@
         <v>VENDA</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>18</v>
@@ -3702,21 +3680,21 @@
       <c r="K50" s="10">
         <v>42744</v>
       </c>
-      <c r="L50" s="31" t="s">
+      <c r="L50" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
-      <c r="O50" s="44">
+      <c r="O50" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="10">
         <v>45870</v>
@@ -3726,11 +3704,11 @@
       </c>
       <c r="E51" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F51" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3740,7 +3718,7 @@
         <v>VENDA</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>18</v>
@@ -3748,21 +3726,21 @@
       <c r="K51" s="10">
         <v>43733</v>
       </c>
-      <c r="L51" s="31" t="s">
+      <c r="L51" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
-      <c r="O51" s="44">
+      <c r="O51" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C52" s="10">
         <v>46033</v>
@@ -3772,11 +3750,11 @@
       </c>
       <c r="E52" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F52" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3786,7 +3764,7 @@
         <v>VENDA</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>18</v>
@@ -3794,106 +3772,106 @@
       <c r="K52" s="10">
         <v>45849</v>
       </c>
-      <c r="L52" s="31" t="s">
+      <c r="L52" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10"/>
-      <c r="O52" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="34" t="s">
+      <c r="O52" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="10">
         <v>44902</v>
       </c>
-      <c r="D53" s="35">
+      <c r="D53" s="10">
         <v>44196</v>
       </c>
-      <c r="E53" s="35">
+      <c r="E53" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="F53" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F53" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
-      </c>
-      <c r="G53" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="H53" s="37" t="str">
+        <v>-2041</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>VENDA</v>
       </c>
-      <c r="I53" s="37" t="s">
+      <c r="I53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J53" s="36" t="s">
+      <c r="J53" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="35">
+      <c r="K53" s="10">
         <v>41320</v>
       </c>
-      <c r="L53" s="35"/>
-      <c r="M53" s="35"/>
-      <c r="N53" s="35"/>
-      <c r="O53" s="46">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="34" t="s">
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="10">
         <v>46234</v>
       </c>
-      <c r="D54" s="35">
+      <c r="D54" s="10">
         <v>47330</v>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="F54" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F54" s="12">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1096</v>
-      </c>
-      <c r="G54" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="H54" s="37" t="str">
+        <v>1093</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H54" s="13" t="str">
         <f t="shared" ref="H54" ca="1" si="8">IF(F54&lt;=0, "VENDA","CAREPACK")</f>
         <v>CAREPACK</v>
       </c>
-      <c r="I54" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="J54" s="36" t="s">
+      <c r="I54" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J54" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="35">
+      <c r="K54" s="10">
         <v>46234</v>
       </c>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="35"/>
-      <c r="O54" s="46">
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>15</v>
@@ -3906,11 +3884,11 @@
       </c>
       <c r="E55" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F55" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3931,13 +3909,13 @@
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
-      <c r="O55" s="44">
+      <c r="O55" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>15</v>
@@ -3950,14 +3928,14 @@
       </c>
       <c r="E56" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F56" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H56" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -3975,13 +3953,13 @@
       <c r="L56" s="10"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
-      <c r="O56" s="44">
+      <c r="O56" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>15</v>
@@ -3994,14 +3972,14 @@
       </c>
       <c r="E57" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F57" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H57" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4019,13 +3997,13 @@
       <c r="L57" s="10"/>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
-      <c r="O57" s="44">
+      <c r="O57" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>15</v>
@@ -4038,11 +4016,11 @@
       </c>
       <c r="E58" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F58" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -4063,13 +4041,13 @@
       <c r="L58" s="10"/>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
-      <c r="O58" s="44">
+      <c r="O58" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>20</v>
@@ -4082,11 +4060,11 @@
       </c>
       <c r="E59" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F59" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -4095,7 +4073,7 @@
         <v>35</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>24</v>
@@ -4106,13 +4084,13 @@
       <c r="L59" s="10"/>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
-      <c r="O59" s="44">
+      <c r="O59" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>15</v>
@@ -4125,11 +4103,11 @@
       </c>
       <c r="E60" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F60" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -4150,13 +4128,13 @@
       <c r="L60" s="15"/>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
-      <c r="O60" s="44">
+      <c r="O60" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>20</v>
@@ -4169,14 +4147,14 @@
       </c>
       <c r="E61" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F61" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H61" s="13" t="str">
         <f ca="1">IF(F61&lt;=0, "VENDA","CAREPACK")</f>
@@ -4194,13 +4172,13 @@
       <c r="L61" s="10"/>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
-      <c r="O61" s="44">
+      <c r="O61" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>15</v>
@@ -4213,14 +4191,14 @@
       </c>
       <c r="E62" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F62" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H62" s="13" t="str">
         <f ca="1">IF(F62&lt;=0, "VENDA","CAREPACK")</f>
@@ -4238,13 +4216,13 @@
       <c r="L62" s="10"/>
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
-      <c r="O62" s="44">
+      <c r="O62" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>15</v>
@@ -4257,14 +4235,14 @@
       </c>
       <c r="E63" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F63" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H63" s="13" t="str">
         <f ca="1">IF(F63&lt;=0, "VENDA","CAREPACK")</f>
@@ -4282,13 +4260,13 @@
       <c r="L63" s="10"/>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
-      <c r="O63" s="44">
+      <c r="O63" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>15</v>
@@ -4301,11 +4279,11 @@
       </c>
       <c r="E64" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F64" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>-152</v>
+        <v>-155</v>
       </c>
       <c r="G64" s="17" t="s">
         <v>16</v>
@@ -4326,13 +4304,13 @@
       <c r="L64" s="11"/>
       <c r="M64" s="11"/>
       <c r="N64" s="11"/>
-      <c r="O64" s="45">
+      <c r="O64" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>20</v>
@@ -4345,20 +4323,20 @@
       </c>
       <c r="E65" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F65" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H65" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>24</v>
@@ -4369,13 +4347,13 @@
       <c r="L65" s="10"/>
       <c r="M65" s="10"/>
       <c r="N65" s="10"/>
-      <c r="O65" s="44">
+      <c r="O65" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>15</v>
@@ -4388,11 +4366,11 @@
       </c>
       <c r="E66" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F66" s="12">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4413,13 +4391,13 @@
       <c r="L66" s="10"/>
       <c r="M66" s="10"/>
       <c r="N66" s="10"/>
-      <c r="O66" s="44">
+      <c r="O66" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>15</v>
@@ -4432,14 +4410,14 @@
       </c>
       <c r="E67" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F67" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H67" s="13" t="str">
         <f ca="1">IF(F67&lt;=0, "VENDA","CAREPACK")</f>
@@ -4457,57 +4435,57 @@
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
       <c r="N67" s="10"/>
-      <c r="O67" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="B68" s="34" t="s">
+      <c r="O67" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A68" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B68" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="35">
+      <c r="C68" s="10">
         <v>45719</v>
       </c>
-      <c r="D68" s="35">
+      <c r="D68" s="10">
         <v>44196</v>
       </c>
-      <c r="E68" s="35">
+      <c r="E68" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46234</v>
-      </c>
-      <c r="F68" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F68" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2038</v>
-      </c>
-      <c r="G68" s="36" t="s">
+        <v>-2041</v>
+      </c>
+      <c r="G68" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="37" t="str">
+      <c r="H68" s="13" t="str">
         <f ca="1">IF(F68&lt;=0, "VENDA","CAREPACK")</f>
         <v>VENDA</v>
       </c>
-      <c r="I68" s="37" t="s">
+      <c r="I68" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="36" t="s">
+      <c r="J68" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K68" s="35">
+      <c r="K68" s="10">
         <v>43661</v>
       </c>
-      <c r="L68" s="35"/>
-      <c r="M68" s="35"/>
-      <c r="N68" s="35"/>
-      <c r="O68" s="46">
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B69" s="14"/>
       <c r="C69" s="10"/>
@@ -4524,13 +4502,13 @@
       <c r="L69" s="10"/>
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
-      <c r="O69" s="44">
+      <c r="O69" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>15</v>
@@ -4543,11 +4521,11 @@
       </c>
       <c r="E70" s="11">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F70" s="17">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G70" s="17" t="s">
         <v>22</v>
@@ -4566,13 +4544,13 @@
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
-      <c r="O70" s="45">
+      <c r="O70" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>20</v>
@@ -4585,11 +4563,11 @@
       </c>
       <c r="E71" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F71" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4598,7 +4576,7 @@
         <v>35</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>24</v>
@@ -4607,17 +4585,17 @@
         <v>44841</v>
       </c>
       <c r="L71" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10"/>
-      <c r="O71" s="44">
+      <c r="O71" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>20</v>
@@ -4630,14 +4608,14 @@
       </c>
       <c r="E72" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F72" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H72" s="13" t="str">
         <f ca="1">IF(F72&lt;=0, "VENDA","CAREPACK")</f>
@@ -4655,13 +4633,13 @@
       <c r="L72" s="10"/>
       <c r="M72" s="10"/>
       <c r="N72" s="10"/>
-      <c r="O72" s="44">
+      <c r="O72" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>20</v>
@@ -4674,11 +4652,11 @@
       </c>
       <c r="E73" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F73" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4699,42 +4677,42 @@
       <c r="L73" s="10"/>
       <c r="M73" s="10"/>
       <c r="N73" s="10"/>
-      <c r="O73" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B74" s="34" t="s">
+      <c r="O73" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36" t="s">
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="J74" s="36" t="s">
+      <c r="H74" s="13"/>
+      <c r="I74" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="J74" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K74" s="35"/>
-      <c r="L74" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="M74" s="35"/>
-      <c r="N74" s="35"/>
-      <c r="O74" s="46"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="37"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>15</v>
@@ -4747,11 +4725,11 @@
       </c>
       <c r="E75" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F75" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>32</v>
@@ -4770,20 +4748,20 @@
         <v>45999</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10"/>
-      <c r="O75" s="44">
+      <c r="O75" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C76" s="10">
         <v>45555</v>
@@ -4793,14 +4771,14 @@
       </c>
       <c r="E76" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F76" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H76" s="13" t="str">
         <f ca="1">IF(F76&lt;=0, "VENDA","CAREPACK")</f>
@@ -4816,17 +4794,17 @@
         <v>45371</v>
       </c>
       <c r="L76" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10"/>
-      <c r="O76" s="44">
+      <c r="O76" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>15</v>
@@ -4839,11 +4817,11 @@
       </c>
       <c r="E77" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F77" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>23</v>
@@ -4862,17 +4840,17 @@
         <v>45273</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10"/>
-      <c r="O77" s="44">
+      <c r="O77" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>51</v>
@@ -4885,20 +4863,20 @@
       </c>
       <c r="E78" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F78" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>24</v>
@@ -4907,17 +4885,17 @@
         <v>45989</v>
       </c>
       <c r="L78" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10"/>
-      <c r="O78" s="44">
+      <c r="O78" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>15</v>
@@ -4930,11 +4908,11 @@
       </c>
       <c r="E79" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F79" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>34</v>
@@ -4944,7 +4922,7 @@
         <v>VENDA</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>24</v>
@@ -4955,13 +4933,13 @@
       <c r="L79" s="10"/>
       <c r="M79" s="10"/>
       <c r="N79" s="10"/>
-      <c r="O79" s="44">
+      <c r="O79" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>15</v>
@@ -4974,14 +4952,14 @@
       </c>
       <c r="E80" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F80" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H80" s="13" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -4999,13 +4977,13 @@
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
       <c r="N80" s="10"/>
-      <c r="O80" s="44">
+      <c r="O80" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>15</v>
@@ -5018,11 +4996,11 @@
       </c>
       <c r="E81" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F81" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -5043,13 +5021,13 @@
       <c r="L81" s="10"/>
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
-      <c r="O81" s="44">
+      <c r="O81" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>15</v>
@@ -5062,11 +5040,11 @@
       </c>
       <c r="E82" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F82" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>26</v>
@@ -5087,16 +5065,16 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
-      <c r="O82" s="44">
+      <c r="O82" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C83" s="10">
         <v>45870</v>
@@ -5106,11 +5084,11 @@
       </c>
       <c r="E83" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F83" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>22</v>
@@ -5131,16 +5109,16 @@
       <c r="L83" s="10"/>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
-      <c r="O83" s="44">
+      <c r="O83" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C84" s="10">
         <v>46054</v>
@@ -5150,11 +5128,11 @@
       </c>
       <c r="E84" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F84" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>16</v>
@@ -5175,13 +5153,13 @@
       <c r="L84" s="10"/>
       <c r="M84" s="10"/>
       <c r="N84" s="10"/>
-      <c r="O84" s="44">
+      <c r="O84" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>28</v>
@@ -5194,38 +5172,38 @@
       </c>
       <c r="E85" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F85" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H85" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10"/>
-      <c r="O85" s="44">
+      <c r="O85" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C86" s="10">
         <v>46082</v>
@@ -5235,11 +5213,11 @@
       </c>
       <c r="E86" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F86" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>34</v>
@@ -5248,7 +5226,7 @@
         <v>35</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J86" s="12" t="s">
         <v>24</v>
@@ -5259,13 +5237,13 @@
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
-      <c r="O86" s="44">
+      <c r="O86" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>20</v>
@@ -5278,23 +5256,23 @@
       </c>
       <c r="E87" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F87" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H87" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K87" s="10">
         <v>45691</v>
@@ -5302,13 +5280,13 @@
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
-      <c r="O87" s="44">
+      <c r="O87" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>15</v>
@@ -5321,11 +5299,11 @@
       </c>
       <c r="E88" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F88" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>21</v>
@@ -5346,13 +5324,13 @@
       <c r="L88" s="10"/>
       <c r="M88" s="10"/>
       <c r="N88" s="10"/>
-      <c r="O88" s="44">
+      <c r="O88" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>15</v>
@@ -5365,11 +5343,11 @@
       </c>
       <c r="E89" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F89" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>31</v>
@@ -5390,16 +5368,16 @@
       <c r="L89" s="10"/>
       <c r="M89" s="10"/>
       <c r="N89" s="10"/>
-      <c r="O89" s="44">
+      <c r="O89" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C90" s="10">
         <v>46199</v>
@@ -5409,20 +5387,20 @@
       </c>
       <c r="E90" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F90" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J90" s="12" t="s">
         <v>18</v>
@@ -5431,16 +5409,16 @@
       <c r="L90" s="10"/>
       <c r="M90" s="10"/>
       <c r="N90" s="10"/>
-      <c r="O90" s="44">
+      <c r="O90" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C91" s="10">
         <v>45822</v>
@@ -5450,11 +5428,11 @@
       </c>
       <c r="E91" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F91" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>22</v>
@@ -5475,16 +5453,16 @@
       <c r="L91" s="10"/>
       <c r="M91" s="10"/>
       <c r="N91" s="10"/>
-      <c r="O91" s="44">
+      <c r="O91" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C92" s="10">
         <v>45993</v>
@@ -5494,11 +5472,11 @@
       </c>
       <c r="E92" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F92" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>16</v>
@@ -5519,13 +5497,13 @@
       <c r="L92" s="10"/>
       <c r="M92" s="10"/>
       <c r="N92" s="10"/>
-      <c r="O92" s="44">
+      <c r="O92" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>15</v>
@@ -5538,14 +5516,14 @@
       </c>
       <c r="E93" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F93" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H93" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5563,16 +5541,16 @@
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
       <c r="N93" s="10"/>
-      <c r="O93" s="44">
+      <c r="O93" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C94" s="11">
         <v>45908</v>
@@ -5582,11 +5560,11 @@
       </c>
       <c r="E94" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F94" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G94" s="17" t="s">
         <v>26</v>
@@ -5596,7 +5574,7 @@
         <v>CAREPACK</v>
       </c>
       <c r="I94" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J94" s="17" t="s">
         <v>18</v>
@@ -5605,17 +5583,17 @@
         <v>45055</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
-      <c r="O94" s="45">
+      <c r="O94" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B95" s="16" t="s">
         <v>51</v>
@@ -5628,11 +5606,11 @@
       </c>
       <c r="E95" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F95" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G95" s="17" t="s">
         <v>16</v>
@@ -5642,7 +5620,7 @@
         <v>CAREPACK</v>
       </c>
       <c r="I95" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J95" s="17" t="s">
         <v>18</v>
@@ -5651,17 +5629,17 @@
         <v>45908</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M95" s="11"/>
       <c r="N95" s="11"/>
-      <c r="O95" s="45">
+      <c r="O95" s="38">
         <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>15</v>
@@ -5674,11 +5652,11 @@
       </c>
       <c r="E96" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F96" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>31</v>
@@ -5699,57 +5677,57 @@
       <c r="L96" s="10"/>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
-      <c r="O96" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B97" s="34" t="s">
+      <c r="O96" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B97" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C97" s="35">
+      <c r="C97" s="10">
         <v>45962</v>
       </c>
-      <c r="D97" s="35">
+      <c r="D97" s="10">
         <v>46537</v>
       </c>
-      <c r="E97" s="35">
+      <c r="E97" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
-      </c>
-      <c r="F97" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F97" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>303</v>
-      </c>
-      <c r="G97" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="G97" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H97" s="37" t="str">
+      <c r="H97" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I97" s="37" t="s">
+      <c r="I97" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="36" t="s">
+      <c r="J97" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K97" s="35">
+      <c r="K97" s="10">
         <v>43301</v>
       </c>
-      <c r="L97" s="35"/>
-      <c r="M97" s="35"/>
-      <c r="N97" s="35"/>
-      <c r="O97" s="46">
+      <c r="L97" s="10"/>
+      <c r="M97" s="10"/>
+      <c r="N97" s="10"/>
+      <c r="O97" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>15</v>
@@ -5762,11 +5740,11 @@
       </c>
       <c r="E98" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F98" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>21</v>
@@ -5787,16 +5765,16 @@
       <c r="L98" s="10"/>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
-      <c r="O98" s="44">
+      <c r="O98" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C99" s="10">
         <v>45874</v>
@@ -5806,14 +5784,14 @@
       </c>
       <c r="E99" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F99" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H99" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5831,13 +5809,13 @@
       <c r="L99" s="10"/>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
-      <c r="O99" s="44">
+      <c r="O99" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>15</v>
@@ -5850,11 +5828,11 @@
       </c>
       <c r="E100" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F100" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>31</v>
@@ -5875,16 +5853,16 @@
       <c r="L100" s="10"/>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
-      <c r="O100" s="44">
+      <c r="O100" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C101" s="10">
         <v>45315</v>
@@ -5894,14 +5872,14 @@
       </c>
       <c r="E101" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F101" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H101" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5919,13 +5897,13 @@
       <c r="L101" s="10"/>
       <c r="M101" s="10"/>
       <c r="N101" s="10"/>
-      <c r="O101" s="44">
+      <c r="O101" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>20</v>
@@ -5938,21 +5916,21 @@
       </c>
       <c r="E102" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F102" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H102" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J102" s="12" t="s">
         <v>18</v>
@@ -5963,16 +5941,16 @@
       <c r="L102" s="10"/>
       <c r="M102" s="10"/>
       <c r="N102" s="10"/>
-      <c r="O102" s="44">
+      <c r="O102" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C103" s="10">
         <v>45928</v>
@@ -5982,11 +5960,11 @@
       </c>
       <c r="E103" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F103" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>16</v>
@@ -6007,57 +5985,57 @@
       <c r="L103" s="10"/>
       <c r="M103" s="10"/>
       <c r="N103" s="10"/>
-      <c r="O103" s="44">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="B104" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C104" s="35">
+      <c r="O103" s="37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A104" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" s="10">
         <v>45757</v>
       </c>
-      <c r="D104" s="35">
+      <c r="D104" s="10">
         <v>46669</v>
       </c>
-      <c r="E104" s="35">
+      <c r="E104" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46234</v>
-      </c>
-      <c r="F104" s="36">
+        <v>46237</v>
+      </c>
+      <c r="F104" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>435</v>
-      </c>
-      <c r="G104" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="H104" s="37" t="str">
+        <v>432</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="H104" s="13" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>CAREPACK</v>
       </c>
-      <c r="I104" s="37" t="s">
+      <c r="I104" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J104" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="K104" s="35">
+      <c r="J104" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K104" s="10">
         <v>45575</v>
       </c>
-      <c r="L104" s="35"/>
-      <c r="M104" s="35"/>
-      <c r="N104" s="35"/>
-      <c r="O104" s="46">
+      <c r="L104" s="10"/>
+      <c r="M104" s="10"/>
+      <c r="N104" s="10"/>
+      <c r="O104" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>20</v>
@@ -6070,11 +6048,11 @@
       </c>
       <c r="E105" s="10">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F105" s="12">
         <f ca="1">D105-E105</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -6095,13 +6073,13 @@
       <c r="L105" s="10"/>
       <c r="M105" s="10"/>
       <c r="N105" s="10"/>
-      <c r="O105" s="44">
+      <c r="O105" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>20</v>
@@ -6114,11 +6092,11 @@
       </c>
       <c r="E106" s="10">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F106" s="12">
         <f ca="1">D106-E106</f>
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -6139,13 +6117,13 @@
       <c r="L106" s="10"/>
       <c r="M106" s="10"/>
       <c r="N106" s="10"/>
-      <c r="O106" s="44">
+      <c r="O106" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>20</v>
@@ -6158,11 +6136,11 @@
       </c>
       <c r="E107" s="10">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F107" s="12">
         <f ca="1">D107-E107</f>
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -6183,13 +6161,13 @@
       <c r="L107" s="10"/>
       <c r="M107" s="10"/>
       <c r="N107" s="10"/>
-      <c r="O107" s="44">
+      <c r="O107" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>15</v>
@@ -6202,14 +6180,14 @@
       </c>
       <c r="E108" s="10">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F108" s="12">
         <f ca="1">D108-E108</f>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H108" s="13" t="str">
         <f ca="1">IF(F108&lt;=0, "VENDA","CAREPACK")</f>
@@ -6227,15 +6205,15 @@
       <c r="L108" s="10"/>
       <c r="M108" s="10"/>
       <c r="N108" s="10"/>
-      <c r="O108" s="44">
+      <c r="O108" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B109" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B109" s="32" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="22">
@@ -6246,11 +6224,11 @@
       </c>
       <c r="E109" s="22">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F109" s="23">
         <f ca="1">D109-E109</f>
-        <v>-2038</v>
+        <v>-2041</v>
       </c>
       <c r="G109" s="23" t="s">
         <v>31</v>
@@ -6271,7 +6249,7 @@
       <c r="L109" s="22"/>
       <c r="M109" s="22"/>
       <c r="N109" s="22"/>
-      <c r="O109" s="47">
+      <c r="O109" s="39">
         <v>90</v>
       </c>
     </row>
@@ -6314,10 +6292,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -6335,16 +6313,16 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
@@ -6352,10 +6330,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3">
         <v>45670</v>
@@ -6366,14 +6344,14 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K2" s="3">
         <v>45670</v>
@@ -6390,10 +6368,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3">
         <v>45670</v>
@@ -6404,14 +6382,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K3" s="3">
         <v>45685</v>
@@ -6428,10 +6406,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C4" s="3">
         <v>45670</v>
@@ -6442,14 +6420,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K4" s="3">
         <v>45670</v>
@@ -6466,10 +6444,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" s="3">
         <v>45670</v>
@@ -6480,14 +6458,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K5" s="3">
         <v>45670</v>
@@ -6504,10 +6482,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3">
         <v>44866</v>
@@ -6518,14 +6496,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K6" s="3">
         <v>42867</v>
@@ -6542,10 +6520,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3">
         <v>45670</v>
@@ -6556,14 +6534,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K7" s="3">
         <v>45670</v>
@@ -6580,10 +6558,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C8" s="3">
         <v>45670</v>
@@ -6594,14 +6572,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K8" s="3">
         <v>45670</v>
@@ -6618,10 +6596,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C9" s="3">
         <v>45670</v>
@@ -6632,14 +6610,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K9" s="3">
         <v>45670</v>
@@ -6656,10 +6634,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C10" s="3">
         <v>44501</v>
@@ -6670,14 +6648,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K10" s="3">
         <v>42949</v>
@@ -6694,10 +6672,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C11" s="3">
         <v>45670</v>
@@ -6708,14 +6686,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K11" s="3">
         <v>45670</v>
@@ -6732,10 +6710,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C12" s="3">
         <v>45670</v>
@@ -6746,14 +6724,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K12" s="3">
         <v>45670</v>
@@ -6770,10 +6748,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C13" s="3">
         <v>45658</v>
@@ -6784,14 +6762,14 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K13" s="3">
         <v>42972</v>
@@ -6808,10 +6786,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C14" s="3">
         <v>45670</v>
@@ -6822,14 +6800,14 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K14" s="3">
         <v>45670</v>
@@ -6846,10 +6824,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C15" s="3">
         <v>44911</v>
@@ -6860,14 +6838,14 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K15" s="3">
         <v>41417</v>
@@ -6884,10 +6862,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3">
         <v>45670</v>
@@ -6898,14 +6876,14 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K16" s="3">
         <v>45670</v>
@@ -6922,10 +6900,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C17" s="3">
         <v>45670</v>
@@ -6936,14 +6914,14 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K17" s="3">
         <v>45670</v>
@@ -6960,10 +6938,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C18" s="3">
         <v>45670</v>
@@ -6974,14 +6952,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K18" s="3">
         <v>45670</v>
@@ -6998,10 +6976,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C19" s="3">
         <v>45670</v>
@@ -7012,14 +6990,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K19" s="3">
         <v>45670</v>
@@ -7036,10 +7014,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C20" s="3">
         <v>45670</v>
@@ -7050,14 +7028,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K20" s="3">
         <v>45670</v>
@@ -7074,10 +7052,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C21" s="3">
         <v>45658</v>
@@ -7088,14 +7066,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K21" s="3">
         <v>40396</v>
@@ -7112,10 +7090,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C22" s="3">
         <v>45658</v>
@@ -7126,14 +7104,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K22" s="3">
         <v>43783</v>
@@ -7150,10 +7128,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C23" s="3">
         <v>44501</v>
@@ -7164,14 +7142,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K23" s="3">
         <v>42119</v>
@@ -7188,10 +7166,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3">
         <v>45670</v>
@@ -7202,14 +7180,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3">
         <v>45670</v>
@@ -7226,10 +7204,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3">
         <v>45670</v>
@@ -7240,14 +7218,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K25" s="3">
         <v>45670</v>
@@ -7264,10 +7242,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3">
         <v>45670</v>
@@ -7278,14 +7256,14 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3">
         <v>45670</v>
@@ -7302,10 +7280,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3">
         <v>45670</v>
@@ -7316,14 +7294,14 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K27" s="3">
         <v>45670</v>
@@ -7340,10 +7318,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C28" s="3">
         <v>45658</v>
@@ -7354,14 +7332,14 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K28" s="3">
         <v>39766</v>
@@ -7378,10 +7356,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C29" s="3">
         <v>45658</v>
@@ -7392,14 +7370,14 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K29" s="3">
         <v>41075</v>
@@ -7416,10 +7394,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3">
         <v>45670</v>
@@ -7430,14 +7408,14 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K30" s="3">
         <v>45670</v>
@@ -7454,10 +7432,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3">
         <v>45670</v>
@@ -7468,14 +7446,14 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K31" s="3">
         <v>45670</v>
@@ -7492,10 +7470,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3">
         <v>45016</v>
@@ -7506,14 +7484,14 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K32" s="3">
         <v>45016</v>
@@ -7530,10 +7508,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C33" s="3">
         <v>44743</v>
@@ -7544,14 +7522,14 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K33" s="3">
         <v>42886</v>
@@ -7568,10 +7546,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3">
         <v>45670</v>
@@ -7582,14 +7560,14 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K34" s="3">
         <v>45670</v>
@@ -7606,10 +7584,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C35" s="3">
         <v>45009</v>
@@ -7620,14 +7598,14 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K35" s="3">
         <v>45009</v>
@@ -7644,10 +7622,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3">
         <v>45658</v>
@@ -7658,14 +7636,14 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K36" s="3">
         <v>43021</v>
@@ -7682,10 +7660,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C37" s="3">
         <v>45670</v>
@@ -7696,14 +7674,14 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K37" s="3">
         <v>45670</v>
@@ -7720,10 +7698,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C38" s="3">
         <v>44866</v>
@@ -7734,14 +7712,14 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K38" s="3">
         <v>40389</v>
@@ -7767,167 +7745,167 @@
   <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.6328125" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="16" width="12.6328125" style="7" customWidth="1"/>
+    <col min="5" max="16" width="12.54296875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="48">
+      <c r="A1" s="45"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="46">
         <v>2026</v>
       </c>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:16" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="53" t="s">
+      <c r="D2" s="40"/>
+      <c r="E2" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="G2" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="H2" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="I2" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="J2" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="O2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="P2" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="L2" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="M2" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="N2" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="O2" s="54" t="s">
-        <v>218</v>
-      </c>
-      <c r="P2" s="54" t="s">
-        <v>209</v>
-      </c>
     </row>
     <row r="3" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="49"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D4" s="49"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D5" s="49"/>
+      <c r="D5" s="45"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D6" s="49"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D7" s="49"/>
+      <c r="D7" s="45"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D8" s="49"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D9" s="49"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D10" s="49"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D11" s="49"/>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D12" s="49"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D13" s="49"/>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D14" s="49"/>
+      <c r="D14" s="45"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D15" s="49"/>
+      <c r="D15" s="45"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D16" s="49"/>
+      <c r="D16" s="45"/>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D17" s="49"/>
+      <c r="D17" s="45"/>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D18" s="49"/>
+      <c r="D18" s="45"/>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D19" s="49"/>
+      <c r="D19" s="45"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D20" s="49"/>
+      <c r="D20" s="45"/>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D21" s="49"/>
+      <c r="D21" s="45"/>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D22" s="49"/>
+      <c r="D22" s="45"/>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D23" s="49"/>
+      <c r="D23" s="45"/>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D24" s="49"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D25" s="49"/>
+      <c r="D25" s="45"/>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D26" s="49"/>
+      <c r="D26" s="45"/>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D27" s="49"/>
+      <c r="D27" s="45"/>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D28" s="49"/>
+      <c r="D28" s="45"/>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D29" s="49"/>
+      <c r="D29" s="45"/>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D30" s="49"/>
+      <c r="D30" s="45"/>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D31" s="49"/>
+      <c r="D31" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="594" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AE2008C-C62A-47A0-93AE-71B451950982}"/>
+  <xr:revisionPtr revIDLastSave="600" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BFBF81B-63A6-48BE-9B70-78C115B5ED49}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -3651,10 +3651,10 @@
         <v>58</v>
       </c>
       <c r="C50" s="10">
-        <v>45870</v>
+        <v>46235</v>
       </c>
       <c r="D50" s="10">
-        <v>46234</v>
+        <v>46599</v>
       </c>
       <c r="E50" s="10">
         <f t="shared" ca="1" si="4"/>
@@ -3662,14 +3662,14 @@
       </c>
       <c r="F50" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>362</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I50" s="13" t="s">
         <v>95</v>
@@ -3697,10 +3697,10 @@
         <v>58</v>
       </c>
       <c r="C51" s="10">
-        <v>45870</v>
+        <v>46235</v>
       </c>
       <c r="D51" s="10">
-        <v>46234</v>
+        <v>46599</v>
       </c>
       <c r="E51" s="10">
         <f t="shared" ca="1" si="4"/>
@@ -3708,14 +3708,14 @@
       </c>
       <c r="F51" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>362</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>95</v>
@@ -3743,10 +3743,10 @@
         <v>58</v>
       </c>
       <c r="C52" s="10">
-        <v>46033</v>
+        <v>46235</v>
       </c>
       <c r="D52" s="10">
-        <v>46213</v>
+        <v>46599</v>
       </c>
       <c r="E52" s="10">
         <f t="shared" ca="1" si="4"/>
@@ -3754,14 +3754,14 @@
       </c>
       <c r="F52" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-24</v>
+        <v>362</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="13" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I52" s="13" t="s">
         <v>95</v>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="600" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BFBF81B-63A6-48BE-9B70-78C115B5ED49}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44922D05-E05D-4E63-82AD-D6AFACE39A79}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
@@ -1538,25 +1538,25 @@
         <v>15</v>
       </c>
       <c r="C2" s="35">
-        <v>46046</v>
+        <v>46235</v>
       </c>
       <c r="D2" s="35">
-        <v>46234</v>
+        <v>46599</v>
       </c>
       <c r="E2" s="35">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F2" s="25">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>-3</v>
+        <v>361</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="26" t="str">
         <f t="shared" ref="H2:H11" ca="1" si="2">IF(F2&lt;=0,"VENDA","CAREPACK")</f>
-        <v>VENDA</v>
+        <v>CAREPACK</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>17</v>
@@ -1589,11 +1589,11 @@
       </c>
       <c r="E3" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1633,11 +1633,11 @@
       </c>
       <c r="E4" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1677,11 +1677,11 @@
       </c>
       <c r="E5" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="E6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1765,11 +1765,11 @@
       </c>
       <c r="E7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="E8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1853,11 +1853,11 @@
       </c>
       <c r="E9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-413</v>
+        <v>-414</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1895,11 +1895,11 @@
       </c>
       <c r="E10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="E11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F12" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -2028,11 +2028,11 @@
       </c>
       <c r="E13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="E14" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -2116,11 +2116,11 @@
       </c>
       <c r="E15" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -2204,11 +2204,11 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2290,11 +2290,11 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
@@ -2333,11 +2333,11 @@
       </c>
       <c r="E20" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2376,11 +2376,11 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2420,11 +2420,11 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2464,11 +2464,11 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2508,11 +2508,11 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F24" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>61</v>
@@ -2554,11 +2554,11 @@
       </c>
       <c r="E25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>61</v>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2692,11 +2692,11 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>65</v>
@@ -2735,11 +2735,11 @@
       </c>
       <c r="E29" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>32</v>
@@ -2779,11 +2779,11 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>68</v>
@@ -2823,11 +2823,11 @@
       </c>
       <c r="E31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F31" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>16</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="E32" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2911,11 +2911,11 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="E34" s="10">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -2999,11 +2999,11 @@
       </c>
       <c r="E35" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>75</v>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>77</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F38" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>75</v>
@@ -3173,11 +3173,11 @@
       </c>
       <c r="E39" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F39" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -3217,11 +3217,11 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F40" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>81</v>
@@ -3261,11 +3261,11 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F41" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G41" s="17" t="s">
         <v>83</v>
@@ -3304,11 +3304,11 @@
       </c>
       <c r="E42" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3348,11 +3348,11 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F43" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F44" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>88</v>
@@ -3436,11 +3436,11 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F45" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="E46" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F46" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3524,11 +3524,11 @@
       </c>
       <c r="E47" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F47" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3568,11 +3568,11 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F48" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>65</v>
@@ -3614,11 +3614,11 @@
       </c>
       <c r="E49" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F49" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>65</v>
@@ -3658,11 +3658,11 @@
       </c>
       <c r="E50" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F50" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3704,11 +3704,11 @@
       </c>
       <c r="E51" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F51" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3750,11 +3750,11 @@
       </c>
       <c r="E52" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F52" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3796,11 +3796,11 @@
       </c>
       <c r="E53" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F53" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>81</v>
@@ -3840,11 +3840,11 @@
       </c>
       <c r="E54" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F54" s="12">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>98</v>
@@ -3884,11 +3884,11 @@
       </c>
       <c r="E55" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F55" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3928,11 +3928,11 @@
       </c>
       <c r="E56" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F56" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>102</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="E57" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F57" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>65</v>
@@ -4016,11 +4016,11 @@
       </c>
       <c r="E58" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F58" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -4060,11 +4060,11 @@
       </c>
       <c r="E59" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F59" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -4103,11 +4103,11 @@
       </c>
       <c r="E60" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F60" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="E61" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F61" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>68</v>
@@ -4191,11 +4191,11 @@
       </c>
       <c r="E62" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F62" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>109</v>
@@ -4235,11 +4235,11 @@
       </c>
       <c r="E63" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F63" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G63" s="12" t="s">
         <v>68</v>
@@ -4279,11 +4279,11 @@
       </c>
       <c r="E64" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F64" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-156</v>
       </c>
       <c r="G64" s="17" t="s">
         <v>16</v>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="E65" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F65" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>65</v>
@@ -4366,11 +4366,11 @@
       </c>
       <c r="E66" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F66" s="12">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4410,11 +4410,11 @@
       </c>
       <c r="E67" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F67" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>65</v>
@@ -4454,11 +4454,11 @@
       </c>
       <c r="E68" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F68" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>32</v>
@@ -4521,11 +4521,11 @@
       </c>
       <c r="E70" s="11">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F70" s="17">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G70" s="17" t="s">
         <v>22</v>
@@ -4563,11 +4563,11 @@
       </c>
       <c r="E71" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F71" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4608,11 +4608,11 @@
       </c>
       <c r="E72" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F72" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>68</v>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E73" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F73" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4725,11 +4725,11 @@
       </c>
       <c r="E75" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F75" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>32</v>
@@ -4771,11 +4771,11 @@
       </c>
       <c r="E76" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F76" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>88</v>
@@ -4817,11 +4817,11 @@
       </c>
       <c r="E77" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F77" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>23</v>
@@ -4863,11 +4863,11 @@
       </c>
       <c r="E78" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F78" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>98</v>
@@ -4908,11 +4908,11 @@
       </c>
       <c r="E79" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F79" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>34</v>
@@ -4952,11 +4952,11 @@
       </c>
       <c r="E80" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F80" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>68</v>
@@ -4996,11 +4996,11 @@
       </c>
       <c r="E81" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F81" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -5040,11 +5040,11 @@
       </c>
       <c r="E82" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F82" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>26</v>
@@ -5084,11 +5084,11 @@
       </c>
       <c r="E83" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F83" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>22</v>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="E84" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F84" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>16</v>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="E85" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F85" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>77</v>
@@ -5213,11 +5213,11 @@
       </c>
       <c r="E86" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F86" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>34</v>
@@ -5256,11 +5256,11 @@
       </c>
       <c r="E87" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F87" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>75</v>
@@ -5299,11 +5299,11 @@
       </c>
       <c r="E88" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F88" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>21</v>
@@ -5343,11 +5343,11 @@
       </c>
       <c r="E89" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F89" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>31</v>
@@ -5387,11 +5387,11 @@
       </c>
       <c r="E90" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F90" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>109</v>
@@ -5428,11 +5428,11 @@
       </c>
       <c r="E91" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F91" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>22</v>
@@ -5472,11 +5472,11 @@
       </c>
       <c r="E92" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F92" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>16</v>
@@ -5516,11 +5516,11 @@
       </c>
       <c r="E93" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F93" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>142</v>
@@ -5560,11 +5560,11 @@
       </c>
       <c r="E94" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F94" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G94" s="17" t="s">
         <v>26</v>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="E95" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F95" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G95" s="17" t="s">
         <v>16</v>
@@ -5652,11 +5652,11 @@
       </c>
       <c r="E96" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F96" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>31</v>
@@ -5696,11 +5696,11 @@
       </c>
       <c r="E97" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F97" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>32</v>
@@ -5740,11 +5740,11 @@
       </c>
       <c r="E98" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F98" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>21</v>
@@ -5784,11 +5784,11 @@
       </c>
       <c r="E99" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F99" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>88</v>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="E100" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F100" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>31</v>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="E101" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F101" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>109</v>
@@ -5916,11 +5916,11 @@
       </c>
       <c r="E102" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F102" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>109</v>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="E103" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F103" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>16</v>
@@ -6004,11 +6004,11 @@
       </c>
       <c r="E104" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F104" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G104" s="12" t="s">
         <v>154</v>
@@ -6048,11 +6048,11 @@
       </c>
       <c r="E105" s="10">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F105" s="12">
         <f ca="1">D105-E105</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -6092,11 +6092,11 @@
       </c>
       <c r="E106" s="10">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F106" s="12">
         <f ca="1">D106-E106</f>
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E107" s="10">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F107" s="12">
         <f ca="1">D107-E107</f>
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -6180,11 +6180,11 @@
       </c>
       <c r="E108" s="10">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F108" s="12">
         <f ca="1">D108-E108</f>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>142</v>
@@ -6224,11 +6224,11 @@
       </c>
       <c r="E109" s="22">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F109" s="23">
         <f ca="1">D109-E109</f>
-        <v>-2041</v>
+        <v>-2042</v>
       </c>
       <c r="G109" s="23" t="s">
         <v>31</v>

--- a/data/Base Instalada.xlsx
+++ b/data/Base Instalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44922D05-E05D-4E63-82AD-D6AFACE39A79}"/>
+  <xr:revisionPtr revIDLastSave="604" documentId="8_{51F1F06D-6D0B-4FE8-9AF7-39931DF9B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91FDB0C9-BDA9-4443-9199-7C0805478FE6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FA3517F6-4E5E-4958-9700-7C1440F86859}"/>
   </bookViews>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="E2" s="35">
         <f t="shared" ref="E2:E33" ca="1" si="0">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F2" s="25">
         <f t="shared" ref="F2:F33" ca="1" si="1">D2-E2</f>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>16</v>
@@ -1589,11 +1589,11 @@
       </c>
       <c r="E3" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
@@ -1633,11 +1633,11 @@
       </c>
       <c r="E4" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>22</v>
@@ -1677,11 +1677,11 @@
       </c>
       <c r="E5" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>23</v>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="E6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>26</v>
@@ -1765,11 +1765,11 @@
       </c>
       <c r="E7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>23</v>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="E8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -1853,11 +1853,11 @@
       </c>
       <c r="E9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-414</v>
+        <v>-415</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>22</v>
@@ -1895,11 +1895,11 @@
       </c>
       <c r="E10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>31</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="E11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>32</v>
@@ -1983,11 +1983,11 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F12" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>34</v>
@@ -2028,11 +2028,11 @@
       </c>
       <c r="E13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>38</v>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="E14" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>16</v>
@@ -2116,11 +2116,11 @@
       </c>
       <c r="E15" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>26</v>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>46</v>
@@ -2204,11 +2204,11 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>49</v>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>16</v>
@@ -2290,11 +2290,11 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>26</v>
@@ -2333,11 +2333,11 @@
       </c>
       <c r="E20" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>16</v>
@@ -2376,11 +2376,11 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>31</v>
@@ -2420,11 +2420,11 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>32</v>
@@ -2464,11 +2464,11 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>38</v>
@@ -2508,11 +2508,11 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F24" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>61</v>
@@ -2554,11 +2554,11 @@
       </c>
       <c r="E25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>61</v>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>34</v>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>34</v>
@@ -2692,11 +2692,11 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>65</v>
@@ -2735,11 +2735,11 @@
       </c>
       <c r="E29" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>32</v>
@@ -2779,11 +2779,11 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>68</v>
@@ -2823,11 +2823,11 @@
       </c>
       <c r="E31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F31" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>16</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="E32" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>31</v>
@@ -2911,11 +2911,11 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>22</v>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="E34" s="10">
         <f t="shared" ref="E34:E68" ca="1" si="4">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F34" s="12">
         <f t="shared" ref="F34:F65" ca="1" si="5">D34-E34</f>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>21</v>
@@ -2999,11 +2999,11 @@
       </c>
       <c r="E35" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F35" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>16</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F36" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>75</v>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F37" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>77</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="E38" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F38" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>75</v>
@@ -3173,11 +3173,11 @@
       </c>
       <c r="E39" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F39" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>31</v>
@@ -3217,11 +3217,11 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F40" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>81</v>
@@ -3261,11 +3261,11 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F41" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G41" s="17" t="s">
         <v>83</v>
@@ -3304,11 +3304,11 @@
       </c>
       <c r="E42" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F42" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>31</v>
@@ -3348,11 +3348,11 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F43" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>32</v>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F44" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>88</v>
@@ -3436,11 +3436,11 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F45" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>31</v>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="E46" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F46" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>16</v>
@@ -3524,11 +3524,11 @@
       </c>
       <c r="E47" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F47" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>21</v>
@@ -3568,11 +3568,11 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F48" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>65</v>
@@ -3614,11 +3614,11 @@
       </c>
       <c r="E49" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F49" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>65</v>
@@ -3658,11 +3658,11 @@
       </c>
       <c r="E50" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F50" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>26</v>
@@ -3704,11 +3704,11 @@
       </c>
       <c r="E51" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F51" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>22</v>
@@ -3750,11 +3750,11 @@
       </c>
       <c r="E52" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F52" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>16</v>
@@ -3796,11 +3796,11 @@
       </c>
       <c r="E53" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F53" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>81</v>
@@ -3840,11 +3840,11 @@
       </c>
       <c r="E54" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F54" s="12">
         <f t="shared" ref="F54" ca="1" si="7">D54-E54</f>
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>98</v>
@@ -3884,11 +3884,11 @@
       </c>
       <c r="E55" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F55" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>22</v>
@@ -3928,11 +3928,11 @@
       </c>
       <c r="E56" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F56" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>102</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="E57" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F57" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>65</v>
@@ -4016,11 +4016,11 @@
       </c>
       <c r="E58" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F58" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>31</v>
@@ -4060,11 +4060,11 @@
       </c>
       <c r="E59" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F59" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>34</v>
@@ -4103,11 +4103,11 @@
       </c>
       <c r="E60" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F60" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>32</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="E61" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F61" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>68</v>
@@ -4191,11 +4191,11 @@
       </c>
       <c r="E62" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F62" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>109</v>
@@ -4235,11 +4235,11 @@
       </c>
       <c r="E63" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F63" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G63" s="12" t="s">
         <v>68</v>
@@ -4279,11 +4279,11 @@
       </c>
       <c r="E64" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F64" s="17">
         <f t="shared" ca="1" si="5"/>
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="G64" s="17" t="s">
         <v>16</v>
@@ -4319,15 +4319,15 @@
         <v>45992</v>
       </c>
       <c r="D65" s="10">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="E65" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F65" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>-35</v>
+        <v>26</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>65</v>
@@ -4366,11 +4366,11 @@
       </c>
       <c r="E66" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F66" s="12">
         <f t="shared" ref="F66:F68" ca="1" si="9">D66-E66</f>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>31</v>
@@ -4410,11 +4410,11 @@
       </c>
       <c r="E67" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F67" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>65</v>
@@ -4454,11 +4454,11 @@
       </c>
       <c r="E68" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F68" s="12">
         <f t="shared" ca="1" si="9"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>32</v>
@@ -4521,11 +4521,11 @@
       </c>
       <c r="E70" s="11">
         <f t="shared" ref="E70:E104" ca="1" si="10">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F70" s="17">
         <f t="shared" ref="F70:F104" ca="1" si="11">D70-E70</f>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G70" s="17" t="s">
         <v>22</v>
@@ -4563,11 +4563,11 @@
       </c>
       <c r="E71" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F71" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>34</v>
@@ -4608,11 +4608,11 @@
       </c>
       <c r="E72" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F72" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>68</v>
@@ -4652,11 +4652,11 @@
       </c>
       <c r="E73" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F73" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>22</v>
@@ -4725,11 +4725,11 @@
       </c>
       <c r="E75" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F75" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G75" s="12" t="s">
         <v>32</v>
@@ -4771,11 +4771,11 @@
       </c>
       <c r="E76" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F76" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G76" s="12" t="s">
         <v>88</v>
@@ -4817,11 +4817,11 @@
       </c>
       <c r="E77" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F77" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>23</v>
@@ -4863,11 +4863,11 @@
       </c>
       <c r="E78" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F78" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>98</v>
@@ -4908,11 +4908,11 @@
       </c>
       <c r="E79" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F79" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>34</v>
@@ -4952,11 +4952,11 @@
       </c>
       <c r="E80" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F80" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G80" s="12" t="s">
         <v>68</v>
@@ -4996,11 +4996,11 @@
       </c>
       <c r="E81" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F81" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>26</v>
@@ -5040,11 +5040,11 @@
       </c>
       <c r="E82" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F82" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>26</v>
@@ -5084,11 +5084,11 @@
       </c>
       <c r="E83" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F83" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>22</v>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="E84" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F84" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>16</v>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="E85" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F85" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G85" s="12" t="s">
         <v>77</v>
@@ -5213,11 +5213,11 @@
       </c>
       <c r="E86" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F86" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>34</v>
@@ -5256,11 +5256,11 @@
       </c>
       <c r="E87" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F87" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>75</v>
@@ -5299,11 +5299,11 @@
       </c>
       <c r="E88" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F88" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G88" s="12" t="s">
         <v>21</v>
@@ -5343,11 +5343,11 @@
       </c>
       <c r="E89" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F89" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>31</v>
@@ -5387,11 +5387,11 @@
       </c>
       <c r="E90" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F90" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>109</v>
@@ -5428,11 +5428,11 @@
       </c>
       <c r="E91" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F91" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G91" s="12" t="s">
         <v>22</v>
@@ -5472,11 +5472,11 @@
       </c>
       <c r="E92" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F92" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G92" s="12" t="s">
         <v>16</v>
@@ -5516,11 +5516,11 @@
       </c>
       <c r="E93" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F93" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>142</v>
@@ -5560,11 +5560,11 @@
       </c>
       <c r="E94" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F94" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G94" s="17" t="s">
         <v>26</v>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="E95" s="11">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F95" s="17">
         <f t="shared" ca="1" si="11"/>
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G95" s="17" t="s">
         <v>16</v>
@@ -5652,11 +5652,11 @@
       </c>
       <c r="E96" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F96" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>31</v>
@@ -5696,11 +5696,11 @@
       </c>
       <c r="E97" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F97" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>32</v>
@@ -5740,11 +5740,11 @@
       </c>
       <c r="E98" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F98" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>21</v>
@@ -5784,11 +5784,11 @@
       </c>
       <c r="E99" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F99" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>88</v>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="E100" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F100" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>31</v>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="E101" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F101" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>109</v>
@@ -5916,11 +5916,11 @@
       </c>
       <c r="E102" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F102" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>109</v>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="E103" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F103" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G103" s="12" t="s">
         <v>16</v>
@@ -6004,11 +6004,11 @@
       </c>
       <c r="E104" s="10">
         <f t="shared" ca="1" si="10"/>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F104" s="12">
         <f t="shared" ca="1" si="11"/>
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G104" s="12" t="s">
         <v>154</v>
@@ -6048,11 +6048,11 @@
       </c>
       <c r="E105" s="10">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F105" s="12">
         <f ca="1">D105-E105</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>38</v>
@@ -6092,11 +6092,11 @@
       </c>
       <c r="E106" s="10">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F106" s="12">
         <f ca="1">D106-E106</f>
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>29</v>
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E107" s="10">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F107" s="12">
         <f ca="1">D107-E107</f>
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>34</v>
@@ -6180,11 +6180,11 @@
       </c>
       <c r="E108" s="10">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F108" s="12">
         <f ca="1">D108-E108</f>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>142</v>
@@ -6224,11 +6224,11 @@
       </c>
       <c r="E109" s="22">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F109" s="23">
         <f ca="1">D109-E109</f>
-        <v>-2042</v>
+        <v>-2043</v>
       </c>
       <c r="G109" s="23" t="s">
         <v>31</v>
